--- a/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
+++ b/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,7 +462,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>490</v>
+        <v>26</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -471,7 +471,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>but-1-yne</t>
+          <t>(Z)-1-fluoroprop-1-ene</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -484,16 +484,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>-18215.21707508305</v>
+        <v>-55976.55926392491</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>513</v>
+        <v>372</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,16 +502,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>but-1-yne</t>
+          <t>buta-1,3-diene</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-67707.3700554548</v>
+        <v>-13217.35369080178</v>
       </c>
     </row>
     <row r="4">
@@ -533,29 +533,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>prop-2-en-1-ol</t>
+          <t>but-1-yne</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>-29469.45577713197</v>
+        <v>-43031.63940057073</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>668</v>
+        <v>846</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -564,16 +564,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(Z)-1-fluoroprop-1-ene</t>
+          <t>prop-2-en-1-ol</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -581,69 +581,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-55976.55926392491</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>695</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>aug-cc-pVDZ</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>buta-1,3-diene</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LUCJ(L=5)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>CCSD</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>-13217.35369080178</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>1042</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>aug-cc-pVDZ</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>but-1-yne</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LUCJ(L=2)</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>MP2</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>-43031.63940057073</v>
+        <v>-29469.45577713197</v>
       </c>
     </row>
   </sheetData>

--- a/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
+++ b/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,7 +462,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>26</v>
+        <v>561</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -471,16 +471,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(Z)-1-fluoroprop-1-ene</t>
+          <t>prop-2-en-1-ol</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -488,12 +488,12 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>-55976.55926392491</v>
+        <v>-29469.45577713197</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>372</v>
+        <v>1041</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -502,86 +502,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>buta-1,3-diene</t>
+          <t>but-1-yne</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-13217.35369080178</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>561</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>aug-cc-pVDZ</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>but-1-yne</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LUCJ(L=2)</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>MP2</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
         <v>-43031.63940057073</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>846</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>aug-cc-pVDZ</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>prop-2-en-1-ol</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LUCJ(L=5)</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ML_exact</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>-29469.45577713197</v>
       </c>
     </row>
   </sheetData>

--- a/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
+++ b/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,37 +489,6 @@
       </c>
       <c r="G2" t="n">
         <v>-29469.45577713197</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1041</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>aug-cc-pVDZ</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>but-1-yne</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LUCJ(L=2)</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>MP2</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>-43031.63940057073</v>
       </c>
     </row>
   </sheetData>

--- a/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
+++ b/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
@@ -462,7 +462,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>561</v>
+        <v>845</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>

--- a/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
+++ b/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-213.1797011444954</v>
+        <v>-212.5076523839172</v>
       </c>
       <c r="H17" t="n">
         <v>9</v>
       </c>
       <c r="I17" t="n">
-        <v>163.9126653559515</v>
+        <v>835.9614259341015</v>
       </c>
       <c r="J17" t="n">
         <v>-213.3436138098513</v>
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-213.2010260388874</v>
+        <v>-213.1913236081741</v>
       </c>
       <c r="H26" t="n">
         <v>9</v>
       </c>
       <c r="I26" t="n">
-        <v>142.5877709638712</v>
+        <v>152.2902016772605</v>
       </c>
       <c r="J26" t="n">
         <v>-213.3436138098513</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-213.1576975976407</v>
+        <v>-213.1453605980934</v>
       </c>
       <c r="H27" t="n">
         <v>9</v>
       </c>
       <c r="I27" t="n">
-        <v>185.9162122106</v>
+        <v>198.2532117579581</v>
       </c>
       <c r="J27" t="n">
         <v>-213.3436138098513</v>
@@ -1657,13 +1657,13 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-213.1494842471058</v>
+        <v>-213.1421481222368</v>
       </c>
       <c r="H28" t="n">
         <v>9</v>
       </c>
       <c r="I28" t="n">
-        <v>194.1295627455588</v>
+        <v>201.4656876145295</v>
       </c>
       <c r="J28" t="n">
         <v>-213.3436138098513</v>
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>-213.1768401791302</v>
+        <v>-213.1504876770753</v>
       </c>
       <c r="H29" t="n">
         <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>166.7736307211385</v>
+        <v>193.1261327760581</v>
       </c>
       <c r="J29" t="n">
         <v>-213.3436138098513</v>
@@ -1745,13 +1745,13 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>-213.2021082851193</v>
+        <v>-213.2021082851187</v>
       </c>
       <c r="H30" t="n">
         <v>9</v>
       </c>
       <c r="I30" t="n">
-        <v>141.5055247320538</v>
+        <v>141.5055247326222</v>
       </c>
       <c r="J30" t="n">
         <v>-213.3436138098513</v>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>-213.3262251973137</v>
+        <v>-213.3245633351582</v>
       </c>
       <c r="H31" t="n">
         <v>9</v>
       </c>
       <c r="I31" t="n">
-        <v>17.3886125376157</v>
+        <v>19.05047469307419</v>
       </c>
       <c r="J31" t="n">
         <v>-213.3436138098513</v>
@@ -1833,13 +1833,13 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>-215.968055814278</v>
+        <v>-214.7028624898805</v>
       </c>
       <c r="H32" t="n">
         <v>9</v>
       </c>
       <c r="I32" t="n">
-        <v>-17.64427274508762</v>
+        <v>1247.549051652413</v>
       </c>
       <c r="J32" t="n">
         <v>-215.950411541533</v>
@@ -2933,13 +2933,13 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>-215.9581723862323</v>
+        <v>-215.9561682360744</v>
       </c>
       <c r="H57" t="n">
         <v>9</v>
       </c>
       <c r="I57" t="n">
-        <v>39.84627146732578</v>
+        <v>41.85042162518471</v>
       </c>
       <c r="J57" t="n">
         <v>-215.9980186576996</v>
@@ -3021,13 +3021,13 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>-215.9644015486025</v>
+        <v>-215.9589175726923</v>
       </c>
       <c r="H59" t="n">
         <v>9</v>
       </c>
       <c r="I59" t="n">
-        <v>33.61710909709359</v>
+        <v>39.10108500727461</v>
       </c>
       <c r="J59" t="n">
         <v>-215.9980186576996</v>
@@ -3109,13 +3109,13 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>-215.9650296003272</v>
+        <v>-215.9462074712169</v>
       </c>
       <c r="H61" t="n">
         <v>9</v>
       </c>
       <c r="I61" t="n">
-        <v>32.98905737241853</v>
+        <v>51.81118648269489</v>
       </c>
       <c r="J61" t="n">
         <v>-215.9980186576996</v>
@@ -3153,13 +3153,13 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>-215.9927398868854</v>
+        <v>-215.9924367471406</v>
       </c>
       <c r="H62" t="n">
         <v>9</v>
       </c>
       <c r="I62" t="n">
-        <v>5.278770814214795</v>
+        <v>5.58191055895918</v>
       </c>
       <c r="J62" t="n">
         <v>-215.9980186576996</v>
@@ -4825,13 +4825,13 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>-154.0374616701789</v>
+        <v>-152.5516160270816</v>
       </c>
       <c r="H100" t="n">
         <v>10</v>
       </c>
       <c r="I100" t="n">
-        <v>880.4808055724038</v>
+        <v>2366.326448669724</v>
       </c>
       <c r="J100" t="n">
         <v>-154.9179424757513</v>
@@ -6805,13 +6805,13 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>-152.4172048110165</v>
+        <v>-150.9927345104938</v>
       </c>
       <c r="H145" t="n">
         <v>10</v>
       </c>
       <c r="I145" t="n">
-        <v>888.2046307869587</v>
+        <v>2312.67493130963</v>
       </c>
       <c r="J145" t="n">
         <v>-153.3054094418034</v>
@@ -7685,13 +7685,13 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>-154.9418518681631</v>
+        <v>-153.2907289076241</v>
       </c>
       <c r="H165" t="n">
         <v>10</v>
       </c>
       <c r="I165" t="n">
-        <v>8.77657079678329</v>
+        <v>1659.899531335782</v>
       </c>
       <c r="J165" t="n">
         <v>-154.9506284389599</v>
@@ -8169,13 +8169,13 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>-154.9428967494533</v>
+        <v>-153.6477628265835</v>
       </c>
       <c r="H176" t="n">
         <v>10</v>
       </c>
       <c r="I176" t="n">
-        <v>7.731689506613293</v>
+        <v>1302.865612376422</v>
       </c>
       <c r="J176" t="n">
         <v>-154.9506284389599</v>
@@ -9093,13 +9093,13 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>-154.9357737754797</v>
+        <v>-153.8618972276274</v>
       </c>
       <c r="H197" t="n">
         <v>10</v>
       </c>
       <c r="I197" t="n">
-        <v>79.67717566805277</v>
+        <v>1153.553723520361</v>
       </c>
       <c r="J197" t="n">
         <v>-155.0154509511478</v>
@@ -9753,13 +9753,13 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>-154.1883851378736</v>
+        <v>-153.7263205808158</v>
       </c>
       <c r="H212" t="n">
         <v>10</v>
       </c>
       <c r="I212" t="n">
-        <v>827.065813274146</v>
+        <v>1289.130370331975</v>
       </c>
       <c r="J212" t="n">
         <v>-155.0154509511478</v>
@@ -15175,13 +15175,13 @@
         </is>
       </c>
       <c r="G333" t="n">
-        <v>-191.9517670449475</v>
+        <v>-190.9183003641962</v>
       </c>
       <c r="H333" t="n">
         <v>10</v>
       </c>
       <c r="I333" t="n">
-        <v>2.004920530794152</v>
+        <v>1035.471601282154</v>
       </c>
       <c r="J333" t="n">
         <v>-191.9537719654783</v>

--- a/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
+++ b/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
@@ -519,13 +519,13 @@
         <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>97.78897019253918</v>
+        <v>97.78897019251076</v>
       </c>
       <c r="J2" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K2" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L2" t="inlineStr"/>
     </row>
@@ -563,13 +563,13 @@
         <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>85.42605764614564</v>
+        <v>85.42605764611721</v>
       </c>
       <c r="J3" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K3" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L3" t="inlineStr"/>
     </row>
@@ -607,13 +607,13 @@
         <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>70.44302343706477</v>
+        <v>70.44302343703635</v>
       </c>
       <c r="J4" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K4" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L4" t="inlineStr"/>
     </row>
@@ -651,13 +651,13 @@
         <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>58.82106509977802</v>
+        <v>58.8210650997496</v>
       </c>
       <c r="J5" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K5" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L5" t="inlineStr"/>
     </row>
@@ -695,13 +695,13 @@
         <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>798.5863601214191</v>
+        <v>798.5863601213907</v>
       </c>
       <c r="J6" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K6" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L6" t="inlineStr"/>
     </row>
@@ -739,13 +739,13 @@
         <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>17.69744216164781</v>
+        <v>17.69744216161939</v>
       </c>
       <c r="J7" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K7" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L7" t="inlineStr"/>
     </row>
@@ -783,13 +783,13 @@
         <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>150.5791615635985</v>
+        <v>150.5791615635701</v>
       </c>
       <c r="J8" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K8" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L8" t="inlineStr"/>
     </row>
@@ -827,13 +827,13 @@
         <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>167.0778928564118</v>
+        <v>167.0778928563834</v>
       </c>
       <c r="J9" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K9" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L9" t="inlineStr"/>
     </row>
@@ -871,13 +871,13 @@
         <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>182.7483257481504</v>
+        <v>182.7483257481219</v>
       </c>
       <c r="J10" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K10" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L10" t="inlineStr"/>
     </row>
@@ -915,13 +915,13 @@
         <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>179.2834781073225</v>
+        <v>179.2834781072941</v>
       </c>
       <c r="J11" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K11" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L11" t="inlineStr"/>
     </row>
@@ -959,13 +959,13 @@
         <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>157.5608317025967</v>
+        <v>157.5608317025683</v>
       </c>
       <c r="J12" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K12" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L12" t="inlineStr"/>
     </row>
@@ -1003,13 +1003,13 @@
         <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>18.44382450059356</v>
+        <v>18.44382450056514</v>
       </c>
       <c r="J13" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K13" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L13" t="inlineStr"/>
     </row>
@@ -1047,13 +1047,13 @@
         <v>9</v>
       </c>
       <c r="I14" t="n">
-        <v>196.3063879067022</v>
+        <v>196.3063879066738</v>
       </c>
       <c r="J14" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K14" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L14" t="inlineStr"/>
     </row>
@@ -1091,13 +1091,13 @@
         <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>1042.96675087113</v>
+        <v>1042.966750871102</v>
       </c>
       <c r="J15" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K15" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L15" t="inlineStr"/>
     </row>
@@ -1135,13 +1135,13 @@
         <v>9</v>
       </c>
       <c r="I16" t="n">
-        <v>170.6724462550255</v>
+        <v>170.6724462549971</v>
       </c>
       <c r="J16" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K16" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L16" t="inlineStr"/>
     </row>
@@ -1179,13 +1179,13 @@
         <v>9</v>
       </c>
       <c r="I17" t="n">
-        <v>835.9614259341015</v>
+        <v>835.9614259340731</v>
       </c>
       <c r="J17" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K17" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L17" t="inlineStr"/>
     </row>
@@ -1223,13 +1223,13 @@
         <v>9</v>
       </c>
       <c r="I18" t="n">
-        <v>179.6927643403592</v>
+        <v>179.6927643403308</v>
       </c>
       <c r="J18" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K18" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L18" t="inlineStr"/>
     </row>
@@ -1267,13 +1267,13 @@
         <v>9</v>
       </c>
       <c r="I19" t="n">
-        <v>18.49148252262012</v>
+        <v>18.4914825225917</v>
       </c>
       <c r="J19" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K19" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L19" t="inlineStr"/>
     </row>
@@ -1311,13 +1311,13 @@
         <v>9</v>
       </c>
       <c r="I20" t="n">
-        <v>177.6330090170291</v>
+        <v>177.6330090170006</v>
       </c>
       <c r="J20" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K20" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L20" t="inlineStr"/>
     </row>
@@ -1355,13 +1355,13 @@
         <v>9</v>
       </c>
       <c r="I21" t="n">
-        <v>220.5363056493752</v>
+        <v>220.5363056493468</v>
       </c>
       <c r="J21" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K21" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L21" t="inlineStr"/>
     </row>
@@ -1399,13 +1399,13 @@
         <v>9</v>
       </c>
       <c r="I22" t="n">
-        <v>191.4272931518894</v>
+        <v>191.427293151861</v>
       </c>
       <c r="J22" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K22" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L22" t="inlineStr"/>
     </row>
@@ -1443,13 +1443,13 @@
         <v>9</v>
       </c>
       <c r="I23" t="n">
-        <v>967.9668978873224</v>
+        <v>967.966897887294</v>
       </c>
       <c r="J23" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K23" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L23" t="inlineStr"/>
     </row>
@@ -1487,13 +1487,13 @@
         <v>9</v>
       </c>
       <c r="I24" t="n">
-        <v>156.787370570612</v>
+        <v>156.7873705705836</v>
       </c>
       <c r="J24" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K24" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L24" t="inlineStr"/>
     </row>
@@ -1531,13 +1531,13 @@
         <v>9</v>
       </c>
       <c r="I25" t="n">
-        <v>24.39224118927541</v>
+        <v>24.39224118924699</v>
       </c>
       <c r="J25" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K25" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L25" t="inlineStr"/>
     </row>
@@ -1575,13 +1575,13 @@
         <v>9</v>
       </c>
       <c r="I26" t="n">
-        <v>152.2902016772605</v>
+        <v>152.2902016772321</v>
       </c>
       <c r="J26" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K26" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L26" t="inlineStr"/>
     </row>
@@ -1619,13 +1619,13 @@
         <v>9</v>
       </c>
       <c r="I27" t="n">
-        <v>198.2532117579581</v>
+        <v>198.2532117579296</v>
       </c>
       <c r="J27" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K27" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L27" t="inlineStr"/>
     </row>
@@ -1663,13 +1663,13 @@
         <v>9</v>
       </c>
       <c r="I28" t="n">
-        <v>201.4656876145295</v>
+        <v>201.4656876145011</v>
       </c>
       <c r="J28" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K28" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L28" t="inlineStr"/>
     </row>
@@ -1707,13 +1707,13 @@
         <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>193.1261327760581</v>
+        <v>193.1261327760296</v>
       </c>
       <c r="J29" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K29" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L29" t="inlineStr"/>
     </row>
@@ -1751,13 +1751,13 @@
         <v>9</v>
       </c>
       <c r="I30" t="n">
-        <v>141.5055247326222</v>
+        <v>141.5055247325938</v>
       </c>
       <c r="J30" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K30" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L30" t="inlineStr"/>
     </row>
@@ -1795,13 +1795,13 @@
         <v>9</v>
       </c>
       <c r="I31" t="n">
-        <v>19.05047469307419</v>
+        <v>19.05047469304577</v>
       </c>
       <c r="J31" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K31" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L31" t="inlineStr"/>
     </row>
@@ -15577,10 +15577,10 @@
         <v>10</v>
       </c>
       <c r="I342" t="n">
-        <v>44.03229792811203</v>
+        <v>44.03229792816887</v>
       </c>
       <c r="J342" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K342" t="n">
         <v>-191.9364953941601</v>
@@ -15621,10 +15621,10 @@
         <v>10</v>
       </c>
       <c r="I343" t="n">
-        <v>23.61748927765461</v>
+        <v>23.61748927771146</v>
       </c>
       <c r="J343" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K343" t="n">
         <v>-191.9364953941601</v>
@@ -15665,10 +15665,10 @@
         <v>10</v>
       </c>
       <c r="I344" t="n">
-        <v>22.89456684908941</v>
+        <v>22.89456684914626</v>
       </c>
       <c r="J344" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K344" t="n">
         <v>-191.9364953941601</v>
@@ -15709,10 +15709,10 @@
         <v>10</v>
       </c>
       <c r="I345" t="n">
-        <v>22.4169098180198</v>
+        <v>22.41690981807665</v>
       </c>
       <c r="J345" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K345" t="n">
         <v>-191.9364953941601</v>
@@ -15753,10 +15753,10 @@
         <v>10</v>
       </c>
       <c r="I346" t="n">
-        <v>59.4595150388102</v>
+        <v>59.45951503886704</v>
       </c>
       <c r="J346" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K346" t="n">
         <v>-191.9364953941601</v>
@@ -15797,10 +15797,10 @@
         <v>10</v>
       </c>
       <c r="I347" t="n">
-        <v>5.350145259257033</v>
+        <v>5.350145259313877</v>
       </c>
       <c r="J347" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K347" t="n">
         <v>-191.9364953941601</v>
@@ -15841,10 +15841,10 @@
         <v>10</v>
       </c>
       <c r="I348" t="n">
-        <v>58.60010115898717</v>
+        <v>58.60010115904402</v>
       </c>
       <c r="J348" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K348" t="n">
         <v>-191.9364953941601</v>
@@ -15885,10 +15885,10 @@
         <v>10</v>
       </c>
       <c r="I349" t="n">
-        <v>41.43802507618943</v>
+        <v>41.43802507624628</v>
       </c>
       <c r="J349" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K349" t="n">
         <v>-191.9364953941601</v>
@@ -15929,10 +15929,10 @@
         <v>10</v>
       </c>
       <c r="I350" t="n">
-        <v>607.0629625944832</v>
+        <v>607.0629625945401</v>
       </c>
       <c r="J350" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K350" t="n">
         <v>-191.9364953941601</v>
@@ -15973,10 +15973,10 @@
         <v>10</v>
       </c>
       <c r="I351" t="n">
-        <v>44.55755224185509</v>
+        <v>44.55755224191194</v>
       </c>
       <c r="J351" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K351" t="n">
         <v>-191.9364953941601</v>
@@ -16017,10 +16017,10 @@
         <v>10</v>
       </c>
       <c r="I352" t="n">
-        <v>47.54739200629388</v>
+        <v>47.54739200635072</v>
       </c>
       <c r="J352" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K352" t="n">
         <v>-191.9364953941601</v>
@@ -16061,10 +16061,10 @@
         <v>10</v>
       </c>
       <c r="I353" t="n">
-        <v>4.66204871409559</v>
+        <v>4.662048714152434</v>
       </c>
       <c r="J353" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K353" t="n">
         <v>-191.9364953941601</v>
@@ -16105,10 +16105,10 @@
         <v>10</v>
       </c>
       <c r="I354" t="n">
-        <v>58.80453826060261</v>
+        <v>58.80453826065946</v>
       </c>
       <c r="J354" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K354" t="n">
         <v>-191.9364953941601</v>
@@ -16149,10 +16149,10 @@
         <v>10</v>
       </c>
       <c r="I355" t="n">
-        <v>57.98485100396533</v>
+        <v>57.98485100402218</v>
       </c>
       <c r="J355" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K355" t="n">
         <v>-191.9364953941601</v>
@@ -16193,10 +16193,10 @@
         <v>10</v>
       </c>
       <c r="I356" t="n">
-        <v>854.1860243963981</v>
+        <v>854.186024396455</v>
       </c>
       <c r="J356" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K356" t="n">
         <v>-191.9364953941601</v>
@@ -16237,10 +16237,10 @@
         <v>10</v>
       </c>
       <c r="I357" t="n">
-        <v>58.9536823763126</v>
+        <v>58.95368237636944</v>
       </c>
       <c r="J357" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K357" t="n">
         <v>-191.9364953941601</v>
@@ -16281,10 +16281,10 @@
         <v>10</v>
       </c>
       <c r="I358" t="n">
-        <v>60.10677300346856</v>
+        <v>60.1067730035254</v>
       </c>
       <c r="J358" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K358" t="n">
         <v>-191.9364953941601</v>
@@ -16325,10 +16325,10 @@
         <v>10</v>
       </c>
       <c r="I359" t="n">
-        <v>4.985772473588668</v>
+        <v>4.985772473645511</v>
       </c>
       <c r="J359" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K359" t="n">
         <v>-191.9364953941601</v>
@@ -16369,10 +16369,10 @@
         <v>10</v>
       </c>
       <c r="I360" t="n">
-        <v>47.00246746583048</v>
+        <v>47.00246746588732</v>
       </c>
       <c r="J360" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K360" t="n">
         <v>-191.9364953941601</v>
@@ -16413,10 +16413,10 @@
         <v>10</v>
       </c>
       <c r="I361" t="n">
-        <v>616.6231967843885</v>
+        <v>616.6231967844453</v>
       </c>
       <c r="J361" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K361" t="n">
         <v>-191.9364953941601</v>
@@ -16457,10 +16457,10 @@
         <v>10</v>
       </c>
       <c r="I362" t="n">
-        <v>723.3386960838004</v>
+        <v>723.3386960838573</v>
       </c>
       <c r="J362" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K362" t="n">
         <v>-191.9364953941601</v>
@@ -16501,10 +16501,10 @@
         <v>10</v>
       </c>
       <c r="I363" t="n">
-        <v>58.12555555471022</v>
+        <v>58.12555555476706</v>
       </c>
       <c r="J363" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K363" t="n">
         <v>-191.9364953941601</v>
@@ -16545,10 +16545,10 @@
         <v>10</v>
       </c>
       <c r="I364" t="n">
-        <v>970.9292260958193</v>
+        <v>970.9292260958762</v>
       </c>
       <c r="J364" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K364" t="n">
         <v>-191.9364953941601</v>
@@ -16589,10 +16589,10 @@
         <v>10</v>
       </c>
       <c r="I365" t="n">
-        <v>5.465570151642396</v>
+        <v>5.465570151699239</v>
       </c>
       <c r="J365" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K365" t="n">
         <v>-191.9364953941601</v>
@@ -16633,10 +16633,10 @@
         <v>10</v>
       </c>
       <c r="I366" t="n">
-        <v>45.10045692356357</v>
+        <v>45.10045692362041</v>
       </c>
       <c r="J366" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K366" t="n">
         <v>-191.9364953941601</v>
@@ -16677,10 +16677,10 @@
         <v>10</v>
       </c>
       <c r="I367" t="n">
-        <v>59.40461628173921</v>
+        <v>59.40461628179605</v>
       </c>
       <c r="J367" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K367" t="n">
         <v>-191.9364953941601</v>
@@ -16721,10 +16721,10 @@
         <v>10</v>
       </c>
       <c r="I368" t="n">
-        <v>874.5082980433665</v>
+        <v>874.5082980434233</v>
       </c>
       <c r="J368" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K368" t="n">
         <v>-191.9364953941601</v>
@@ -16765,10 +16765,10 @@
         <v>10</v>
       </c>
       <c r="I369" t="n">
-        <v>43.11670959603475</v>
+        <v>43.1167095960916</v>
       </c>
       <c r="J369" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K369" t="n">
         <v>-191.9364953941601</v>
@@ -16809,10 +16809,10 @@
         <v>10</v>
       </c>
       <c r="I370" t="n">
-        <v>57.50251164207043</v>
+        <v>57.50251164212727</v>
       </c>
       <c r="J370" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K370" t="n">
         <v>-191.9364953941601</v>
@@ -16853,10 +16853,10 @@
         <v>10</v>
       </c>
       <c r="I371" t="n">
-        <v>5.28800995729739</v>
+        <v>5.288009957354234</v>
       </c>
       <c r="J371" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K371" t="n">
         <v>-191.9364953941601</v>

--- a/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
+++ b/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L371"/>
+  <dimension ref="A1:L373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,13 +519,13 @@
         <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>97.78897019251076</v>
+        <v>97.78897019253918</v>
       </c>
       <c r="J2" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K2" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L2" t="inlineStr"/>
     </row>
@@ -563,13 +563,13 @@
         <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>85.42605764611721</v>
+        <v>85.42605764614564</v>
       </c>
       <c r="J3" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K3" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L3" t="inlineStr"/>
     </row>
@@ -607,13 +607,13 @@
         <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>70.44302343703635</v>
+        <v>70.44302343706477</v>
       </c>
       <c r="J4" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K4" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L4" t="inlineStr"/>
     </row>
@@ -651,13 +651,13 @@
         <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>58.8210650997496</v>
+        <v>58.82106509977802</v>
       </c>
       <c r="J5" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K5" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L5" t="inlineStr"/>
     </row>
@@ -695,13 +695,13 @@
         <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>798.5863601213907</v>
+        <v>798.5863601214191</v>
       </c>
       <c r="J6" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K6" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L6" t="inlineStr"/>
     </row>
@@ -739,13 +739,13 @@
         <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>17.69744216161939</v>
+        <v>17.69744216164781</v>
       </c>
       <c r="J7" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K7" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L7" t="inlineStr"/>
     </row>
@@ -783,13 +783,13 @@
         <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>150.5791615635701</v>
+        <v>150.5791615635985</v>
       </c>
       <c r="J8" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K8" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L8" t="inlineStr"/>
     </row>
@@ -827,13 +827,13 @@
         <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>167.0778928563834</v>
+        <v>167.0778928564118</v>
       </c>
       <c r="J9" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K9" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L9" t="inlineStr"/>
     </row>
@@ -871,13 +871,13 @@
         <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>182.7483257481219</v>
+        <v>182.7483257481504</v>
       </c>
       <c r="J10" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K10" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L10" t="inlineStr"/>
     </row>
@@ -915,13 +915,13 @@
         <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>179.2834781072941</v>
+        <v>179.2834781073225</v>
       </c>
       <c r="J11" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K11" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L11" t="inlineStr"/>
     </row>
@@ -959,13 +959,13 @@
         <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>157.5608317025683</v>
+        <v>157.5608317025967</v>
       </c>
       <c r="J12" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K12" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L12" t="inlineStr"/>
     </row>
@@ -1003,13 +1003,13 @@
         <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>18.44382450056514</v>
+        <v>18.44382450059356</v>
       </c>
       <c r="J13" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K13" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L13" t="inlineStr"/>
     </row>
@@ -1047,13 +1047,13 @@
         <v>9</v>
       </c>
       <c r="I14" t="n">
-        <v>196.3063879066738</v>
+        <v>196.3063879067022</v>
       </c>
       <c r="J14" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K14" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L14" t="inlineStr"/>
     </row>
@@ -1091,13 +1091,13 @@
         <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>1042.966750871102</v>
+        <v>1042.96675087113</v>
       </c>
       <c r="J15" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K15" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L15" t="inlineStr"/>
     </row>
@@ -1135,13 +1135,13 @@
         <v>9</v>
       </c>
       <c r="I16" t="n">
-        <v>170.6724462549971</v>
+        <v>170.6724462550255</v>
       </c>
       <c r="J16" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K16" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L16" t="inlineStr"/>
     </row>
@@ -1179,13 +1179,13 @@
         <v>9</v>
       </c>
       <c r="I17" t="n">
-        <v>835.9614259340731</v>
+        <v>835.9614259341015</v>
       </c>
       <c r="J17" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K17" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L17" t="inlineStr"/>
     </row>
@@ -1223,13 +1223,13 @@
         <v>9</v>
       </c>
       <c r="I18" t="n">
-        <v>179.6927643403308</v>
+        <v>179.6927643403592</v>
       </c>
       <c r="J18" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K18" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L18" t="inlineStr"/>
     </row>
@@ -1267,13 +1267,13 @@
         <v>9</v>
       </c>
       <c r="I19" t="n">
-        <v>18.4914825225917</v>
+        <v>18.49148252262012</v>
       </c>
       <c r="J19" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K19" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L19" t="inlineStr"/>
     </row>
@@ -1311,13 +1311,13 @@
         <v>9</v>
       </c>
       <c r="I20" t="n">
-        <v>177.6330090170006</v>
+        <v>177.6330090170291</v>
       </c>
       <c r="J20" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K20" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L20" t="inlineStr"/>
     </row>
@@ -1355,13 +1355,13 @@
         <v>9</v>
       </c>
       <c r="I21" t="n">
-        <v>220.5363056493468</v>
+        <v>220.5363056493752</v>
       </c>
       <c r="J21" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K21" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L21" t="inlineStr"/>
     </row>
@@ -1399,13 +1399,13 @@
         <v>9</v>
       </c>
       <c r="I22" t="n">
-        <v>191.427293151861</v>
+        <v>191.4272931518894</v>
       </c>
       <c r="J22" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K22" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L22" t="inlineStr"/>
     </row>
@@ -1443,13 +1443,13 @@
         <v>9</v>
       </c>
       <c r="I23" t="n">
-        <v>967.966897887294</v>
+        <v>967.9668978873224</v>
       </c>
       <c r="J23" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K23" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L23" t="inlineStr"/>
     </row>
@@ -1487,13 +1487,13 @@
         <v>9</v>
       </c>
       <c r="I24" t="n">
-        <v>156.7873705705836</v>
+        <v>156.787370570612</v>
       </c>
       <c r="J24" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K24" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L24" t="inlineStr"/>
     </row>
@@ -1531,13 +1531,13 @@
         <v>9</v>
       </c>
       <c r="I25" t="n">
-        <v>24.39224118924699</v>
+        <v>24.39224118927541</v>
       </c>
       <c r="J25" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K25" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L25" t="inlineStr"/>
     </row>
@@ -1575,13 +1575,13 @@
         <v>9</v>
       </c>
       <c r="I26" t="n">
-        <v>152.2902016772321</v>
+        <v>152.2902016772605</v>
       </c>
       <c r="J26" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K26" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L26" t="inlineStr"/>
     </row>
@@ -1619,13 +1619,13 @@
         <v>9</v>
       </c>
       <c r="I27" t="n">
-        <v>198.2532117579296</v>
+        <v>198.2532117579581</v>
       </c>
       <c r="J27" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K27" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L27" t="inlineStr"/>
     </row>
@@ -1663,13 +1663,13 @@
         <v>9</v>
       </c>
       <c r="I28" t="n">
-        <v>201.4656876145011</v>
+        <v>201.4656876145295</v>
       </c>
       <c r="J28" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K28" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L28" t="inlineStr"/>
     </row>
@@ -1707,13 +1707,13 @@
         <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>193.1261327760296</v>
+        <v>193.1261327760581</v>
       </c>
       <c r="J29" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K29" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L29" t="inlineStr"/>
     </row>
@@ -1751,13 +1751,13 @@
         <v>9</v>
       </c>
       <c r="I30" t="n">
-        <v>141.5055247325938</v>
+        <v>141.5055247326222</v>
       </c>
       <c r="J30" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K30" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L30" t="inlineStr"/>
     </row>
@@ -1795,13 +1795,13 @@
         <v>9</v>
       </c>
       <c r="I31" t="n">
-        <v>19.05047469304577</v>
+        <v>19.05047469307419</v>
       </c>
       <c r="J31" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K31" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L31" t="inlineStr"/>
     </row>
@@ -4505,25 +4505,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>-153.7883019965702</v>
+        <v>-152.6307807091584</v>
       </c>
       <c r="H93" t="n">
         <v>10</v>
       </c>
       <c r="I93" t="n">
-        <v>1129.640479181148</v>
+        <v>2287.161766592931</v>
       </c>
       <c r="J93" t="n">
         <v>-154.9179424757513</v>
@@ -4557,17 +4557,17 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>-154.1403536040909</v>
+        <v>-153.7883019965702</v>
       </c>
       <c r="H94" t="n">
         <v>10</v>
       </c>
       <c r="I94" t="n">
-        <v>777.5888716604413</v>
+        <v>1129.640479181148</v>
       </c>
       <c r="J94" t="n">
         <v>-154.9179424757513</v>
@@ -4593,25 +4593,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>-153.8484792747023</v>
+        <v>-154.1403536040909</v>
       </c>
       <c r="H95" t="n">
         <v>10</v>
       </c>
       <c r="I95" t="n">
-        <v>1069.463201049018</v>
+        <v>777.5888716604413</v>
       </c>
       <c r="J95" t="n">
         <v>-154.9179424757513</v>
@@ -4645,17 +4645,17 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>-154.0723245882149</v>
+        <v>-153.8484792747023</v>
       </c>
       <c r="H96" t="n">
         <v>10</v>
       </c>
       <c r="I96" t="n">
-        <v>845.6178875363776</v>
+        <v>1069.463201049018</v>
       </c>
       <c r="J96" t="n">
         <v>-154.9179424757513</v>
@@ -4689,17 +4689,17 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>-154.1052151121582</v>
+        <v>-154.0723245882149</v>
       </c>
       <c r="H97" t="n">
         <v>10</v>
       </c>
       <c r="I97" t="n">
-        <v>812.727363593126</v>
+        <v>845.6178875363776</v>
       </c>
       <c r="J97" t="n">
         <v>-154.9179424757513</v>
@@ -4725,25 +4725,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>-153.9810908348413</v>
+        <v>-154.1052151121582</v>
       </c>
       <c r="H98" t="n">
         <v>10</v>
       </c>
       <c r="I98" t="n">
-        <v>936.8516409100494</v>
+        <v>812.727363593126</v>
       </c>
       <c r="J98" t="n">
         <v>-154.9179424757513</v>
@@ -4777,17 +4777,17 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>-154.0936799418998</v>
+        <v>-153.9810908348413</v>
       </c>
       <c r="H99" t="n">
         <v>10</v>
       </c>
       <c r="I99" t="n">
-        <v>824.2625338515381</v>
+        <v>936.8516409100494</v>
       </c>
       <c r="J99" t="n">
         <v>-154.9179424757513</v>
@@ -4813,25 +4813,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>-152.5516160270816</v>
+        <v>-154.0936799418998</v>
       </c>
       <c r="H100" t="n">
         <v>10</v>
       </c>
       <c r="I100" t="n">
-        <v>2366.326448669724</v>
+        <v>824.2625338515381</v>
       </c>
       <c r="J100" t="n">
         <v>-154.9179424757513</v>
@@ -4865,17 +4865,17 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>-154.0822000866224</v>
+        <v>-152.5516160270816</v>
       </c>
       <c r="H101" t="n">
         <v>10</v>
       </c>
       <c r="I101" t="n">
-        <v>835.7423891288818</v>
+        <v>2366.326448669724</v>
       </c>
       <c r="J101" t="n">
         <v>-154.9179424757513</v>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>cc-pVDZ</t>
+          <t>aug-cc-pVDZ</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4901,31 +4901,31 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>-154.9604387305679</v>
+        <v>-154.0822000866224</v>
       </c>
       <c r="H102" t="n">
         <v>10</v>
       </c>
       <c r="I102" t="n">
-        <v>40.00963367150234</v>
+        <v>835.7423891288818</v>
       </c>
       <c r="J102" t="n">
-        <v>-155.0004483642394</v>
+        <v>-154.9179424757513</v>
       </c>
       <c r="K102" t="n">
-        <v>-154.9113882737664</v>
+        <v>-154.9167852198248</v>
       </c>
       <c r="L102" t="inlineStr"/>
     </row>
@@ -4953,17 +4953,17 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>-154.9371994097458</v>
+        <v>-154.9604387305679</v>
       </c>
       <c r="H103" t="n">
         <v>10</v>
       </c>
       <c r="I103" t="n">
-        <v>63.24895449364476</v>
+        <v>40.00963367150234</v>
       </c>
       <c r="J103" t="n">
         <v>-155.0004483642394</v>
@@ -4997,17 +4997,17 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>-154.9476789329767</v>
+        <v>-154.9371994097458</v>
       </c>
       <c r="H104" t="n">
         <v>10</v>
       </c>
       <c r="I104" t="n">
-        <v>52.76943126278866</v>
+        <v>63.24895449364476</v>
       </c>
       <c r="J104" t="n">
         <v>-155.0004483642394</v>
@@ -5041,17 +5041,17 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>-154.9746179553749</v>
+        <v>-154.9476789329767</v>
       </c>
       <c r="H105" t="n">
         <v>10</v>
       </c>
       <c r="I105" t="n">
-        <v>25.83040886452181</v>
+        <v>52.76943126278866</v>
       </c>
       <c r="J105" t="n">
         <v>-155.0004483642394</v>
@@ -5085,17 +5085,17 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>-154.1756441030229</v>
+        <v>-154.9746179553749</v>
       </c>
       <c r="H106" t="n">
         <v>10</v>
       </c>
       <c r="I106" t="n">
-        <v>824.8042612165136</v>
+        <v>25.83040886452181</v>
       </c>
       <c r="J106" t="n">
         <v>-155.0004483642394</v>
@@ -5129,17 +5129,17 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>-154.9924580310285</v>
+        <v>-154.1756441030229</v>
       </c>
       <c r="H107" t="n">
         <v>10</v>
       </c>
       <c r="I107" t="n">
-        <v>7.99033321089837</v>
+        <v>824.8042612165136</v>
       </c>
       <c r="J107" t="n">
         <v>-155.0004483642394</v>
@@ -5165,25 +5165,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>-154.9168910292446</v>
+        <v>-154.9924580310285</v>
       </c>
       <c r="H108" t="n">
         <v>10</v>
       </c>
       <c r="I108" t="n">
-        <v>83.55733499485041</v>
+        <v>7.99033321089837</v>
       </c>
       <c r="J108" t="n">
         <v>-155.0004483642394</v>
@@ -5217,17 +5217,17 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>-154.9126678451285</v>
+        <v>-154.9168910292446</v>
       </c>
       <c r="H109" t="n">
         <v>10</v>
       </c>
       <c r="I109" t="n">
-        <v>87.78051911093598</v>
+        <v>83.55733499485041</v>
       </c>
       <c r="J109" t="n">
         <v>-155.0004483642394</v>
@@ -5261,17 +5261,17 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>-154.3087374891909</v>
+        <v>-154.9126678451285</v>
       </c>
       <c r="H110" t="n">
         <v>10</v>
       </c>
       <c r="I110" t="n">
-        <v>691.7108750485568</v>
+        <v>87.78051911093598</v>
       </c>
       <c r="J110" t="n">
         <v>-155.0004483642394</v>
@@ -5305,17 +5305,17 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>-154.1265950108659</v>
+        <v>-154.3087374891909</v>
       </c>
       <c r="H111" t="n">
         <v>10</v>
       </c>
       <c r="I111" t="n">
-        <v>873.8533533735904</v>
+        <v>691.7108750485568</v>
       </c>
       <c r="J111" t="n">
         <v>-155.0004483642394</v>
@@ -5349,17 +5349,17 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>-154.2105318303757</v>
+        <v>-154.1265950108659</v>
       </c>
       <c r="H112" t="n">
         <v>10</v>
       </c>
       <c r="I112" t="n">
-        <v>789.9165338637886</v>
+        <v>873.8533533735904</v>
       </c>
       <c r="J112" t="n">
         <v>-155.0004483642394</v>
@@ -5393,17 +5393,17 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>-154.9909733297587</v>
+        <v>-154.2105318303757</v>
       </c>
       <c r="H113" t="n">
         <v>10</v>
       </c>
       <c r="I113" t="n">
-        <v>9.475034480715294</v>
+        <v>789.9165338637886</v>
       </c>
       <c r="J113" t="n">
         <v>-155.0004483642394</v>
@@ -5429,25 +5429,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>-154.9236801062594</v>
+        <v>-154.9909733297587</v>
       </c>
       <c r="H114" t="n">
         <v>10</v>
       </c>
       <c r="I114" t="n">
-        <v>76.76825798000664</v>
+        <v>9.475034480715294</v>
       </c>
       <c r="J114" t="n">
         <v>-155.0004483642394</v>
@@ -5481,17 +5481,17 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>-154.2608204602884</v>
+        <v>-154.9236801062594</v>
       </c>
       <c r="H115" t="n">
         <v>10</v>
       </c>
       <c r="I115" t="n">
-        <v>739.6279039510887</v>
+        <v>76.76825798000664</v>
       </c>
       <c r="J115" t="n">
         <v>-155.0004483642394</v>
@@ -5525,17 +5525,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>-154.9180734742404</v>
+        <v>-154.2608204602884</v>
       </c>
       <c r="H116" t="n">
         <v>10</v>
       </c>
       <c r="I116" t="n">
-        <v>82.37488999907328</v>
+        <v>739.6279039510887</v>
       </c>
       <c r="J116" t="n">
         <v>-155.0004483642394</v>
@@ -5569,17 +5569,17 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>-154.1275624523181</v>
+        <v>-154.9180734742404</v>
       </c>
       <c r="H117" t="n">
         <v>10</v>
       </c>
       <c r="I117" t="n">
-        <v>872.8859119213439</v>
+        <v>82.37488999907328</v>
       </c>
       <c r="J117" t="n">
         <v>-155.0004483642394</v>
@@ -5613,17 +5613,17 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>-154.9165278927681</v>
+        <v>-154.1275624523181</v>
       </c>
       <c r="H118" t="n">
         <v>10</v>
       </c>
       <c r="I118" t="n">
-        <v>83.92047147134463</v>
+        <v>872.8859119213439</v>
       </c>
       <c r="J118" t="n">
         <v>-155.0004483642394</v>
@@ -5657,17 +5657,17 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>-154.9895590821297</v>
+        <v>-154.9165278927681</v>
       </c>
       <c r="H119" t="n">
         <v>10</v>
       </c>
       <c r="I119" t="n">
-        <v>10.88928210970153</v>
+        <v>83.92047147134463</v>
       </c>
       <c r="J119" t="n">
         <v>-155.0004483642394</v>
@@ -5693,25 +5693,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>-154.9123634039216</v>
+        <v>-154.9895590821297</v>
       </c>
       <c r="H120" t="n">
         <v>10</v>
       </c>
       <c r="I120" t="n">
-        <v>88.08496031787172</v>
+        <v>10.88928210970153</v>
       </c>
       <c r="J120" t="n">
         <v>-155.0004483642394</v>
@@ -5745,17 +5745,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>-154.9139583139124</v>
+        <v>-154.9123634039216</v>
       </c>
       <c r="H121" t="n">
         <v>10</v>
       </c>
       <c r="I121" t="n">
-        <v>86.49005032708601</v>
+        <v>88.08496031787172</v>
       </c>
       <c r="J121" t="n">
         <v>-155.0004483642394</v>
@@ -5789,17 +5789,17 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>-153.9190263904062</v>
+        <v>-154.9139583139124</v>
       </c>
       <c r="H122" t="n">
         <v>10</v>
       </c>
       <c r="I122" t="n">
-        <v>1081.421973833244</v>
+        <v>86.49005032708601</v>
       </c>
       <c r="J122" t="n">
         <v>-155.0004483642394</v>
@@ -5833,17 +5833,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>-154.225733955447</v>
+        <v>-153.9190263904062</v>
       </c>
       <c r="H123" t="n">
         <v>10</v>
       </c>
       <c r="I123" t="n">
-        <v>774.7144087924198</v>
+        <v>1081.421973833244</v>
       </c>
       <c r="J123" t="n">
         <v>-155.0004483642394</v>
@@ -5877,17 +5877,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>-154.1709053146757</v>
+        <v>-154.225733955447</v>
       </c>
       <c r="H124" t="n">
         <v>10</v>
       </c>
       <c r="I124" t="n">
-        <v>829.5430495637675</v>
+        <v>774.7144087924198</v>
       </c>
       <c r="J124" t="n">
         <v>-155.0004483642394</v>
@@ -5921,17 +5921,17 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>-154.9911800855448</v>
+        <v>-154.1709053146757</v>
       </c>
       <c r="H125" t="n">
         <v>10</v>
       </c>
       <c r="I125" t="n">
-        <v>9.268278694605669</v>
+        <v>829.5430495637675</v>
       </c>
       <c r="J125" t="n">
         <v>-155.0004483642394</v>
@@ -5957,25 +5957,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>-154.9163737412194</v>
+        <v>-154.9911800855448</v>
       </c>
       <c r="H126" t="n">
         <v>10</v>
       </c>
       <c r="I126" t="n">
-        <v>84.07462302005797</v>
+        <v>9.268278694605669</v>
       </c>
       <c r="J126" t="n">
         <v>-155.0004483642394</v>
@@ -6009,17 +6009,17 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>-154.2544363264691</v>
+        <v>-154.9163737412194</v>
       </c>
       <c r="H127" t="n">
         <v>10</v>
       </c>
       <c r="I127" t="n">
-        <v>746.0120377702992</v>
+        <v>84.07462302005797</v>
       </c>
       <c r="J127" t="n">
         <v>-155.0004483642394</v>
@@ -6053,17 +6053,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>-154.1524634303498</v>
+        <v>-154.2544363264691</v>
       </c>
       <c r="H128" t="n">
         <v>10</v>
       </c>
       <c r="I128" t="n">
-        <v>847.9849338896202</v>
+        <v>746.0120377702992</v>
       </c>
       <c r="J128" t="n">
         <v>-155.0004483642394</v>
@@ -6097,17 +6097,17 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>-154.1179874924097</v>
+        <v>-154.1524634303498</v>
       </c>
       <c r="H129" t="n">
         <v>10</v>
       </c>
       <c r="I129" t="n">
-        <v>882.4608718297213</v>
+        <v>847.9849338896202</v>
       </c>
       <c r="J129" t="n">
         <v>-155.0004483642394</v>
@@ -6141,17 +6141,17 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>-154.0297068113391</v>
+        <v>-154.1179874924097</v>
       </c>
       <c r="H130" t="n">
         <v>10</v>
       </c>
       <c r="I130" t="n">
-        <v>970.7415529003356</v>
+        <v>882.4608718297213</v>
       </c>
       <c r="J130" t="n">
         <v>-155.0004483642394</v>
@@ -6185,17 +6185,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>-154.9930708100015</v>
+        <v>-154.0297068113391</v>
       </c>
       <c r="H131" t="n">
         <v>10</v>
       </c>
       <c r="I131" t="n">
-        <v>7.377554237962158</v>
+        <v>970.7415529003356</v>
       </c>
       <c r="J131" t="n">
         <v>-155.0004483642394</v>
@@ -6211,41 +6211,41 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>STO-3G</t>
+          <t>cc-pVDZ</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>buta-1,3-diene</t>
+          <t>but-1-yne</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>-153.1357241386908</v>
+        <v>-154.9930708100015</v>
       </c>
       <c r="H132" t="n">
         <v>10</v>
       </c>
       <c r="I132" t="n">
-        <v>169.6853031126011</v>
+        <v>7.377554237962158</v>
       </c>
       <c r="J132" t="n">
-        <v>-153.3054094418034</v>
+        <v>-155.0004483642394</v>
       </c>
       <c r="K132" t="n">
-        <v>-153.0165417465354</v>
+        <v>-154.9113882737664</v>
       </c>
       <c r="L132" t="inlineStr"/>
     </row>
@@ -6273,17 +6273,17 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>-153.0825559470882</v>
+        <v>-153.1357241386908</v>
       </c>
       <c r="H133" t="n">
         <v>10</v>
       </c>
       <c r="I133" t="n">
-        <v>222.8534947151957</v>
+        <v>169.6853031126011</v>
       </c>
       <c r="J133" t="n">
         <v>-153.3054094418034</v>
@@ -6317,17 +6317,17 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>-153.1700705200813</v>
+        <v>-153.0825559470882</v>
       </c>
       <c r="H134" t="n">
         <v>10</v>
       </c>
       <c r="I134" t="n">
-        <v>135.3389217221093</v>
+        <v>222.8534947151957</v>
       </c>
       <c r="J134" t="n">
         <v>-153.3054094418034</v>
@@ -6361,17 +6361,17 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>-153.1855539197828</v>
+        <v>-153.1700705200813</v>
       </c>
       <c r="H135" t="n">
         <v>10</v>
       </c>
       <c r="I135" t="n">
-        <v>119.8555220206572</v>
+        <v>135.3389217221093</v>
       </c>
       <c r="J135" t="n">
         <v>-153.3054094418034</v>
@@ -6405,17 +6405,17 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>-152.1912761606471</v>
+        <v>-153.1855539197828</v>
       </c>
       <c r="H136" t="n">
         <v>10</v>
       </c>
       <c r="I136" t="n">
-        <v>1114.133281156285</v>
+        <v>119.8555220206572</v>
       </c>
       <c r="J136" t="n">
         <v>-153.3054094418034</v>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>-153.2736973281175</v>
+        <v>-152.1912761606471</v>
       </c>
       <c r="H137" t="n">
         <v>10</v>
       </c>
       <c r="I137" t="n">
-        <v>31.7121136859555</v>
+        <v>1114.133281156285</v>
       </c>
       <c r="J137" t="n">
         <v>-153.3054094418034</v>
@@ -6485,25 +6485,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>-151.4779430502417</v>
+        <v>-153.2736973281175</v>
       </c>
       <c r="H138" t="n">
         <v>10</v>
       </c>
       <c r="I138" t="n">
-        <v>1827.4663915617</v>
+        <v>31.7121136859555</v>
       </c>
       <c r="J138" t="n">
         <v>-153.3054094418034</v>
@@ -6537,17 +6537,17 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>-152.1722607199707</v>
+        <v>-151.4779430502417</v>
       </c>
       <c r="H139" t="n">
         <v>10</v>
       </c>
       <c r="I139" t="n">
-        <v>1133.148721832754</v>
+        <v>1827.4663915617</v>
       </c>
       <c r="J139" t="n">
         <v>-153.3054094418034</v>
@@ -6581,17 +6581,17 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>-152.5185784052967</v>
+        <v>-152.1722607199707</v>
       </c>
       <c r="H140" t="n">
         <v>10</v>
       </c>
       <c r="I140" t="n">
-        <v>786.8310365067259</v>
+        <v>1133.148721832754</v>
       </c>
       <c r="J140" t="n">
         <v>-153.3054094418034</v>
@@ -6625,17 +6625,17 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>-153.0335802359963</v>
+        <v>-152.5185784052967</v>
       </c>
       <c r="H141" t="n">
         <v>10</v>
       </c>
       <c r="I141" t="n">
-        <v>271.8292058070801</v>
+        <v>786.8310365067259</v>
       </c>
       <c r="J141" t="n">
         <v>-153.3054094418034</v>
@@ -6669,17 +6669,17 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>-153.0434858295429</v>
+        <v>-153.0335802359963</v>
       </c>
       <c r="H142" t="n">
         <v>10</v>
       </c>
       <c r="I142" t="n">
-        <v>261.9236122604889</v>
+        <v>271.8292058070801</v>
       </c>
       <c r="J142" t="n">
         <v>-153.3054094418034</v>
@@ -6713,17 +6713,17 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>-153.2729045549831</v>
+        <v>-153.0434858295429</v>
       </c>
       <c r="H143" t="n">
         <v>10</v>
       </c>
       <c r="I143" t="n">
-        <v>32.50488682027708</v>
+        <v>261.9236122604889</v>
       </c>
       <c r="J143" t="n">
         <v>-153.3054094418034</v>
@@ -6749,25 +6749,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>-152.2466387535251</v>
+        <v>-153.2729045549831</v>
       </c>
       <c r="H144" t="n">
         <v>10</v>
       </c>
       <c r="I144" t="n">
-        <v>1058.770688278287</v>
+        <v>32.50488682027708</v>
       </c>
       <c r="J144" t="n">
         <v>-153.3054094418034</v>
@@ -6801,17 +6801,17 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>-150.9927345104938</v>
+        <v>-152.2466387535251</v>
       </c>
       <c r="H145" t="n">
         <v>10</v>
       </c>
       <c r="I145" t="n">
-        <v>2312.67493130963</v>
+        <v>1058.770688278287</v>
       </c>
       <c r="J145" t="n">
         <v>-153.3054094418034</v>
@@ -6845,17 +6845,17 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>-152.301396128385</v>
+        <v>-150.9927345104938</v>
       </c>
       <c r="H146" t="n">
         <v>10</v>
       </c>
       <c r="I146" t="n">
-        <v>1004.013313418398</v>
+        <v>2312.67493130963</v>
       </c>
       <c r="J146" t="n">
         <v>-153.3054094418034</v>
@@ -6889,17 +6889,17 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>-152.2521532075726</v>
+        <v>-152.301396128385</v>
       </c>
       <c r="H147" t="n">
         <v>10</v>
       </c>
       <c r="I147" t="n">
-        <v>1053.256234230844</v>
+        <v>1004.013313418398</v>
       </c>
       <c r="J147" t="n">
         <v>-153.3054094418034</v>
@@ -6933,17 +6933,17 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>-152.5599510049397</v>
+        <v>-152.2521532075726</v>
       </c>
       <c r="H148" t="n">
         <v>10</v>
       </c>
       <c r="I148" t="n">
-        <v>745.4584368637143</v>
+        <v>1053.256234230844</v>
       </c>
       <c r="J148" t="n">
         <v>-153.3054094418034</v>
@@ -6977,17 +6977,17 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>-153.2723894363922</v>
+        <v>-152.5599510049397</v>
       </c>
       <c r="H149" t="n">
         <v>10</v>
       </c>
       <c r="I149" t="n">
-        <v>33.02000541117422</v>
+        <v>745.4584368637143</v>
       </c>
       <c r="J149" t="n">
         <v>-153.3054094418034</v>
@@ -7013,25 +7013,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>-152.2603539718137</v>
+        <v>-153.2723894363922</v>
       </c>
       <c r="H150" t="n">
         <v>10</v>
       </c>
       <c r="I150" t="n">
-        <v>1045.055469989734</v>
+        <v>33.02000541117422</v>
       </c>
       <c r="J150" t="n">
         <v>-153.3054094418034</v>
@@ -7065,17 +7065,17 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>-152.2549373588304</v>
+        <v>-152.2603539718137</v>
       </c>
       <c r="H151" t="n">
         <v>10</v>
       </c>
       <c r="I151" t="n">
-        <v>1050.472082973045</v>
+        <v>1045.055469989734</v>
       </c>
       <c r="J151" t="n">
         <v>-153.3054094418034</v>
@@ -7109,17 +7109,17 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G152" t="n">
-        <v>-153.0445493061444</v>
+        <v>-152.2549373588304</v>
       </c>
       <c r="H152" t="n">
         <v>10</v>
       </c>
       <c r="I152" t="n">
-        <v>260.8601356590157</v>
+        <v>1050.472082973045</v>
       </c>
       <c r="J152" t="n">
         <v>-153.3054094418034</v>
@@ -7153,17 +7153,17 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G153" t="n">
-        <v>-153.0185693032415</v>
+        <v>-153.0445493061444</v>
       </c>
       <c r="H153" t="n">
         <v>10</v>
       </c>
       <c r="I153" t="n">
-        <v>286.8401385618995</v>
+        <v>260.8601356590157</v>
       </c>
       <c r="J153" t="n">
         <v>-153.3054094418034</v>
@@ -7197,17 +7197,17 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>-153.0307479602722</v>
+        <v>-153.0185693032415</v>
       </c>
       <c r="H154" t="n">
         <v>10</v>
       </c>
       <c r="I154" t="n">
-        <v>274.6614815312682</v>
+        <v>286.8401385618995</v>
       </c>
       <c r="J154" t="n">
         <v>-153.3054094418034</v>
@@ -7241,17 +7241,17 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>-153.2720371935036</v>
+        <v>-153.0307479602722</v>
       </c>
       <c r="H155" t="n">
         <v>10</v>
       </c>
       <c r="I155" t="n">
-        <v>33.37224829982688</v>
+        <v>274.6614815312682</v>
       </c>
       <c r="J155" t="n">
         <v>-153.3054094418034</v>
@@ -7277,25 +7277,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G156" t="n">
-        <v>-152.5203527261951</v>
+        <v>-153.2720371935036</v>
       </c>
       <c r="H156" t="n">
         <v>10</v>
       </c>
       <c r="I156" t="n">
-        <v>785.0567156083343</v>
+        <v>33.37224829982688</v>
       </c>
       <c r="J156" t="n">
         <v>-153.3054094418034</v>
@@ -7329,17 +7329,17 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G157" t="n">
-        <v>-152.5578242154852</v>
+        <v>-152.5203527261951</v>
       </c>
       <c r="H157" t="n">
         <v>10</v>
       </c>
       <c r="I157" t="n">
-        <v>747.5852263182219</v>
+        <v>785.0567156083343</v>
       </c>
       <c r="J157" t="n">
         <v>-153.3054094418034</v>
@@ -7373,17 +7373,17 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>-153.0179266922524</v>
+        <v>-152.5578242154852</v>
       </c>
       <c r="H158" t="n">
         <v>10</v>
       </c>
       <c r="I158" t="n">
-        <v>287.4827495509749</v>
+        <v>747.5852263182219</v>
       </c>
       <c r="J158" t="n">
         <v>-153.3054094418034</v>
@@ -7417,17 +7417,17 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G159" t="n">
-        <v>-153.02621965425</v>
+        <v>-153.0179266922524</v>
       </c>
       <c r="H159" t="n">
         <v>10</v>
       </c>
       <c r="I159" t="n">
-        <v>279.1897875533778</v>
+        <v>287.4827495509749</v>
       </c>
       <c r="J159" t="n">
         <v>-153.3054094418034</v>
@@ -7461,17 +7461,17 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>-152.162777322356</v>
+        <v>-153.02621965425</v>
       </c>
       <c r="H160" t="n">
         <v>10</v>
       </c>
       <c r="I160" t="n">
-        <v>1142.632119447455</v>
+        <v>279.1897875533778</v>
       </c>
       <c r="J160" t="n">
         <v>-153.3054094418034</v>
@@ -7505,17 +7505,17 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>-153.2633835948676</v>
+        <v>-152.162777322356</v>
       </c>
       <c r="H161" t="n">
         <v>10</v>
       </c>
       <c r="I161" t="n">
-        <v>42.02584693581457</v>
+        <v>1142.632119447455</v>
       </c>
       <c r="J161" t="n">
         <v>-153.3054094418034</v>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>aug-cc-pVDZ</t>
+          <t>STO-3G</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -7541,31 +7541,31 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G162" t="n">
-        <v>-154.9488075532024</v>
+        <v>-153.2633835948676</v>
       </c>
       <c r="H162" t="n">
         <v>10</v>
       </c>
       <c r="I162" t="n">
-        <v>1.820885757524593</v>
+        <v>42.02584693581457</v>
       </c>
       <c r="J162" t="n">
-        <v>-154.9506284389599</v>
+        <v>-153.3054094418034</v>
       </c>
       <c r="K162" t="n">
-        <v>-154.9399130373333</v>
+        <v>-153.0165417465354</v>
       </c>
       <c r="L162" t="inlineStr"/>
     </row>
@@ -7593,17 +7593,17 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>-154.9438242507404</v>
+        <v>-154.9488075532024</v>
       </c>
       <c r="H163" t="n">
         <v>10</v>
       </c>
       <c r="I163" t="n">
-        <v>6.804188219518892</v>
+        <v>1.820885757524593</v>
       </c>
       <c r="J163" t="n">
         <v>-154.9506284389599</v>
@@ -7637,17 +7637,17 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>-154.4689745381633</v>
+        <v>-154.9438242507404</v>
       </c>
       <c r="H164" t="n">
         <v>10</v>
       </c>
       <c r="I164" t="n">
-        <v>481.653900796573</v>
+        <v>6.804188219518892</v>
       </c>
       <c r="J164" t="n">
         <v>-154.9506284389599</v>
@@ -7673,25 +7673,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G165" t="n">
-        <v>-153.2907289076241</v>
+        <v>-154.4689745381633</v>
       </c>
       <c r="H165" t="n">
         <v>10</v>
       </c>
       <c r="I165" t="n">
-        <v>1659.899531335782</v>
+        <v>481.653900796573</v>
       </c>
       <c r="J165" t="n">
         <v>-154.9506284389599</v>
@@ -7725,17 +7725,17 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G166" t="n">
-        <v>-154.5043398844805</v>
+        <v>-153.2907289076241</v>
       </c>
       <c r="H166" t="n">
         <v>10</v>
       </c>
       <c r="I166" t="n">
-        <v>446.2885544793949</v>
+        <v>1659.899531335782</v>
       </c>
       <c r="J166" t="n">
         <v>-154.9506284389599</v>
@@ -7769,17 +7769,17 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>-154.4686442903764</v>
+        <v>-154.5043398844805</v>
       </c>
       <c r="H167" t="n">
         <v>10</v>
       </c>
       <c r="I167" t="n">
-        <v>481.9841485834786</v>
+        <v>446.2885544793949</v>
       </c>
       <c r="J167" t="n">
         <v>-154.9506284389599</v>
@@ -7813,17 +7813,17 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G168" t="n">
-        <v>-154.9399609062344</v>
+        <v>-154.4686442903764</v>
       </c>
       <c r="H168" t="n">
         <v>10</v>
       </c>
       <c r="I168" t="n">
-        <v>10.66753272544929</v>
+        <v>481.9841485834786</v>
       </c>
       <c r="J168" t="n">
         <v>-154.9506284389599</v>
@@ -7857,17 +7857,17 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G169" t="n">
-        <v>-154.9475255907902</v>
+        <v>-154.9399609062344</v>
       </c>
       <c r="H169" t="n">
         <v>10</v>
       </c>
       <c r="I169" t="n">
-        <v>3.102848169646677</v>
+        <v>10.66753272544929</v>
       </c>
       <c r="J169" t="n">
         <v>-154.9506284389599</v>
@@ -7893,25 +7893,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G170" t="n">
-        <v>-154.1604878868675</v>
+        <v>-154.9475255907902</v>
       </c>
       <c r="H170" t="n">
         <v>10</v>
       </c>
       <c r="I170" t="n">
-        <v>790.140552092339</v>
+        <v>3.102848169646677</v>
       </c>
       <c r="J170" t="n">
         <v>-154.9506284389599</v>
@@ -7945,17 +7945,17 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>-153.153376547367</v>
+        <v>-154.1604878868675</v>
       </c>
       <c r="H171" t="n">
         <v>10</v>
       </c>
       <c r="I171" t="n">
-        <v>1797.251891592907</v>
+        <v>790.140552092339</v>
       </c>
       <c r="J171" t="n">
         <v>-154.9506284389599</v>
@@ -7989,17 +7989,17 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>-154.5230638947714</v>
+        <v>-153.153376547367</v>
       </c>
       <c r="H172" t="n">
         <v>10</v>
       </c>
       <c r="I172" t="n">
-        <v>427.564544188499</v>
+        <v>1797.251891592907</v>
       </c>
       <c r="J172" t="n">
         <v>-154.9506284389599</v>
@@ -8033,17 +8033,17 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>-154.305877222469</v>
+        <v>-154.5230638947714</v>
       </c>
       <c r="H173" t="n">
         <v>10</v>
       </c>
       <c r="I173" t="n">
-        <v>644.7512164909313</v>
+        <v>427.564544188499</v>
       </c>
       <c r="J173" t="n">
         <v>-154.9506284389599</v>
@@ -8077,17 +8077,17 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>-154.4690160198077</v>
+        <v>-154.305877222469</v>
       </c>
       <c r="H174" t="n">
         <v>10</v>
       </c>
       <c r="I174" t="n">
-        <v>481.6124191521567</v>
+        <v>644.7512164909313</v>
       </c>
       <c r="J174" t="n">
         <v>-154.9506284389599</v>
@@ -8113,25 +8113,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>-154.1685204078196</v>
+        <v>-154.4690160198077</v>
       </c>
       <c r="H175" t="n">
         <v>10</v>
       </c>
       <c r="I175" t="n">
-        <v>782.1080311402966</v>
+        <v>481.6124191521567</v>
       </c>
       <c r="J175" t="n">
         <v>-154.9506284389599</v>
@@ -8165,17 +8165,17 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>-153.6477628265835</v>
+        <v>-154.1685204078196</v>
       </c>
       <c r="H176" t="n">
         <v>10</v>
       </c>
       <c r="I176" t="n">
-        <v>1302.865612376422</v>
+        <v>782.1080311402966</v>
       </c>
       <c r="J176" t="n">
         <v>-154.9506284389599</v>
@@ -8209,17 +8209,17 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G177" t="n">
-        <v>-154.9401073107348</v>
+        <v>-153.6477628265835</v>
       </c>
       <c r="H177" t="n">
         <v>10</v>
       </c>
       <c r="I177" t="n">
-        <v>10.52112822509343</v>
+        <v>1302.865612376422</v>
       </c>
       <c r="J177" t="n">
         <v>-154.9506284389599</v>
@@ -8253,17 +8253,17 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G178" t="n">
-        <v>-154.4311851621608</v>
+        <v>-154.9401073107348</v>
       </c>
       <c r="H178" t="n">
         <v>10</v>
       </c>
       <c r="I178" t="n">
-        <v>519.443276799052</v>
+        <v>10.52112822509343</v>
       </c>
       <c r="J178" t="n">
         <v>-154.9506284389599</v>
@@ -8297,17 +8297,17 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>-154.4804480292407</v>
+        <v>-154.4311851621608</v>
       </c>
       <c r="H179" t="n">
         <v>10</v>
       </c>
       <c r="I179" t="n">
-        <v>470.1804097191484</v>
+        <v>519.443276799052</v>
       </c>
       <c r="J179" t="n">
         <v>-154.9506284389599</v>
@@ -8333,25 +8333,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G180" t="n">
-        <v>-154.433529233188</v>
+        <v>-154.4804480292407</v>
       </c>
       <c r="H180" t="n">
         <v>10</v>
       </c>
       <c r="I180" t="n">
-        <v>517.0992057718422</v>
+        <v>470.1804097191484</v>
       </c>
       <c r="J180" t="n">
         <v>-154.9506284389599</v>
@@ -8385,17 +8385,17 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>-154.4284944202545</v>
+        <v>-154.433529233188</v>
       </c>
       <c r="H181" t="n">
         <v>10</v>
       </c>
       <c r="I181" t="n">
-        <v>522.1340187053443</v>
+        <v>517.0992057718422</v>
       </c>
       <c r="J181" t="n">
         <v>-154.9506284389599</v>
@@ -8429,17 +8429,17 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>-154.4685976123411</v>
+        <v>-154.4284944202545</v>
       </c>
       <c r="H182" t="n">
         <v>10</v>
       </c>
       <c r="I182" t="n">
-        <v>482.0308266187681</v>
+        <v>522.1340187053443</v>
       </c>
       <c r="J182" t="n">
         <v>-154.9506284389599</v>
@@ -8473,17 +8473,17 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>-154.9465329751051</v>
+        <v>-154.4685976123411</v>
       </c>
       <c r="H183" t="n">
         <v>10</v>
       </c>
       <c r="I183" t="n">
-        <v>4.095463854753234</v>
+        <v>482.0308266187681</v>
       </c>
       <c r="J183" t="n">
         <v>-154.9506284389599</v>
@@ -8517,17 +8517,17 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>-164.5766676544592</v>
+        <v>-154.9465329751051</v>
       </c>
       <c r="H184" t="n">
         <v>10</v>
       </c>
       <c r="I184" t="n">
-        <v>-9626.039215499304</v>
+        <v>4.095463854753234</v>
       </c>
       <c r="J184" t="n">
         <v>-154.9506284389599</v>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>cc-pVDZ</t>
+          <t>aug-cc-pVDZ</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -8553,31 +8553,31 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>-154.9828572449146</v>
+        <v>-164.5766676544592</v>
       </c>
       <c r="H185" t="n">
         <v>10</v>
       </c>
       <c r="I185" t="n">
-        <v>32.59370623322866</v>
+        <v>-9626.039215499304</v>
       </c>
       <c r="J185" t="n">
-        <v>-155.0154509511478</v>
+        <v>-154.9506284389599</v>
       </c>
       <c r="K185" t="n">
-        <v>-154.933920403517</v>
+        <v>-154.9399130373333</v>
       </c>
       <c r="L185" t="inlineStr"/>
     </row>
@@ -8605,17 +8605,17 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G186" t="n">
-        <v>-154.9728386518885</v>
+        <v>-154.9828572449146</v>
       </c>
       <c r="H186" t="n">
         <v>10</v>
       </c>
       <c r="I186" t="n">
-        <v>42.61229925924681</v>
+        <v>32.59370623322866</v>
       </c>
       <c r="J186" t="n">
         <v>-155.0154509511478</v>
@@ -8649,17 +8649,17 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>-154.96930026494</v>
+        <v>-154.9728386518885</v>
       </c>
       <c r="H187" t="n">
         <v>10</v>
       </c>
       <c r="I187" t="n">
-        <v>46.15068620773854</v>
+        <v>42.61229925924681</v>
       </c>
       <c r="J187" t="n">
         <v>-155.0154509511478</v>
@@ -8693,17 +8693,17 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>-154.9943678069919</v>
+        <v>-154.96930026494</v>
       </c>
       <c r="H188" t="n">
         <v>10</v>
       </c>
       <c r="I188" t="n">
-        <v>21.08314415590939</v>
+        <v>46.15068620773854</v>
       </c>
       <c r="J188" t="n">
         <v>-155.0154509511478</v>
@@ -8737,17 +8737,17 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G189" t="n">
-        <v>-154.0099647675274</v>
+        <v>-154.9943678069919</v>
       </c>
       <c r="H189" t="n">
         <v>10</v>
       </c>
       <c r="I189" t="n">
-        <v>1005.486183620405</v>
+        <v>21.08314415590939</v>
       </c>
       <c r="J189" t="n">
         <v>-155.0154509511478</v>
@@ -8781,17 +8781,17 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>-155.0072537721249</v>
+        <v>-154.0099647675274</v>
       </c>
       <c r="H190" t="n">
         <v>10</v>
       </c>
       <c r="I190" t="n">
-        <v>8.197179022886303</v>
+        <v>1005.486183620405</v>
       </c>
       <c r="J190" t="n">
         <v>-155.0154509511478</v>
@@ -8817,25 +8817,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G191" t="n">
-        <v>-154.5216029992076</v>
+        <v>-155.0072537721249</v>
       </c>
       <c r="H191" t="n">
         <v>10</v>
       </c>
       <c r="I191" t="n">
-        <v>493.8479519402108</v>
+        <v>8.197179022886303</v>
       </c>
       <c r="J191" t="n">
         <v>-155.0154509511478</v>
@@ -8869,17 +8869,17 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G192" t="n">
-        <v>-154.955759414188</v>
+        <v>-154.5216029992076</v>
       </c>
       <c r="H192" t="n">
         <v>10</v>
       </c>
       <c r="I192" t="n">
-        <v>59.69153695974683</v>
+        <v>493.8479519402108</v>
       </c>
       <c r="J192" t="n">
         <v>-155.0154509511478</v>
@@ -8913,17 +8913,17 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G193" t="n">
-        <v>-154.2495660081191</v>
+        <v>-154.955759414188</v>
       </c>
       <c r="H193" t="n">
         <v>10</v>
       </c>
       <c r="I193" t="n">
-        <v>765.8849430287091</v>
+        <v>59.69153695974683</v>
       </c>
       <c r="J193" t="n">
         <v>-155.0154509511478</v>
@@ -8957,17 +8957,17 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G194" t="n">
-        <v>-154.9423798434264</v>
+        <v>-154.2495660081191</v>
       </c>
       <c r="H194" t="n">
         <v>10</v>
       </c>
       <c r="I194" t="n">
-        <v>73.07110772143233</v>
+        <v>765.8849430287091</v>
       </c>
       <c r="J194" t="n">
         <v>-155.0154509511478</v>
@@ -9001,17 +9001,17 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G195" t="n">
-        <v>-154.1234010517957</v>
+        <v>-154.9423798434264</v>
       </c>
       <c r="H195" t="n">
         <v>10</v>
       </c>
       <c r="I195" t="n">
-        <v>892.0498993521164</v>
+        <v>73.07110772143233</v>
       </c>
       <c r="J195" t="n">
         <v>-155.0154509511478</v>
@@ -9045,17 +9045,17 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G196" t="n">
-        <v>-155.0072179491773</v>
+        <v>-154.1234010517957</v>
       </c>
       <c r="H196" t="n">
         <v>10</v>
       </c>
       <c r="I196" t="n">
-        <v>8.233001970438636</v>
+        <v>892.0498993521164</v>
       </c>
       <c r="J196" t="n">
         <v>-155.0154509511478</v>
@@ -9081,25 +9081,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G197" t="n">
-        <v>-153.8618972276274</v>
+        <v>-155.0072179491773</v>
       </c>
       <c r="H197" t="n">
         <v>10</v>
       </c>
       <c r="I197" t="n">
-        <v>1153.553723520361</v>
+        <v>8.233001970438636</v>
       </c>
       <c r="J197" t="n">
         <v>-155.0154509511478</v>
@@ -9133,17 +9133,17 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G198" t="n">
-        <v>-154.9410086202933</v>
+        <v>-153.8618972276274</v>
       </c>
       <c r="H198" t="n">
         <v>10</v>
       </c>
       <c r="I198" t="n">
-        <v>74.44233085448104</v>
+        <v>1153.553723520361</v>
       </c>
       <c r="J198" t="n">
         <v>-155.0154509511478</v>
@@ -9177,17 +9177,17 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G199" t="n">
-        <v>-154.2140950329367</v>
+        <v>-154.9410086202933</v>
       </c>
       <c r="H199" t="n">
         <v>10</v>
       </c>
       <c r="I199" t="n">
-        <v>801.3559182111294</v>
+        <v>74.44233085448104</v>
       </c>
       <c r="J199" t="n">
         <v>-155.0154509511478</v>
@@ -9221,17 +9221,17 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G200" t="n">
-        <v>-154.2023495894866</v>
+        <v>-154.2140950329367</v>
       </c>
       <c r="H200" t="n">
         <v>10</v>
       </c>
       <c r="I200" t="n">
-        <v>813.1013616612108</v>
+        <v>801.3559182111294</v>
       </c>
       <c r="J200" t="n">
         <v>-155.0154509511478</v>
@@ -9265,17 +9265,17 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G201" t="n">
-        <v>-154.2660968446507</v>
+        <v>-154.2023495894866</v>
       </c>
       <c r="H201" t="n">
         <v>10</v>
       </c>
       <c r="I201" t="n">
-        <v>749.3541064970941</v>
+        <v>813.1013616612108</v>
       </c>
       <c r="J201" t="n">
         <v>-155.0154509511478</v>
@@ -9309,17 +9309,17 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G202" t="n">
-        <v>-155.0063190205414</v>
+        <v>-154.2660968446507</v>
       </c>
       <c r="H202" t="n">
         <v>10</v>
       </c>
       <c r="I202" t="n">
-        <v>9.131930606372407</v>
+        <v>749.3541064970941</v>
       </c>
       <c r="J202" t="n">
         <v>-155.0154509511478</v>
@@ -9345,25 +9345,25 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G203" t="n">
-        <v>-154.0376337493756</v>
+        <v>-155.0063190205414</v>
       </c>
       <c r="H203" t="n">
         <v>10</v>
       </c>
       <c r="I203" t="n">
-        <v>977.8172017721545</v>
+        <v>9.131930606372407</v>
       </c>
       <c r="J203" t="n">
         <v>-155.0154509511478</v>
@@ -9397,17 +9397,17 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G204" t="n">
-        <v>-154.9572276804694</v>
+        <v>-154.0376337493756</v>
       </c>
       <c r="H204" t="n">
         <v>10</v>
       </c>
       <c r="I204" t="n">
-        <v>58.22327067841115</v>
+        <v>977.8172017721545</v>
       </c>
       <c r="J204" t="n">
         <v>-155.0154509511478</v>
@@ -9441,17 +9441,17 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G205" t="n">
-        <v>-154.0686668026786</v>
+        <v>-154.9572276804694</v>
       </c>
       <c r="H205" t="n">
         <v>10</v>
       </c>
       <c r="I205" t="n">
-        <v>946.7841484691917</v>
+        <v>58.22327067841115</v>
       </c>
       <c r="J205" t="n">
         <v>-155.0154509511478</v>
@@ -9485,17 +9485,17 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G206" t="n">
-        <v>-154.5199058494725</v>
+        <v>-154.0686668026786</v>
       </c>
       <c r="H206" t="n">
         <v>10</v>
       </c>
       <c r="I206" t="n">
-        <v>495.5451016752477</v>
+        <v>946.7841484691917</v>
       </c>
       <c r="J206" t="n">
         <v>-155.0154509511478</v>
@@ -9529,17 +9529,17 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G207" t="n">
-        <v>-154.5185769124535</v>
+        <v>-154.5199058494725</v>
       </c>
       <c r="H207" t="n">
         <v>10</v>
       </c>
       <c r="I207" t="n">
-        <v>496.8740386942727</v>
+        <v>495.5451016752477</v>
       </c>
       <c r="J207" t="n">
         <v>-155.0154509511478</v>
@@ -9573,17 +9573,17 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G208" t="n">
-        <v>-155.0077217756853</v>
+        <v>-154.5185769124535</v>
       </c>
       <c r="H208" t="n">
         <v>10</v>
       </c>
       <c r="I208" t="n">
-        <v>7.729175462486637</v>
+        <v>496.8740386942727</v>
       </c>
       <c r="J208" t="n">
         <v>-155.0154509511478</v>
@@ -9609,25 +9609,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G209" t="n">
-        <v>-154.1615220618183</v>
+        <v>-155.0077217756853</v>
       </c>
       <c r="H209" t="n">
         <v>10</v>
       </c>
       <c r="I209" t="n">
-        <v>853.9288893294383</v>
+        <v>7.729175462486637</v>
       </c>
       <c r="J209" t="n">
         <v>-155.0154509511478</v>
@@ -9661,17 +9661,17 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G210" t="n">
-        <v>-154.0535367301257</v>
+        <v>-154.1615220618183</v>
       </c>
       <c r="H210" t="n">
         <v>10</v>
       </c>
       <c r="I210" t="n">
-        <v>961.9142210220843</v>
+        <v>853.9288893294383</v>
       </c>
       <c r="J210" t="n">
         <v>-155.0154509511478</v>
@@ -9705,17 +9705,17 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G211" t="n">
-        <v>-153.7385544493961</v>
+        <v>-154.0535367301257</v>
       </c>
       <c r="H211" t="n">
         <v>10</v>
       </c>
       <c r="I211" t="n">
-        <v>1276.896501751708</v>
+        <v>961.9142210220843</v>
       </c>
       <c r="J211" t="n">
         <v>-155.0154509511478</v>
@@ -9749,17 +9749,17 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G212" t="n">
-        <v>-153.7263205808158</v>
+        <v>-153.7385544493961</v>
       </c>
       <c r="H212" t="n">
         <v>10</v>
       </c>
       <c r="I212" t="n">
-        <v>1289.130370331975</v>
+        <v>1276.896501751708</v>
       </c>
       <c r="J212" t="n">
         <v>-155.0154509511478</v>
@@ -9793,17 +9793,17 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G213" t="n">
-        <v>-154.5494403032813</v>
+        <v>-153.7263205808158</v>
       </c>
       <c r="H213" t="n">
         <v>10</v>
       </c>
       <c r="I213" t="n">
-        <v>466.0106478664829</v>
+        <v>1289.130370331975</v>
       </c>
       <c r="J213" t="n">
         <v>-155.0154509511478</v>
@@ -9837,17 +9837,17 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G214" t="n">
-        <v>-155.0072144416225</v>
+        <v>-154.5494403032813</v>
       </c>
       <c r="H214" t="n">
         <v>10</v>
       </c>
       <c r="I214" t="n">
-        <v>8.23650952531807</v>
+        <v>466.0106478664829</v>
       </c>
       <c r="J214" t="n">
         <v>-155.0154509511478</v>
@@ -9863,45 +9863,43 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>STO-3G</t>
+          <t>cc-pVDZ</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>ethane</t>
+          <t>buta-1,3-diene</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G215" t="n">
-        <v>-78.45196026902894</v>
+        <v>-155.0072144416225</v>
       </c>
       <c r="H215" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I215" t="n">
-        <v>-3.005041094212402</v>
+        <v>8.23650952531807</v>
       </c>
       <c r="J215" t="n">
-        <v>-78.44895522793473</v>
+        <v>-155.0154509511478</v>
       </c>
       <c r="K215" t="n">
-        <v>-78.30581623656136</v>
-      </c>
-      <c r="L215" t="n">
-        <v>-78.45323232971093</v>
-      </c>
+        <v>-154.933920403517</v>
+      </c>
+      <c r="L215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
@@ -9927,17 +9925,17 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>-78.45228458153218</v>
+        <v>-78.45196026902894</v>
       </c>
       <c r="H216" t="n">
         <v>8</v>
       </c>
       <c r="I216" t="n">
-        <v>-3.32935359745079</v>
+        <v>-3.005041094212402</v>
       </c>
       <c r="J216" t="n">
         <v>-78.44895522793473</v>
@@ -9973,17 +9971,17 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G217" t="n">
-        <v>-78.45244225817562</v>
+        <v>-78.45228458153218</v>
       </c>
       <c r="H217" t="n">
         <v>8</v>
       </c>
       <c r="I217" t="n">
-        <v>-3.487030240890476</v>
+        <v>-3.32935359745079</v>
       </c>
       <c r="J217" t="n">
         <v>-78.44895522793473</v>
@@ -10019,17 +10017,17 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G218" t="n">
-        <v>-78.4519487833831</v>
+        <v>-78.45244225817562</v>
       </c>
       <c r="H218" t="n">
         <v>8</v>
       </c>
       <c r="I218" t="n">
-        <v>-2.993555448369989</v>
+        <v>-3.487030240890476</v>
       </c>
       <c r="J218" t="n">
         <v>-78.44895522793473</v>
@@ -10065,17 +10063,17 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G219" t="n">
-        <v>-78.45103206369764</v>
+        <v>-78.4519487833831</v>
       </c>
       <c r="H219" t="n">
         <v>8</v>
       </c>
       <c r="I219" t="n">
-        <v>-2.076835762906626</v>
+        <v>-2.993555448369989</v>
       </c>
       <c r="J219" t="n">
         <v>-78.44895522793473</v>
@@ -10111,17 +10109,17 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G220" t="n">
-        <v>-78.45084519677899</v>
+        <v>-78.45103206369764</v>
       </c>
       <c r="H220" t="n">
         <v>8</v>
       </c>
       <c r="I220" t="n">
-        <v>-1.889968844253076</v>
+        <v>-2.076835762906626</v>
       </c>
       <c r="J220" t="n">
         <v>-78.44895522793473</v>
@@ -10149,25 +10147,25 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G221" t="n">
-        <v>-78.451003025067</v>
+        <v>-78.45084519677899</v>
       </c>
       <c r="H221" t="n">
         <v>8</v>
       </c>
       <c r="I221" t="n">
-        <v>-2.04779713226344</v>
+        <v>-1.889968844253076</v>
       </c>
       <c r="J221" t="n">
         <v>-78.44895522793473</v>
@@ -10203,17 +10201,17 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G222" t="n">
-        <v>-78.45180484524627</v>
+        <v>-78.451003025067</v>
       </c>
       <c r="H222" t="n">
         <v>8</v>
       </c>
       <c r="I222" t="n">
-        <v>-2.849617311539987</v>
+        <v>-2.04779713226344</v>
       </c>
       <c r="J222" t="n">
         <v>-78.44895522793473</v>
@@ -10249,17 +10247,17 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G223" t="n">
-        <v>-78.45230285960164</v>
+        <v>-78.45180484524627</v>
       </c>
       <c r="H223" t="n">
         <v>8</v>
       </c>
       <c r="I223" t="n">
-        <v>-3.347631666912321</v>
+        <v>-2.849617311539987</v>
       </c>
       <c r="J223" t="n">
         <v>-78.44895522793473</v>
@@ -10295,17 +10293,17 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G224" t="n">
-        <v>-78.45125327478137</v>
+        <v>-78.45230285960164</v>
       </c>
       <c r="H224" t="n">
         <v>8</v>
       </c>
       <c r="I224" t="n">
-        <v>-2.298046846632928</v>
+        <v>-3.347631666912321</v>
       </c>
       <c r="J224" t="n">
         <v>-78.44895522793473</v>
@@ -10341,17 +10339,17 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G225" t="n">
-        <v>-78.45098619000125</v>
+        <v>-78.45125327478137</v>
       </c>
       <c r="H225" t="n">
         <v>8</v>
       </c>
       <c r="I225" t="n">
-        <v>-2.030962066513098</v>
+        <v>-2.298046846632928</v>
       </c>
       <c r="J225" t="n">
         <v>-78.44895522793473</v>
@@ -10387,17 +10385,17 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G226" t="n">
-        <v>-78.45129476263865</v>
+        <v>-78.45098619000125</v>
       </c>
       <c r="H226" t="n">
         <v>8</v>
       </c>
       <c r="I226" t="n">
-        <v>-2.339534703921231</v>
+        <v>-2.030962066513098</v>
       </c>
       <c r="J226" t="n">
         <v>-78.44895522793473</v>
@@ -10425,25 +10423,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G227" t="n">
-        <v>-78.45092299128842</v>
+        <v>-78.45129476263865</v>
       </c>
       <c r="H227" t="n">
         <v>8</v>
       </c>
       <c r="I227" t="n">
-        <v>-1.967763353690088</v>
+        <v>-2.339534703921231</v>
       </c>
       <c r="J227" t="n">
         <v>-78.44895522793473</v>
@@ -10479,17 +10477,17 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G228" t="n">
-        <v>-78.45119224568596</v>
+        <v>-78.45092299128842</v>
       </c>
       <c r="H228" t="n">
         <v>8</v>
       </c>
       <c r="I228" t="n">
-        <v>-2.237017751227199</v>
+        <v>-1.967763353690088</v>
       </c>
       <c r="J228" t="n">
         <v>-78.44895522793473</v>
@@ -10525,17 +10523,17 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G229" t="n">
-        <v>-78.4508099090957</v>
+        <v>-78.45119224568596</v>
       </c>
       <c r="H229" t="n">
         <v>8</v>
       </c>
       <c r="I229" t="n">
-        <v>-1.854681160963878</v>
+        <v>-2.237017751227199</v>
       </c>
       <c r="J229" t="n">
         <v>-78.44895522793473</v>
@@ -10571,17 +10569,17 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G230" t="n">
-        <v>-78.4517986241586</v>
+        <v>-78.4508099090957</v>
       </c>
       <c r="H230" t="n">
         <v>8</v>
       </c>
       <c r="I230" t="n">
-        <v>-2.843396223866534</v>
+        <v>-1.854681160963878</v>
       </c>
       <c r="J230" t="n">
         <v>-78.44895522793473</v>
@@ -10609,25 +10607,25 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G231" t="n">
-        <v>-78.45105137304746</v>
+        <v>-78.4517986241586</v>
       </c>
       <c r="H231" t="n">
         <v>8</v>
       </c>
       <c r="I231" t="n">
-        <v>-2.096145112730596</v>
+        <v>-2.843396223866534</v>
       </c>
       <c r="J231" t="n">
         <v>-78.44895522793473</v>
@@ -10663,17 +10661,17 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G232" t="n">
-        <v>-78.45097882394616</v>
+        <v>-78.45105137304746</v>
       </c>
       <c r="H232" t="n">
         <v>8</v>
       </c>
       <c r="I232" t="n">
-        <v>-2.023596011426321</v>
+        <v>-2.096145112730596</v>
       </c>
       <c r="J232" t="n">
         <v>-78.44895522793473</v>
@@ -10709,17 +10707,17 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G233" t="n">
-        <v>-78.45105229101422</v>
+        <v>-78.45097882394616</v>
       </c>
       <c r="H233" t="n">
         <v>8</v>
       </c>
       <c r="I233" t="n">
-        <v>-2.097063079489203</v>
+        <v>-2.023596011426321</v>
       </c>
       <c r="J233" t="n">
         <v>-78.44895522793473</v>
@@ -10755,17 +10753,17 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G234" t="n">
-        <v>-78.45068550173808</v>
+        <v>-78.45105229101422</v>
       </c>
       <c r="H234" t="n">
         <v>8</v>
       </c>
       <c r="I234" t="n">
-        <v>-1.730273803346449</v>
+        <v>-2.097063079489203</v>
       </c>
       <c r="J234" t="n">
         <v>-78.44895522793473</v>
@@ -10793,25 +10791,25 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G235" t="n">
-        <v>-78.45134280809079</v>
+        <v>-78.45068550173808</v>
       </c>
       <c r="H235" t="n">
         <v>8</v>
       </c>
       <c r="I235" t="n">
-        <v>-2.387580156053559</v>
+        <v>-1.730273803346449</v>
       </c>
       <c r="J235" t="n">
         <v>-78.44895522793473</v>
@@ -10847,17 +10845,17 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G236" t="n">
-        <v>-78.45117878732135</v>
+        <v>-78.45134280809079</v>
       </c>
       <c r="H236" t="n">
         <v>8</v>
       </c>
       <c r="I236" t="n">
-        <v>-2.223559386621332</v>
+        <v>-2.387580156053559</v>
       </c>
       <c r="J236" t="n">
         <v>-78.44895522793473</v>
@@ -10893,17 +10891,17 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G237" t="n">
-        <v>-78.45137478893351</v>
+        <v>-78.45117878732135</v>
       </c>
       <c r="H237" t="n">
         <v>8</v>
       </c>
       <c r="I237" t="n">
-        <v>-2.419560998774273</v>
+        <v>-2.223559386621332</v>
       </c>
       <c r="J237" t="n">
         <v>-78.44895522793473</v>
@@ -10939,17 +10937,17 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G238" t="n">
-        <v>-78.45061780340897</v>
+        <v>-78.45137478893351</v>
       </c>
       <c r="H238" t="n">
         <v>8</v>
       </c>
       <c r="I238" t="n">
-        <v>-1.66257547424209</v>
+        <v>-2.419560998774273</v>
       </c>
       <c r="J238" t="n">
         <v>-78.44895522793473</v>
@@ -10972,38 +10970,40 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>fluoroform</t>
+          <t>ethane</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G239" t="n">
-        <v>-332.2246365681235</v>
+        <v>-78.45061780340897</v>
       </c>
       <c r="H239" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I239" t="n">
-        <v>-2.941598056793282</v>
+        <v>-1.66257547424209</v>
       </c>
       <c r="J239" t="n">
-        <v>-332.2216949700667</v>
+        <v>-78.44895522793473</v>
       </c>
       <c r="K239" t="n">
-        <v>-332.0975924899263</v>
-      </c>
-      <c r="L239" t="inlineStr"/>
+        <v>-78.30581623656136</v>
+      </c>
+      <c r="L239" t="n">
+        <v>-78.45323232971093</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
@@ -11029,17 +11029,17 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G240" t="n">
-        <v>-332.2246307453493</v>
+        <v>-332.2246365681235</v>
       </c>
       <c r="H240" t="n">
         <v>5</v>
       </c>
       <c r="I240" t="n">
-        <v>-2.935775282594477</v>
+        <v>-2.941598056793282</v>
       </c>
       <c r="J240" t="n">
         <v>-332.2216949700667</v>
@@ -11073,17 +11073,17 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G241" t="n">
-        <v>-332.22442506618</v>
+        <v>-332.2246307453493</v>
       </c>
       <c r="H241" t="n">
         <v>5</v>
       </c>
       <c r="I241" t="n">
-        <v>-2.730096113339187</v>
+        <v>-2.935775282594477</v>
       </c>
       <c r="J241" t="n">
         <v>-332.2216949700667</v>
@@ -11117,17 +11117,17 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G242" t="n">
-        <v>-332.2244710473527</v>
+        <v>-332.22442506618</v>
       </c>
       <c r="H242" t="n">
         <v>5</v>
       </c>
       <c r="I242" t="n">
-        <v>-2.7760772860006</v>
+        <v>-2.730096113339187</v>
       </c>
       <c r="J242" t="n">
         <v>-332.2216949700667</v>
@@ -11161,17 +11161,17 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G243" t="n">
-        <v>-332.2246224829088</v>
+        <v>-332.2244710473527</v>
       </c>
       <c r="H243" t="n">
         <v>5</v>
       </c>
       <c r="I243" t="n">
-        <v>-2.92751284212045</v>
+        <v>-2.7760772860006</v>
       </c>
       <c r="J243" t="n">
         <v>-332.2216949700667</v>
@@ -11205,17 +11205,17 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G244" t="n">
-        <v>-332.2240364957947</v>
+        <v>-332.2246224829088</v>
       </c>
       <c r="H244" t="n">
         <v>5</v>
       </c>
       <c r="I244" t="n">
-        <v>-2.341525728070337</v>
+        <v>-2.92751284212045</v>
       </c>
       <c r="J244" t="n">
         <v>-332.2216949700667</v>
@@ -11241,25 +11241,25 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G245" t="n">
-        <v>-332.224676388053</v>
+        <v>-332.2240364957947</v>
       </c>
       <c r="H245" t="n">
         <v>5</v>
       </c>
       <c r="I245" t="n">
-        <v>-2.981417986347878</v>
+        <v>-2.341525728070337</v>
       </c>
       <c r="J245" t="n">
         <v>-332.2216949700667</v>
@@ -11293,17 +11293,17 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G246" t="n">
-        <v>-332.2251305982015</v>
+        <v>-332.224676388053</v>
       </c>
       <c r="H246" t="n">
         <v>5</v>
       </c>
       <c r="I246" t="n">
-        <v>-3.435628134809576</v>
+        <v>-2.981417986347878</v>
       </c>
       <c r="J246" t="n">
         <v>-332.2216949700667</v>
@@ -11337,17 +11337,17 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G247" t="n">
-        <v>-332.2249345028254</v>
+        <v>-332.2251305982015</v>
       </c>
       <c r="H247" t="n">
         <v>5</v>
       </c>
       <c r="I247" t="n">
-        <v>-3.23953275869826</v>
+        <v>-3.435628134809576</v>
       </c>
       <c r="J247" t="n">
         <v>-332.2216949700667</v>
@@ -11381,17 +11381,17 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G248" t="n">
-        <v>-332.2246195686212</v>
+        <v>-332.2249345028254</v>
       </c>
       <c r="H248" t="n">
         <v>5</v>
       </c>
       <c r="I248" t="n">
-        <v>-2.924598554557178</v>
+        <v>-3.23953275869826</v>
       </c>
       <c r="J248" t="n">
         <v>-332.2216949700667</v>
@@ -11425,17 +11425,17 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G249" t="n">
-        <v>-332.2249202894409</v>
+        <v>-332.2246195686212</v>
       </c>
       <c r="H249" t="n">
         <v>5</v>
       </c>
       <c r="I249" t="n">
-        <v>-3.225319374223545</v>
+        <v>-2.924598554557178</v>
       </c>
       <c r="J249" t="n">
         <v>-332.2216949700667</v>
@@ -11469,17 +11469,17 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>-332.2237835069325</v>
+        <v>-332.2249202894409</v>
       </c>
       <c r="H250" t="n">
         <v>5</v>
       </c>
       <c r="I250" t="n">
-        <v>-2.088536865812785</v>
+        <v>-3.225319374223545</v>
       </c>
       <c r="J250" t="n">
         <v>-332.2216949700667</v>
@@ -11505,25 +11505,25 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>-332.2247230941931</v>
+        <v>-332.2237835069325</v>
       </c>
       <c r="H251" t="n">
         <v>5</v>
       </c>
       <c r="I251" t="n">
-        <v>-3.028124126387866</v>
+        <v>-2.088536865812785</v>
       </c>
       <c r="J251" t="n">
         <v>-332.2216949700667</v>
@@ -11557,17 +11557,17 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>-332.2249892256363</v>
+        <v>-332.2247230941931</v>
       </c>
       <c r="H252" t="n">
         <v>5</v>
       </c>
       <c r="I252" t="n">
-        <v>-3.294255569642246</v>
+        <v>-3.028124126387866</v>
       </c>
       <c r="J252" t="n">
         <v>-332.2216949700667</v>
@@ -11601,17 +11601,17 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>-332.2247979015166</v>
+        <v>-332.2249892256363</v>
       </c>
       <c r="H253" t="n">
         <v>5</v>
       </c>
       <c r="I253" t="n">
-        <v>-3.102931449916468</v>
+        <v>-3.294255569642246</v>
       </c>
       <c r="J253" t="n">
         <v>-332.2216949700667</v>
@@ -11645,17 +11645,17 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G254" t="n">
-        <v>-332.2248094077499</v>
+        <v>-332.2247979015166</v>
       </c>
       <c r="H254" t="n">
         <v>5</v>
       </c>
       <c r="I254" t="n">
-        <v>-3.114437683279903</v>
+        <v>-3.102931449916468</v>
       </c>
       <c r="J254" t="n">
         <v>-332.2216949700667</v>
@@ -11689,17 +11689,17 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>-332.2248433300495</v>
+        <v>-332.2248094077499</v>
       </c>
       <c r="H255" t="n">
         <v>5</v>
       </c>
       <c r="I255" t="n">
-        <v>-3.148359982844795</v>
+        <v>-3.114437683279903</v>
       </c>
       <c r="J255" t="n">
         <v>-332.2216949700667</v>
@@ -11733,17 +11733,17 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>-332.2243650958763</v>
+        <v>-332.2248433300495</v>
       </c>
       <c r="H256" t="n">
         <v>5</v>
       </c>
       <c r="I256" t="n">
-        <v>-2.670125809629553</v>
+        <v>-3.148359982844795</v>
       </c>
       <c r="J256" t="n">
         <v>-332.2216949700667</v>
@@ -11769,25 +11769,25 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G257" t="n">
-        <v>-332.2248500701731</v>
+        <v>-332.2243650958763</v>
       </c>
       <c r="H257" t="n">
         <v>5</v>
       </c>
       <c r="I257" t="n">
-        <v>-3.155100106482678</v>
+        <v>-2.670125809629553</v>
       </c>
       <c r="J257" t="n">
         <v>-332.2216949700667</v>
@@ -11821,17 +11821,17 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G258" t="n">
-        <v>-332.2248193754481</v>
+        <v>-332.2248500701731</v>
       </c>
       <c r="H258" t="n">
         <v>5</v>
       </c>
       <c r="I258" t="n">
-        <v>-3.124405381470297</v>
+        <v>-3.155100106482678</v>
       </c>
       <c r="J258" t="n">
         <v>-332.2216949700667</v>
@@ -11865,17 +11865,17 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G259" t="n">
-        <v>-332.2250752968361</v>
+        <v>-332.2248193754481</v>
       </c>
       <c r="H259" t="n">
         <v>5</v>
       </c>
       <c r="I259" t="n">
-        <v>-3.380326769388375</v>
+        <v>-3.124405381470297</v>
       </c>
       <c r="J259" t="n">
         <v>-332.2216949700667</v>
@@ -11909,17 +11909,17 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G260" t="n">
-        <v>-332.2249500221382</v>
+        <v>-332.2250752968361</v>
       </c>
       <c r="H260" t="n">
         <v>5</v>
       </c>
       <c r="I260" t="n">
-        <v>-3.255052071494902</v>
+        <v>-3.380326769388375</v>
       </c>
       <c r="J260" t="n">
         <v>-332.2216949700667</v>
@@ -11953,17 +11953,17 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G261" t="n">
-        <v>-332.2247981413528</v>
+        <v>-332.2249500221382</v>
       </c>
       <c r="H261" t="n">
         <v>5</v>
       </c>
       <c r="I261" t="n">
-        <v>-3.103171286170436</v>
+        <v>-3.255052071494902</v>
       </c>
       <c r="J261" t="n">
         <v>-332.2216949700667</v>
@@ -11997,17 +11997,17 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G262" t="n">
-        <v>-332.2241428665708</v>
+        <v>-332.2247981413528</v>
       </c>
       <c r="H262" t="n">
         <v>5</v>
       </c>
       <c r="I262" t="n">
-        <v>-2.447896504179425</v>
+        <v>-3.103171286170436</v>
       </c>
       <c r="J262" t="n">
         <v>-332.2216949700667</v>
@@ -12033,25 +12033,25 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G263" t="n">
-        <v>-332.2249277911654</v>
+        <v>-332.2241428665708</v>
       </c>
       <c r="H263" t="n">
         <v>5</v>
       </c>
       <c r="I263" t="n">
-        <v>-3.232821098720251</v>
+        <v>-2.447896504179425</v>
       </c>
       <c r="J263" t="n">
         <v>-332.2216949700667</v>
@@ -12085,17 +12085,17 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G264" t="n">
-        <v>-332.2251275965907</v>
+        <v>-332.2249277911654</v>
       </c>
       <c r="H264" t="n">
         <v>5</v>
       </c>
       <c r="I264" t="n">
-        <v>-3.432626523988347</v>
+        <v>-3.232821098720251</v>
       </c>
       <c r="J264" t="n">
         <v>-332.2216949700667</v>
@@ -12129,17 +12129,17 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G265" t="n">
-        <v>-332.2249630125604</v>
+        <v>-332.2251275965907</v>
       </c>
       <c r="H265" t="n">
         <v>5</v>
       </c>
       <c r="I265" t="n">
-        <v>-3.268042493743906</v>
+        <v>-3.432626523988347</v>
       </c>
       <c r="J265" t="n">
         <v>-332.2216949700667</v>
@@ -12173,17 +12173,17 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G266" t="n">
-        <v>-332.2248289997194</v>
+        <v>-332.2249630125604</v>
       </c>
       <c r="H266" t="n">
         <v>5</v>
       </c>
       <c r="I266" t="n">
-        <v>-3.134029652699155</v>
+        <v>-3.268042493743906</v>
       </c>
       <c r="J266" t="n">
         <v>-332.2216949700667</v>
@@ -12217,17 +12217,17 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G267" t="n">
-        <v>-332.2248642431461</v>
+        <v>-332.2248289997194</v>
       </c>
       <c r="H267" t="n">
         <v>5</v>
       </c>
       <c r="I267" t="n">
-        <v>-3.169273079436152</v>
+        <v>-3.134029652699155</v>
       </c>
       <c r="J267" t="n">
         <v>-332.2216949700667</v>
@@ -12261,17 +12261,17 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G268" t="n">
-        <v>-332.2240040230492</v>
+        <v>-332.2248642431461</v>
       </c>
       <c r="H268" t="n">
         <v>5</v>
       </c>
       <c r="I268" t="n">
-        <v>-2.309052982525372</v>
+        <v>-3.169273079436152</v>
       </c>
       <c r="J268" t="n">
         <v>-332.2216949700667</v>
@@ -12287,7 +12287,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>cc-pVDZ</t>
+          <t>STO-3G</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -12297,31 +12297,31 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G269" t="n">
-        <v>-336.8260363693874</v>
+        <v>-332.2240040230492</v>
       </c>
       <c r="H269" t="n">
         <v>5</v>
       </c>
       <c r="I269" t="n">
-        <v>-1.60436881020587</v>
+        <v>-2.309052982525372</v>
       </c>
       <c r="J269" t="n">
-        <v>-336.8244320005772</v>
+        <v>-332.2216949700667</v>
       </c>
       <c r="K269" t="n">
-        <v>-336.7867835322212</v>
+        <v>-332.0975924899263</v>
       </c>
       <c r="L269" t="inlineStr"/>
     </row>
@@ -12349,17 +12349,17 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G270" t="n">
-        <v>-336.8260349315088</v>
+        <v>-336.8260363693874</v>
       </c>
       <c r="H270" t="n">
         <v>5</v>
       </c>
       <c r="I270" t="n">
-        <v>-1.602930931653646</v>
+        <v>-1.60436881020587</v>
       </c>
       <c r="J270" t="n">
         <v>-336.8244320005772</v>
@@ -12385,25 +12385,25 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G271" t="n">
-        <v>-336.8260355655501</v>
+        <v>-336.8260349315088</v>
       </c>
       <c r="H271" t="n">
         <v>5</v>
       </c>
       <c r="I271" t="n">
-        <v>-1.603564972924687</v>
+        <v>-1.602930931653646</v>
       </c>
       <c r="J271" t="n">
         <v>-336.8244320005772</v>
@@ -12429,25 +12429,25 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G272" t="n">
-        <v>-336.8260602705358</v>
+        <v>-336.8260355655501</v>
       </c>
       <c r="H272" t="n">
         <v>5</v>
       </c>
       <c r="I272" t="n">
-        <v>-1.628269958587225</v>
+        <v>-1.603564972924687</v>
       </c>
       <c r="J272" t="n">
         <v>-336.8244320005772</v>
@@ -12463,45 +12463,43 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>STO-3G</t>
+          <t>cc-pVDZ</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>methanol</t>
+          <t>fluoroform</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G273" t="n">
-        <v>-113.662465407226</v>
+        <v>-336.8260602705358</v>
       </c>
       <c r="H273" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I273" t="n">
-        <v>-1.699912164056627</v>
+        <v>-1.628269958587225</v>
       </c>
       <c r="J273" t="n">
-        <v>-113.660765495062</v>
+        <v>-336.8244320005772</v>
       </c>
       <c r="K273" t="n">
-        <v>-113.5447589109086</v>
-      </c>
-      <c r="L273" t="n">
-        <v>-113.6626087137703</v>
-      </c>
+        <v>-336.7867835322212</v>
+      </c>
+      <c r="L273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
@@ -12527,17 +12525,17 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G274" t="n">
-        <v>-113.6624868064293</v>
+        <v>-113.662465407226</v>
       </c>
       <c r="H274" t="n">
         <v>6</v>
       </c>
       <c r="I274" t="n">
-        <v>-1.721311367376188</v>
+        <v>-1.699912164056627</v>
       </c>
       <c r="J274" t="n">
         <v>-113.660765495062</v>
@@ -12573,17 +12571,17 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G275" t="n">
-        <v>-113.6624880300175</v>
+        <v>-113.6624868064293</v>
       </c>
       <c r="H275" t="n">
         <v>6</v>
       </c>
       <c r="I275" t="n">
-        <v>-1.722534955561628</v>
+        <v>-1.721311367376188</v>
       </c>
       <c r="J275" t="n">
         <v>-113.660765495062</v>
@@ -12619,17 +12617,17 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G276" t="n">
-        <v>-113.662529006638</v>
+        <v>-113.6624880300175</v>
       </c>
       <c r="H276" t="n">
         <v>6</v>
       </c>
       <c r="I276" t="n">
-        <v>-1.76351157601573</v>
+        <v>-1.722534955561628</v>
       </c>
       <c r="J276" t="n">
         <v>-113.660765495062</v>
@@ -12665,17 +12663,17 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G277" t="n">
-        <v>-113.6625658140582</v>
+        <v>-113.662529006638</v>
       </c>
       <c r="H277" t="n">
         <v>6</v>
       </c>
       <c r="I277" t="n">
-        <v>-1.800318996217243</v>
+        <v>-1.76351157601573</v>
       </c>
       <c r="J277" t="n">
         <v>-113.660765495062</v>
@@ -12703,25 +12701,25 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G278" t="n">
-        <v>-113.6625710272076</v>
+        <v>-113.6625658140582</v>
       </c>
       <c r="H278" t="n">
         <v>6</v>
       </c>
       <c r="I278" t="n">
-        <v>-1.8055321456103</v>
+        <v>-1.800318996217243</v>
       </c>
       <c r="J278" t="n">
         <v>-113.660765495062</v>
@@ -12757,17 +12755,17 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G279" t="n">
-        <v>-113.662560752718</v>
+        <v>-113.6625710272076</v>
       </c>
       <c r="H279" t="n">
         <v>6</v>
       </c>
       <c r="I279" t="n">
-        <v>-1.795257656041827</v>
+        <v>-1.8055321456103</v>
       </c>
       <c r="J279" t="n">
         <v>-113.660765495062</v>
@@ -12803,17 +12801,17 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G280" t="n">
-        <v>-113.6625647001974</v>
+        <v>-113.662560752718</v>
       </c>
       <c r="H280" t="n">
         <v>6</v>
       </c>
       <c r="I280" t="n">
-        <v>-1.799205135469606</v>
+        <v>-1.795257656041827</v>
       </c>
       <c r="J280" t="n">
         <v>-113.660765495062</v>
@@ -12849,17 +12847,17 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G281" t="n">
-        <v>-113.6625437333032</v>
+        <v>-113.6625647001974</v>
       </c>
       <c r="H281" t="n">
         <v>6</v>
       </c>
       <c r="I281" t="n">
-        <v>-1.778238241243457</v>
+        <v>-1.799205135469606</v>
       </c>
       <c r="J281" t="n">
         <v>-113.660765495062</v>
@@ -12895,17 +12893,17 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G282" t="n">
-        <v>-113.6625601893481</v>
+        <v>-113.6625437333032</v>
       </c>
       <c r="H282" t="n">
         <v>6</v>
       </c>
       <c r="I282" t="n">
-        <v>-1.794694286147092</v>
+        <v>-1.778238241243457</v>
       </c>
       <c r="J282" t="n">
         <v>-113.660765495062</v>
@@ -12933,25 +12931,25 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G283" t="n">
-        <v>-113.6625479048084</v>
+        <v>-113.6625601893481</v>
       </c>
       <c r="H283" t="n">
         <v>6</v>
       </c>
       <c r="I283" t="n">
-        <v>-1.782409746439839</v>
+        <v>-1.794694286147092</v>
       </c>
       <c r="J283" t="n">
         <v>-113.660765495062</v>
@@ -12987,17 +12985,17 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G284" t="n">
-        <v>-113.6625624986648</v>
+        <v>-113.6625479048084</v>
       </c>
       <c r="H284" t="n">
         <v>6</v>
       </c>
       <c r="I284" t="n">
-        <v>-1.797003602817426</v>
+        <v>-1.782409746439839</v>
       </c>
       <c r="J284" t="n">
         <v>-113.660765495062</v>
@@ -13033,17 +13031,17 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G285" t="n">
-        <v>-113.6625700252463</v>
+        <v>-113.6625624986648</v>
       </c>
       <c r="H285" t="n">
         <v>6</v>
       </c>
       <c r="I285" t="n">
-        <v>-1.804530184372766</v>
+        <v>-1.797003602817426</v>
       </c>
       <c r="J285" t="n">
         <v>-113.660765495062</v>
@@ -13079,17 +13077,17 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G286" t="n">
-        <v>-113.6625657413047</v>
+        <v>-113.6625700252463</v>
       </c>
       <c r="H286" t="n">
         <v>6</v>
       </c>
       <c r="I286" t="n">
-        <v>-1.800246242723347</v>
+        <v>-1.804530184372766</v>
       </c>
       <c r="J286" t="n">
         <v>-113.660765495062</v>
@@ -13125,17 +13123,17 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G287" t="n">
-        <v>-113.6625601119439</v>
+        <v>-113.6625657413047</v>
       </c>
       <c r="H287" t="n">
         <v>6</v>
       </c>
       <c r="I287" t="n">
-        <v>-1.794616881952038</v>
+        <v>-1.800246242723347</v>
       </c>
       <c r="J287" t="n">
         <v>-113.660765495062</v>
@@ -13163,25 +13161,25 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G288" t="n">
-        <v>-113.6625502308704</v>
+        <v>-113.6625601119439</v>
       </c>
       <c r="H288" t="n">
         <v>6</v>
       </c>
       <c r="I288" t="n">
-        <v>-1.784735808413984</v>
+        <v>-1.794616881952038</v>
       </c>
       <c r="J288" t="n">
         <v>-113.660765495062</v>
@@ -13217,17 +13215,17 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G289" t="n">
-        <v>-113.6625663277787</v>
+        <v>-113.6625502308704</v>
       </c>
       <c r="H289" t="n">
         <v>6</v>
       </c>
       <c r="I289" t="n">
-        <v>-1.800832716767786</v>
+        <v>-1.784735808413984</v>
       </c>
       <c r="J289" t="n">
         <v>-113.660765495062</v>
@@ -13263,17 +13261,17 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G290" t="n">
-        <v>-113.6625684815751</v>
+        <v>-113.6625663277787</v>
       </c>
       <c r="H290" t="n">
         <v>6</v>
       </c>
       <c r="I290" t="n">
-        <v>-1.802986513084193</v>
+        <v>-1.800832716767786</v>
       </c>
       <c r="J290" t="n">
         <v>-113.660765495062</v>
@@ -13309,17 +13307,17 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G291" t="n">
-        <v>-113.662569827856</v>
+        <v>-113.6625684815751</v>
       </c>
       <c r="H291" t="n">
         <v>6</v>
       </c>
       <c r="I291" t="n">
-        <v>-1.804332794009156</v>
+        <v>-1.802986513084193</v>
       </c>
       <c r="J291" t="n">
         <v>-113.660765495062</v>
@@ -13355,17 +13353,17 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G292" t="n">
-        <v>-113.6625550727545</v>
+        <v>-113.662569827856</v>
       </c>
       <c r="H292" t="n">
         <v>6</v>
       </c>
       <c r="I292" t="n">
-        <v>-1.789577692520083</v>
+        <v>-1.804332794009156</v>
       </c>
       <c r="J292" t="n">
         <v>-113.660765495062</v>
@@ -13393,25 +13391,25 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G293" t="n">
-        <v>-113.6625602992152</v>
+        <v>-113.6625550727545</v>
       </c>
       <c r="H293" t="n">
         <v>6</v>
       </c>
       <c r="I293" t="n">
-        <v>-1.794804153220753</v>
+        <v>-1.789577692520083</v>
       </c>
       <c r="J293" t="n">
         <v>-113.660765495062</v>
@@ -13447,17 +13445,17 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G294" t="n">
-        <v>-113.6625603727529</v>
+        <v>-113.6625602992152</v>
       </c>
       <c r="H294" t="n">
         <v>6</v>
       </c>
       <c r="I294" t="n">
-        <v>-1.794877690926455</v>
+        <v>-1.794804153220753</v>
       </c>
       <c r="J294" t="n">
         <v>-113.660765495062</v>
@@ -13493,17 +13491,17 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G295" t="n">
-        <v>-113.6625716349185</v>
+        <v>-113.6625603727529</v>
       </c>
       <c r="H295" t="n">
         <v>6</v>
       </c>
       <c r="I295" t="n">
-        <v>-1.806139856554978</v>
+        <v>-1.794877690926455</v>
       </c>
       <c r="J295" t="n">
         <v>-113.660765495062</v>
@@ -13539,17 +13537,17 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G296" t="n">
-        <v>-113.6625638130971</v>
+        <v>-113.6625716349185</v>
       </c>
       <c r="H296" t="n">
         <v>6</v>
       </c>
       <c r="I296" t="n">
-        <v>-1.79831803517061</v>
+        <v>-1.806139856554978</v>
       </c>
       <c r="J296" t="n">
         <v>-113.660765495062</v>
@@ -13585,17 +13583,17 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G297" t="n">
-        <v>-113.6625610067019</v>
+        <v>-113.6625638130971</v>
       </c>
       <c r="H297" t="n">
         <v>6</v>
       </c>
       <c r="I297" t="n">
-        <v>-1.79551163996905</v>
+        <v>-1.79831803517061</v>
       </c>
       <c r="J297" t="n">
         <v>-113.660765495062</v>
@@ -13618,38 +13616,40 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>prop-2-en-1-ol</t>
+          <t>methanol</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G298" t="n">
-        <v>-189.6808205163561</v>
+        <v>-113.6625610067019</v>
       </c>
       <c r="H298" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I298" t="n">
-        <v>46.19523674443826</v>
+        <v>-1.79551163996905</v>
       </c>
       <c r="J298" t="n">
-        <v>-189.7270157531005</v>
+        <v>-113.660765495062</v>
       </c>
       <c r="K298" t="n">
-        <v>-189.4804271888057</v>
-      </c>
-      <c r="L298" t="inlineStr"/>
+        <v>-113.5447589109086</v>
+      </c>
+      <c r="L298" t="n">
+        <v>-113.6626087137703</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
@@ -13675,17 +13675,17 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G299" t="n">
-        <v>-189.6143465310523</v>
+        <v>-189.6808205163561</v>
       </c>
       <c r="H299" t="n">
         <v>10</v>
       </c>
       <c r="I299" t="n">
-        <v>112.6692220482255</v>
+        <v>46.19523674443826</v>
       </c>
       <c r="J299" t="n">
         <v>-189.7270157531005</v>
@@ -13719,17 +13719,17 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G300" t="n">
-        <v>-189.6031336104605</v>
+        <v>-189.6143465310523</v>
       </c>
       <c r="H300" t="n">
         <v>10</v>
       </c>
       <c r="I300" t="n">
-        <v>123.8821426400136</v>
+        <v>112.6692220482255</v>
       </c>
       <c r="J300" t="n">
         <v>-189.7270157531005</v>
@@ -13763,17 +13763,17 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G301" t="n">
-        <v>-189.5769119101616</v>
+        <v>-189.6031336104605</v>
       </c>
       <c r="H301" t="n">
         <v>10</v>
       </c>
       <c r="I301" t="n">
-        <v>150.1038429388473</v>
+        <v>123.8821426400136</v>
       </c>
       <c r="J301" t="n">
         <v>-189.7270157531005</v>
@@ -13807,17 +13807,17 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G302" t="n">
-        <v>-188.8520013562317</v>
+        <v>-189.5769119101616</v>
       </c>
       <c r="H302" t="n">
         <v>10</v>
       </c>
       <c r="I302" t="n">
-        <v>875.0143968688349</v>
+        <v>150.1038429388473</v>
       </c>
       <c r="J302" t="n">
         <v>-189.7270157531005</v>
@@ -13851,17 +13851,17 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G303" t="n">
-        <v>-189.7120631697455</v>
+        <v>-188.8520013562317</v>
       </c>
       <c r="H303" t="n">
         <v>10</v>
       </c>
       <c r="I303" t="n">
-        <v>14.95258335495464</v>
+        <v>875.0143968688349</v>
       </c>
       <c r="J303" t="n">
         <v>-189.7270157531005</v>
@@ -13887,25 +13887,25 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G304" t="n">
-        <v>-189.518883282987</v>
+        <v>-189.7120631697455</v>
       </c>
       <c r="H304" t="n">
         <v>10</v>
       </c>
       <c r="I304" t="n">
-        <v>208.132470113469</v>
+        <v>14.95258335495464</v>
       </c>
       <c r="J304" t="n">
         <v>-189.7270157531005</v>
@@ -13939,17 +13939,17 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G305" t="n">
-        <v>-189.5285622451023</v>
+        <v>-189.518883282987</v>
       </c>
       <c r="H305" t="n">
         <v>10</v>
       </c>
       <c r="I305" t="n">
-        <v>198.4535079982379</v>
+        <v>208.132470113469</v>
       </c>
       <c r="J305" t="n">
         <v>-189.7270157531005</v>
@@ -13983,17 +13983,17 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G306" t="n">
-        <v>-189.5014081997568</v>
+        <v>-189.5285622451023</v>
       </c>
       <c r="H306" t="n">
         <v>10</v>
       </c>
       <c r="I306" t="n">
-        <v>225.6075533436501</v>
+        <v>198.4535079982379</v>
       </c>
       <c r="J306" t="n">
         <v>-189.7270157531005</v>
@@ -14027,17 +14027,17 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G307" t="n">
-        <v>-189.5268304577797</v>
+        <v>-189.5014081997568</v>
       </c>
       <c r="H307" t="n">
         <v>10</v>
       </c>
       <c r="I307" t="n">
-        <v>200.1852953208072</v>
+        <v>225.6075533436501</v>
       </c>
       <c r="J307" t="n">
         <v>-189.7270157531005</v>
@@ -14071,17 +14071,17 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G308" t="n">
-        <v>-189.5282989439489</v>
+        <v>-189.5268304577797</v>
       </c>
       <c r="H308" t="n">
         <v>10</v>
       </c>
       <c r="I308" t="n">
-        <v>198.7168091515628</v>
+        <v>200.1852953208072</v>
       </c>
       <c r="J308" t="n">
         <v>-189.7270157531005</v>
@@ -14115,17 +14115,17 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G309" t="n">
-        <v>-189.7090767448711</v>
+        <v>-189.5282989439489</v>
       </c>
       <c r="H309" t="n">
         <v>10</v>
       </c>
       <c r="I309" t="n">
-        <v>17.93900822934802</v>
+        <v>198.7168091515628</v>
       </c>
       <c r="J309" t="n">
         <v>-189.7270157531005</v>
@@ -14151,25 +14151,25 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>-189.4953906383641</v>
+        <v>-189.7090767448711</v>
       </c>
       <c r="H310" t="n">
         <v>10</v>
       </c>
       <c r="I310" t="n">
-        <v>231.6251147363459</v>
+        <v>17.93900822934802</v>
       </c>
       <c r="J310" t="n">
         <v>-189.7270157531005</v>
@@ -14203,17 +14203,17 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>-189.524292952043</v>
+        <v>-189.4953906383641</v>
       </c>
       <c r="H311" t="n">
         <v>10</v>
       </c>
       <c r="I311" t="n">
-        <v>202.7228010574618</v>
+        <v>231.6251147363459</v>
       </c>
       <c r="J311" t="n">
         <v>-189.7270157531005</v>
@@ -14247,17 +14247,17 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G312" t="n">
-        <v>-189.535138180474</v>
+        <v>-189.524292952043</v>
       </c>
       <c r="H312" t="n">
         <v>10</v>
       </c>
       <c r="I312" t="n">
-        <v>191.877572626538</v>
+        <v>202.7228010574618</v>
       </c>
       <c r="J312" t="n">
         <v>-189.7270157531005</v>
@@ -14291,17 +14291,17 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G313" t="n">
-        <v>-188.8723347083925</v>
+        <v>-189.535138180474</v>
       </c>
       <c r="H313" t="n">
         <v>10</v>
       </c>
       <c r="I313" t="n">
-        <v>854.6810447079451</v>
+        <v>191.877572626538</v>
       </c>
       <c r="J313" t="n">
         <v>-189.7270157531005</v>
@@ -14335,17 +14335,17 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G314" t="n">
-        <v>-188.8735615062697</v>
+        <v>-188.8723347083925</v>
       </c>
       <c r="H314" t="n">
         <v>10</v>
       </c>
       <c r="I314" t="n">
-        <v>853.4542468308359</v>
+        <v>854.6810447079451</v>
       </c>
       <c r="J314" t="n">
         <v>-189.7270157531005</v>
@@ -14379,17 +14379,17 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G315" t="n">
-        <v>-189.7107457557645</v>
+        <v>-188.8735615062697</v>
       </c>
       <c r="H315" t="n">
         <v>10</v>
       </c>
       <c r="I315" t="n">
-        <v>16.26999733599632</v>
+        <v>853.4542468308359</v>
       </c>
       <c r="J315" t="n">
         <v>-189.7270157531005</v>
@@ -14415,25 +14415,25 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G316" t="n">
-        <v>-189.5250776033889</v>
+        <v>-189.7107457557645</v>
       </c>
       <c r="H316" t="n">
         <v>10</v>
       </c>
       <c r="I316" t="n">
-        <v>201.9381497116228</v>
+        <v>16.26999733599632</v>
       </c>
       <c r="J316" t="n">
         <v>-189.7270157531005</v>
@@ -14467,17 +14467,17 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G317" t="n">
-        <v>-189.4969202256459</v>
+        <v>-189.5250776033889</v>
       </c>
       <c r="H317" t="n">
         <v>10</v>
       </c>
       <c r="I317" t="n">
-        <v>230.09552745458</v>
+        <v>201.9381497116228</v>
       </c>
       <c r="J317" t="n">
         <v>-189.7270157531005</v>
@@ -14511,17 +14511,17 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G318" t="n">
-        <v>-189.4977761056279</v>
+        <v>-189.4969202256459</v>
       </c>
       <c r="H318" t="n">
         <v>10</v>
       </c>
       <c r="I318" t="n">
-        <v>229.239647472582</v>
+        <v>230.09552745458</v>
       </c>
       <c r="J318" t="n">
         <v>-189.7270157531005</v>
@@ -14555,17 +14555,17 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G319" t="n">
-        <v>-189.4941653785411</v>
+        <v>-189.4977761056279</v>
       </c>
       <c r="H319" t="n">
         <v>10</v>
       </c>
       <c r="I319" t="n">
-        <v>232.850374559348</v>
+        <v>229.239647472582</v>
       </c>
       <c r="J319" t="n">
         <v>-189.7270157531005</v>
@@ -14599,17 +14599,17 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G320" t="n">
-        <v>-188.2617589485396</v>
+        <v>-189.4941653785411</v>
       </c>
       <c r="H320" t="n">
         <v>10</v>
       </c>
       <c r="I320" t="n">
-        <v>1465.256804560852</v>
+        <v>232.850374559348</v>
       </c>
       <c r="J320" t="n">
         <v>-189.7270157531005</v>
@@ -14643,17 +14643,17 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G321" t="n">
-        <v>-189.7114958132647</v>
+        <v>-188.2617589485396</v>
       </c>
       <c r="H321" t="n">
         <v>10</v>
       </c>
       <c r="I321" t="n">
-        <v>15.51993983576949</v>
+        <v>1465.256804560852</v>
       </c>
       <c r="J321" t="n">
         <v>-189.7270157531005</v>
@@ -14679,25 +14679,25 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G322" t="n">
-        <v>-189.5210193298893</v>
+        <v>-189.7114958132647</v>
       </c>
       <c r="H322" t="n">
         <v>10</v>
       </c>
       <c r="I322" t="n">
-        <v>205.9964232112179</v>
+        <v>15.51993983576949</v>
       </c>
       <c r="J322" t="n">
         <v>-189.7270157531005</v>
@@ -14731,17 +14731,17 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G323" t="n">
-        <v>-189.5239469397676</v>
+        <v>-189.5210193298893</v>
       </c>
       <c r="H323" t="n">
         <v>10</v>
       </c>
       <c r="I323" t="n">
-        <v>203.0688133328908</v>
+        <v>205.9964232112179</v>
       </c>
       <c r="J323" t="n">
         <v>-189.7270157531005</v>
@@ -14775,17 +14775,17 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G324" t="n">
-        <v>-188.5096926436997</v>
+        <v>-189.5239469397676</v>
       </c>
       <c r="H324" t="n">
         <v>10</v>
       </c>
       <c r="I324" t="n">
-        <v>1217.323109400752</v>
+        <v>203.0688133328908</v>
       </c>
       <c r="J324" t="n">
         <v>-189.7270157531005</v>
@@ -14819,17 +14819,17 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G325" t="n">
-        <v>-188.4868484899191</v>
+        <v>-188.5096926436997</v>
       </c>
       <c r="H325" t="n">
         <v>10</v>
       </c>
       <c r="I325" t="n">
-        <v>1240.167263181377</v>
+        <v>1217.323109400752</v>
       </c>
       <c r="J325" t="n">
         <v>-189.7270157531005</v>
@@ -14863,17 +14863,17 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G326" t="n">
-        <v>-188.5297595444494</v>
+        <v>-188.4868484899191</v>
       </c>
       <c r="H326" t="n">
         <v>10</v>
       </c>
       <c r="I326" t="n">
-        <v>1197.256208651083</v>
+        <v>1240.167263181377</v>
       </c>
       <c r="J326" t="n">
         <v>-189.7270157531005</v>
@@ -14907,17 +14907,17 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G327" t="n">
-        <v>-189.7115870741756</v>
+        <v>-188.5297595444494</v>
       </c>
       <c r="H327" t="n">
         <v>10</v>
       </c>
       <c r="I327" t="n">
-        <v>15.42867892493405</v>
+        <v>1197.256208651083</v>
       </c>
       <c r="J327" t="n">
         <v>-189.7270157531005</v>
@@ -14933,7 +14933,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>aug-cc-pVDZ</t>
+          <t>STO-3G</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -14943,31 +14943,31 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G328" t="n">
-        <v>-191.1634841176429</v>
+        <v>-189.7115870741756</v>
       </c>
       <c r="H328" t="n">
         <v>10</v>
       </c>
       <c r="I328" t="n">
-        <v>790.2878478354296</v>
+        <v>15.42867892493405</v>
       </c>
       <c r="J328" t="n">
-        <v>-191.9537719654783</v>
+        <v>-189.7270157531005</v>
       </c>
       <c r="K328" t="n">
-        <v>-191.9516344755187</v>
+        <v>-189.4804271888057</v>
       </c>
       <c r="L328" t="inlineStr"/>
     </row>
@@ -14987,11 +14987,11 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -14999,13 +14999,13 @@
         </is>
       </c>
       <c r="G329" t="n">
-        <v>-191.0731092276205</v>
+        <v>-191.9519974141113</v>
       </c>
       <c r="H329" t="n">
         <v>10</v>
       </c>
       <c r="I329" t="n">
-        <v>880.6627378578469</v>
+        <v>1.774551367020649</v>
       </c>
       <c r="J329" t="n">
         <v>-191.9537719654783</v>
@@ -15031,25 +15031,25 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G330" t="n">
-        <v>-191.149782554133</v>
+        <v>-191.1634841176429</v>
       </c>
       <c r="H330" t="n">
         <v>10</v>
       </c>
       <c r="I330" t="n">
-        <v>803.9894113453556</v>
+        <v>790.2878478354296</v>
       </c>
       <c r="J330" t="n">
         <v>-191.9537719654783</v>
@@ -15075,25 +15075,25 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>-191.9516573003273</v>
+        <v>-191.0731092276205</v>
       </c>
       <c r="H331" t="n">
         <v>10</v>
       </c>
       <c r="I331" t="n">
-        <v>2.114665150998007</v>
+        <v>880.6627378578469</v>
       </c>
       <c r="J331" t="n">
         <v>-191.9537719654783</v>
@@ -15119,25 +15119,25 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G332" t="n">
-        <v>-191.2452709160886</v>
+        <v>-191.149782554133</v>
       </c>
       <c r="H332" t="n">
         <v>10</v>
       </c>
       <c r="I332" t="n">
-        <v>708.5010493897244</v>
+        <v>803.9894113453556</v>
       </c>
       <c r="J332" t="n">
         <v>-191.9537719654783</v>
@@ -15171,17 +15171,17 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>-190.9183003641962</v>
+        <v>-191.9516573003273</v>
       </c>
       <c r="H333" t="n">
         <v>10</v>
       </c>
       <c r="I333" t="n">
-        <v>1035.471601282154</v>
+        <v>2.114665150998007</v>
       </c>
       <c r="J333" t="n">
         <v>-191.9537719654783</v>
@@ -15215,17 +15215,17 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G334" t="n">
-        <v>-191.2200076349744</v>
+        <v>-191.2452709160886</v>
       </c>
       <c r="H334" t="n">
         <v>10</v>
       </c>
       <c r="I334" t="n">
-        <v>733.7643305039592</v>
+        <v>708.5010493897244</v>
       </c>
       <c r="J334" t="n">
         <v>-191.9537719654783</v>
@@ -15259,17 +15259,17 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G335" t="n">
-        <v>-191.9516742432006</v>
+        <v>-190.9183003641962</v>
       </c>
       <c r="H335" t="n">
         <v>10</v>
       </c>
       <c r="I335" t="n">
-        <v>2.097722277710545</v>
+        <v>1035.471601282154</v>
       </c>
       <c r="J335" t="n">
         <v>-191.9537719654783</v>
@@ -15295,25 +15295,25 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>-191.1458496642358</v>
+        <v>-191.2200076349744</v>
       </c>
       <c r="H336" t="n">
         <v>10</v>
       </c>
       <c r="I336" t="n">
-        <v>807.92230124257</v>
+        <v>733.7643305039592</v>
       </c>
       <c r="J336" t="n">
         <v>-191.9537719654783</v>
@@ -15339,25 +15339,25 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G337" t="n">
-        <v>-191.2428047671126</v>
+        <v>-191.9516742432006</v>
       </c>
       <c r="H337" t="n">
         <v>10</v>
       </c>
       <c r="I337" t="n">
-        <v>710.9671983657222</v>
+        <v>2.097722277710545</v>
       </c>
       <c r="J337" t="n">
         <v>-191.9537719654783</v>
@@ -15391,17 +15391,17 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G338" t="n">
-        <v>-191.9518400899062</v>
+        <v>-191.1458496642358</v>
       </c>
       <c r="H338" t="n">
         <v>10</v>
       </c>
       <c r="I338" t="n">
-        <v>1.931875572097397</v>
+        <v>807.92230124257</v>
       </c>
       <c r="J338" t="n">
         <v>-191.9537719654783</v>
@@ -15427,25 +15427,25 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G339" t="n">
-        <v>-191.9516652011622</v>
+        <v>-191.2428047671126</v>
       </c>
       <c r="H339" t="n">
         <v>10</v>
       </c>
       <c r="I339" t="n">
-        <v>2.106764316124554</v>
+        <v>710.9671983657222</v>
       </c>
       <c r="J339" t="n">
         <v>-191.9537719654783</v>
@@ -15471,25 +15471,25 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G340" t="n">
-        <v>-191.9516657338321</v>
+        <v>-191.9518400899062</v>
       </c>
       <c r="H340" t="n">
         <v>10</v>
       </c>
       <c r="I340" t="n">
-        <v>2.106231646223478</v>
+        <v>1.931875572097397</v>
       </c>
       <c r="J340" t="n">
         <v>-191.9537719654783</v>
@@ -15523,17 +15523,17 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G341" t="n">
-        <v>-191.1482922822166</v>
+        <v>-191.9516652011622</v>
       </c>
       <c r="H341" t="n">
         <v>10</v>
       </c>
       <c r="I341" t="n">
-        <v>805.4796832617512</v>
+        <v>2.106764316124554</v>
       </c>
       <c r="J341" t="n">
         <v>-191.9537719654783</v>
@@ -15549,7 +15549,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>cc-pVDZ</t>
+          <t>aug-cc-pVDZ</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -15559,31 +15559,31 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G342" t="n">
-        <v>-191.9534485891146</v>
+        <v>-191.9516657338321</v>
       </c>
       <c r="H342" t="n">
         <v>10</v>
       </c>
       <c r="I342" t="n">
-        <v>44.03229792816887</v>
+        <v>2.106231646223478</v>
       </c>
       <c r="J342" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9537719654783</v>
       </c>
       <c r="K342" t="n">
-        <v>-191.9364953941601</v>
+        <v>-191.9516344755187</v>
       </c>
       <c r="L342" t="inlineStr"/>
     </row>
@@ -15593,7 +15593,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>cc-pVDZ</t>
+          <t>aug-cc-pVDZ</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -15603,31 +15603,31 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G343" t="n">
-        <v>-191.9738633977651</v>
+        <v>-191.1482922822166</v>
       </c>
       <c r="H343" t="n">
         <v>10</v>
       </c>
       <c r="I343" t="n">
-        <v>23.61748927771146</v>
+        <v>805.4796832617512</v>
       </c>
       <c r="J343" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9537719654783</v>
       </c>
       <c r="K343" t="n">
-        <v>-191.9364953941601</v>
+        <v>-191.9516344755187</v>
       </c>
       <c r="L343" t="inlineStr"/>
     </row>
@@ -15655,20 +15655,20 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G344" t="n">
-        <v>-191.9745863201936</v>
+        <v>-191.9534485891146</v>
       </c>
       <c r="H344" t="n">
         <v>10</v>
       </c>
       <c r="I344" t="n">
-        <v>22.89456684914626</v>
+        <v>44.03229792811203</v>
       </c>
       <c r="J344" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K344" t="n">
         <v>-191.9364953941601</v>
@@ -15699,20 +15699,20 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G345" t="n">
-        <v>-191.9750639772247</v>
+        <v>-191.9738633977651</v>
       </c>
       <c r="H345" t="n">
         <v>10</v>
       </c>
       <c r="I345" t="n">
-        <v>22.41690981807665</v>
+        <v>23.61748927765461</v>
       </c>
       <c r="J345" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K345" t="n">
         <v>-191.9364953941601</v>
@@ -15743,20 +15743,20 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G346" t="n">
-        <v>-191.9380213720039</v>
+        <v>-191.9745863201936</v>
       </c>
       <c r="H346" t="n">
         <v>10</v>
       </c>
       <c r="I346" t="n">
-        <v>59.45951503886704</v>
+        <v>22.89456684908941</v>
       </c>
       <c r="J346" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K346" t="n">
         <v>-191.9364953941601</v>
@@ -15787,20 +15787,20 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G347" t="n">
-        <v>-191.9921307417835</v>
+        <v>-191.9750639772247</v>
       </c>
       <c r="H347" t="n">
         <v>10</v>
       </c>
       <c r="I347" t="n">
-        <v>5.350145259313877</v>
+        <v>22.4169098180198</v>
       </c>
       <c r="J347" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K347" t="n">
         <v>-191.9364953941601</v>
@@ -15823,28 +15823,28 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G348" t="n">
-        <v>-191.9388807858837</v>
+        <v>-191.9380213720039</v>
       </c>
       <c r="H348" t="n">
         <v>10</v>
       </c>
       <c r="I348" t="n">
-        <v>58.60010115904402</v>
+        <v>59.4595150388102</v>
       </c>
       <c r="J348" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K348" t="n">
         <v>-191.9364953941601</v>
@@ -15867,28 +15867,28 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G349" t="n">
-        <v>-191.9560428619665</v>
+        <v>-191.9921307417835</v>
       </c>
       <c r="H349" t="n">
         <v>10</v>
       </c>
       <c r="I349" t="n">
-        <v>41.43802507624628</v>
+        <v>5.350145259257033</v>
       </c>
       <c r="J349" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K349" t="n">
         <v>-191.9364953941601</v>
@@ -15919,20 +15919,20 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G350" t="n">
-        <v>-191.3904179244482</v>
+        <v>-191.9388807858837</v>
       </c>
       <c r="H350" t="n">
         <v>10</v>
       </c>
       <c r="I350" t="n">
-        <v>607.0629625945401</v>
+        <v>58.60010115898717</v>
       </c>
       <c r="J350" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K350" t="n">
         <v>-191.9364953941601</v>
@@ -15963,20 +15963,20 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G351" t="n">
-        <v>-191.9529233348009</v>
+        <v>-191.9560428619665</v>
       </c>
       <c r="H351" t="n">
         <v>10</v>
       </c>
       <c r="I351" t="n">
-        <v>44.55755224191194</v>
+        <v>41.43802507618943</v>
       </c>
       <c r="J351" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K351" t="n">
         <v>-191.9364953941601</v>
@@ -16007,20 +16007,20 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G352" t="n">
-        <v>-191.9499334950364</v>
+        <v>-191.3904179244482</v>
       </c>
       <c r="H352" t="n">
         <v>10</v>
       </c>
       <c r="I352" t="n">
-        <v>47.54739200635072</v>
+        <v>607.0629625944832</v>
       </c>
       <c r="J352" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K352" t="n">
         <v>-191.9364953941601</v>
@@ -16051,20 +16051,20 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G353" t="n">
-        <v>-191.9928188383286</v>
+        <v>-191.9529233348009</v>
       </c>
       <c r="H353" t="n">
         <v>10</v>
       </c>
       <c r="I353" t="n">
-        <v>4.662048714152434</v>
+        <v>44.55755224185509</v>
       </c>
       <c r="J353" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K353" t="n">
         <v>-191.9364953941601</v>
@@ -16087,28 +16087,28 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E354" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G354" t="n">
-        <v>-191.9386763487821</v>
+        <v>-191.9499334950364</v>
       </c>
       <c r="H354" t="n">
         <v>10</v>
       </c>
       <c r="I354" t="n">
-        <v>58.80453826065946</v>
+        <v>47.54739200629388</v>
       </c>
       <c r="J354" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K354" t="n">
         <v>-191.9364953941601</v>
@@ -16131,28 +16131,28 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G355" t="n">
-        <v>-191.9394960360387</v>
+        <v>-191.9928188383286</v>
       </c>
       <c r="H355" t="n">
         <v>10</v>
       </c>
       <c r="I355" t="n">
-        <v>57.98485100402218</v>
+        <v>4.66204871409559</v>
       </c>
       <c r="J355" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K355" t="n">
         <v>-191.9364953941601</v>
@@ -16183,20 +16183,20 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G356" t="n">
-        <v>-191.1432948626463</v>
+        <v>-191.9386763487821</v>
       </c>
       <c r="H356" t="n">
         <v>10</v>
       </c>
       <c r="I356" t="n">
-        <v>854.186024396455</v>
+        <v>58.80453826060261</v>
       </c>
       <c r="J356" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K356" t="n">
         <v>-191.9364953941601</v>
@@ -16227,20 +16227,20 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G357" t="n">
-        <v>-191.9385272046664</v>
+        <v>-191.9394960360387</v>
       </c>
       <c r="H357" t="n">
         <v>10</v>
       </c>
       <c r="I357" t="n">
-        <v>58.95368237636944</v>
+        <v>57.98485100396533</v>
       </c>
       <c r="J357" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K357" t="n">
         <v>-191.9364953941601</v>
@@ -16271,20 +16271,20 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G358" t="n">
-        <v>-191.9373741140392</v>
+        <v>-191.1432948626463</v>
       </c>
       <c r="H358" t="n">
         <v>10</v>
       </c>
       <c r="I358" t="n">
-        <v>60.1067730035254</v>
+        <v>854.1860243963981</v>
       </c>
       <c r="J358" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K358" t="n">
         <v>-191.9364953941601</v>
@@ -16315,20 +16315,20 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G359" t="n">
-        <v>-191.9924951145691</v>
+        <v>-191.9385272046664</v>
       </c>
       <c r="H359" t="n">
         <v>10</v>
       </c>
       <c r="I359" t="n">
-        <v>4.985772473645511</v>
+        <v>58.9536823763126</v>
       </c>
       <c r="J359" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K359" t="n">
         <v>-191.9364953941601</v>
@@ -16351,28 +16351,28 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G360" t="n">
-        <v>-191.9504784195769</v>
+        <v>-191.9373741140392</v>
       </c>
       <c r="H360" t="n">
         <v>10</v>
       </c>
       <c r="I360" t="n">
-        <v>47.00246746588732</v>
+        <v>60.10677300346856</v>
       </c>
       <c r="J360" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K360" t="n">
         <v>-191.9364953941601</v>
@@ -16395,28 +16395,28 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E361" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G361" t="n">
-        <v>-191.3808576902583</v>
+        <v>-191.9924951145691</v>
       </c>
       <c r="H361" t="n">
         <v>10</v>
       </c>
       <c r="I361" t="n">
-        <v>616.6231967844453</v>
+        <v>4.985772473588668</v>
       </c>
       <c r="J361" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K361" t="n">
         <v>-191.9364953941601</v>
@@ -16447,20 +16447,20 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G362" t="n">
-        <v>-191.2741421909589</v>
+        <v>-191.9504784195769</v>
       </c>
       <c r="H362" t="n">
         <v>10</v>
       </c>
       <c r="I362" t="n">
-        <v>723.3386960838573</v>
+        <v>47.00246746583048</v>
       </c>
       <c r="J362" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K362" t="n">
         <v>-191.9364953941601</v>
@@ -16491,20 +16491,20 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G363" t="n">
-        <v>-191.939355331488</v>
+        <v>-191.3808576902583</v>
       </c>
       <c r="H363" t="n">
         <v>10</v>
       </c>
       <c r="I363" t="n">
-        <v>58.12555555476706</v>
+        <v>616.6231967843885</v>
       </c>
       <c r="J363" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K363" t="n">
         <v>-191.9364953941601</v>
@@ -16535,20 +16535,20 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G364" t="n">
-        <v>-191.0265516609469</v>
+        <v>-191.2741421909589</v>
       </c>
       <c r="H364" t="n">
         <v>10</v>
       </c>
       <c r="I364" t="n">
-        <v>970.9292260958762</v>
+        <v>723.3386960838004</v>
       </c>
       <c r="J364" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K364" t="n">
         <v>-191.9364953941601</v>
@@ -16579,20 +16579,20 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G365" t="n">
-        <v>-191.9920153168911</v>
+        <v>-191.939355331488</v>
       </c>
       <c r="H365" t="n">
         <v>10</v>
       </c>
       <c r="I365" t="n">
-        <v>5.465570151699239</v>
+        <v>58.12555555471022</v>
       </c>
       <c r="J365" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K365" t="n">
         <v>-191.9364953941601</v>
@@ -16615,28 +16615,28 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G366" t="n">
-        <v>-191.9523804301191</v>
+        <v>-191.0265516609469</v>
       </c>
       <c r="H366" t="n">
         <v>10</v>
       </c>
       <c r="I366" t="n">
-        <v>45.10045692362041</v>
+        <v>970.9292260958193</v>
       </c>
       <c r="J366" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K366" t="n">
         <v>-191.9364953941601</v>
@@ -16659,28 +16659,28 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E367" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G367" t="n">
-        <v>-191.938076270761</v>
+        <v>-191.9920153168911</v>
       </c>
       <c r="H367" t="n">
         <v>10</v>
       </c>
       <c r="I367" t="n">
-        <v>59.40461628179605</v>
+        <v>5.465570151642396</v>
       </c>
       <c r="J367" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K367" t="n">
         <v>-191.9364953941601</v>
@@ -16711,20 +16711,20 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G368" t="n">
-        <v>-191.1229725889993</v>
+        <v>-191.9523804301191</v>
       </c>
       <c r="H368" t="n">
         <v>10</v>
       </c>
       <c r="I368" t="n">
-        <v>874.5082980434233</v>
+        <v>45.10045692356357</v>
       </c>
       <c r="J368" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K368" t="n">
         <v>-191.9364953941601</v>
@@ -16755,20 +16755,20 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G369" t="n">
-        <v>-191.9543641774467</v>
+        <v>-191.938076270761</v>
       </c>
       <c r="H369" t="n">
         <v>10</v>
       </c>
       <c r="I369" t="n">
-        <v>43.1167095960916</v>
+        <v>59.40461628173921</v>
       </c>
       <c r="J369" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K369" t="n">
         <v>-191.9364953941601</v>
@@ -16799,20 +16799,20 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G370" t="n">
-        <v>-191.9399783754006</v>
+        <v>-191.1229725889993</v>
       </c>
       <c r="H370" t="n">
         <v>10</v>
       </c>
       <c r="I370" t="n">
-        <v>57.50251164212727</v>
+        <v>874.5082980433665</v>
       </c>
       <c r="J370" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K370" t="n">
         <v>-191.9364953941601</v>
@@ -16843,25 +16843,113 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G371" t="n">
-        <v>-191.9921928770854</v>
+        <v>-191.9543641774467</v>
       </c>
       <c r="H371" t="n">
         <v>10</v>
       </c>
       <c r="I371" t="n">
-        <v>5.288009957354234</v>
+        <v>43.11670959603475</v>
       </c>
       <c r="J371" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K371" t="n">
         <v>-191.9364953941601</v>
       </c>
       <c r="L371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="n">
+        <v>370</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>cc-pVDZ</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>prop-2-en-1-ol</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>LUCJ(L=5)</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>5</v>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="G372" t="n">
+        <v>-191.9399783754006</v>
+      </c>
+      <c r="H372" t="n">
+        <v>10</v>
+      </c>
+      <c r="I372" t="n">
+        <v>57.50251164207043</v>
+      </c>
+      <c r="J372" t="n">
+        <v>-191.9974808870427</v>
+      </c>
+      <c r="K372" t="n">
+        <v>-191.9364953941601</v>
+      </c>
+      <c r="L372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="n">
+        <v>371</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>cc-pVDZ</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>prop-2-en-1-ol</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>LUCJ(L=5)</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>5</v>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>zeroes</t>
+        </is>
+      </c>
+      <c r="G373" t="n">
+        <v>-191.9921928770854</v>
+      </c>
+      <c r="H373" t="n">
+        <v>10</v>
+      </c>
+      <c r="I373" t="n">
+        <v>5.28800995729739</v>
+      </c>
+      <c r="J373" t="n">
+        <v>-191.9974808870427</v>
+      </c>
+      <c r="K373" t="n">
+        <v>-191.9364953941601</v>
+      </c>
+      <c r="L373" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
+++ b/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L373"/>
+  <dimension ref="A1:L371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>-213.2458248396588</v>
+        <v>-213.16894626</v>
       </c>
       <c r="H2" t="n">
         <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>97.78897019253918</v>
+        <v>174.6675498512786</v>
       </c>
       <c r="J2" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K2" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L2" t="inlineStr"/>
     </row>
@@ -557,19 +557,19 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-213.2581877522052</v>
+        <v>-213.18162456</v>
       </c>
       <c r="H3" t="n">
         <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>85.42605764614564</v>
+        <v>161.9892498513025</v>
       </c>
       <c r="J3" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K3" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L3" t="inlineStr"/>
     </row>
@@ -601,19 +601,19 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>-213.2731707864143</v>
+        <v>-213.19520563</v>
       </c>
       <c r="H4" t="n">
         <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>70.44302343706477</v>
+        <v>148.4081798512875</v>
       </c>
       <c r="J4" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K4" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L4" t="inlineStr"/>
     </row>
@@ -645,19 +645,19 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-213.2847927447515</v>
+        <v>-213.25573934</v>
       </c>
       <c r="H5" t="n">
         <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>58.82106509977802</v>
+        <v>87.87446985130032</v>
       </c>
       <c r="J5" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K5" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L5" t="inlineStr"/>
     </row>
@@ -689,19 +689,19 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-212.5450274497299</v>
+        <v>-213.16037326</v>
       </c>
       <c r="H6" t="n">
         <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>798.5863601214191</v>
+        <v>183.2405498512912</v>
       </c>
       <c r="J6" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K6" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L6" t="inlineStr"/>
     </row>
@@ -733,19 +733,19 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>-213.3259163676897</v>
+        <v>-213.26472788</v>
       </c>
       <c r="H7" t="n">
         <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>17.69744216164781</v>
+        <v>78.88592985128184</v>
       </c>
       <c r="J7" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K7" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L7" t="inlineStr"/>
     </row>
@@ -777,19 +777,19 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>-213.1930346482877</v>
+        <v>-213.13533629</v>
       </c>
       <c r="H8" t="n">
         <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>150.5791615635985</v>
+        <v>208.2775198512934</v>
       </c>
       <c r="J8" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K8" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L8" t="inlineStr"/>
     </row>
@@ -821,19 +821,19 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>-213.1765359169949</v>
+        <v>-213.1398302</v>
       </c>
       <c r="H9" t="n">
         <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>167.0778928564118</v>
+        <v>203.7836098512855</v>
       </c>
       <c r="J9" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K9" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L9" t="inlineStr"/>
     </row>
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>-213.1608654841032</v>
+        <v>-213.13816999</v>
       </c>
       <c r="H10" t="n">
         <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>182.7483257481504</v>
+        <v>205.4438198512969</v>
       </c>
       <c r="J10" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K10" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L10" t="inlineStr"/>
     </row>
@@ -909,19 +909,19 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>-213.164330331744</v>
+        <v>-213.14702262</v>
       </c>
       <c r="H11" t="n">
         <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>179.2834781073225</v>
+        <v>196.59118985129</v>
       </c>
       <c r="J11" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K11" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L11" t="inlineStr"/>
     </row>
@@ -953,19 +953,19 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>-213.1860529781487</v>
+        <v>-213.16426166</v>
       </c>
       <c r="H12" t="n">
         <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>157.5608317025967</v>
+        <v>179.3521498512973</v>
       </c>
       <c r="J12" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K12" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L12" t="inlineStr"/>
     </row>
@@ -997,19 +997,19 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-213.3251699853507</v>
+        <v>-213.2959336</v>
       </c>
       <c r="H13" t="n">
         <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>18.44382450059356</v>
+        <v>47.68020985127919</v>
       </c>
       <c r="J13" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K13" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L13" t="inlineStr"/>
     </row>
@@ -1041,19 +1041,19 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>-213.1473074219446</v>
+        <v>-213.13068391</v>
       </c>
       <c r="H14" t="n">
         <v>9</v>
       </c>
       <c r="I14" t="n">
-        <v>196.3063879067022</v>
+        <v>212.9298998513036</v>
       </c>
       <c r="J14" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K14" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L14" t="inlineStr"/>
     </row>
@@ -1085,19 +1085,19 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-212.3006470589802</v>
+        <v>-213.13153293</v>
       </c>
       <c r="H15" t="n">
         <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>1042.96675087113</v>
+        <v>212.0808798512996</v>
       </c>
       <c r="J15" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K15" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L15" t="inlineStr"/>
     </row>
@@ -1129,19 +1129,19 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>-213.1729413635963</v>
+        <v>-213.14214654</v>
       </c>
       <c r="H16" t="n">
         <v>9</v>
       </c>
       <c r="I16" t="n">
-        <v>170.6724462550255</v>
+        <v>201.4672698512925</v>
       </c>
       <c r="J16" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K16" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L16" t="inlineStr"/>
     </row>
@@ -1173,19 +1173,19 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-212.5076523839172</v>
+        <v>-213.14090022</v>
       </c>
       <c r="H17" t="n">
         <v>9</v>
       </c>
       <c r="I17" t="n">
-        <v>835.9614259341015</v>
+        <v>202.7135898512995</v>
       </c>
       <c r="J17" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K17" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L17" t="inlineStr"/>
     </row>
@@ -1217,19 +1217,19 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>-213.163921045511</v>
+        <v>-213.13738237</v>
       </c>
       <c r="H18" t="n">
         <v>9</v>
       </c>
       <c r="I18" t="n">
-        <v>179.6927643403592</v>
+        <v>206.2314398512797</v>
       </c>
       <c r="J18" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K18" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L18" t="inlineStr"/>
     </row>
@@ -1261,19 +1261,19 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>-213.3251223273287</v>
+        <v>-213.30264625</v>
       </c>
       <c r="H19" t="n">
         <v>9</v>
       </c>
       <c r="I19" t="n">
-        <v>18.49148252262012</v>
+        <v>40.96755985128198</v>
       </c>
       <c r="J19" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K19" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L19" t="inlineStr"/>
     </row>
@@ -1305,19 +1305,19 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>-213.1659808008343</v>
+        <v>-213.1297768</v>
       </c>
       <c r="H20" t="n">
         <v>9</v>
       </c>
       <c r="I20" t="n">
-        <v>177.6330090170291</v>
+        <v>213.8370098512894</v>
       </c>
       <c r="J20" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K20" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L20" t="inlineStr"/>
     </row>
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-213.1230775042019</v>
+        <v>-213.14037764</v>
       </c>
       <c r="H21" t="n">
         <v>9</v>
       </c>
       <c r="I21" t="n">
-        <v>220.5363056493752</v>
+        <v>203.2361698512943</v>
       </c>
       <c r="J21" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K21" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L21" t="inlineStr"/>
     </row>
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>-213.1521865166994</v>
+        <v>-213.12566579</v>
       </c>
       <c r="H22" t="n">
         <v>9</v>
       </c>
       <c r="I22" t="n">
-        <v>191.4272931518894</v>
+        <v>217.948019851292</v>
       </c>
       <c r="J22" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K22" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L22" t="inlineStr"/>
     </row>
@@ -1437,19 +1437,19 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>-212.375646911964</v>
+        <v>-213.12707207</v>
       </c>
       <c r="H23" t="n">
         <v>9</v>
       </c>
       <c r="I23" t="n">
-        <v>967.9668978873224</v>
+        <v>216.5417398512943</v>
       </c>
       <c r="J23" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K23" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L23" t="inlineStr"/>
     </row>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-213.1868264392807</v>
+        <v>-213.13651013</v>
       </c>
       <c r="H24" t="n">
         <v>9</v>
       </c>
       <c r="I24" t="n">
-        <v>156.787370570612</v>
+        <v>207.1036798512864</v>
       </c>
       <c r="J24" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K24" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L24" t="inlineStr"/>
     </row>
@@ -1525,19 +1525,19 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-213.319221568662</v>
+        <v>-213.30023224</v>
       </c>
       <c r="H25" t="n">
         <v>9</v>
       </c>
       <c r="I25" t="n">
-        <v>24.39224118927541</v>
+        <v>43.38156985127739</v>
       </c>
       <c r="J25" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K25" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L25" t="inlineStr"/>
     </row>
@@ -1569,19 +1569,19 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-213.1913236081741</v>
+        <v>-213.13373741</v>
       </c>
       <c r="H26" t="n">
         <v>9</v>
       </c>
       <c r="I26" t="n">
-        <v>152.2902016772605</v>
+        <v>209.8763998512823</v>
       </c>
       <c r="J26" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K26" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L26" t="inlineStr"/>
     </row>
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-213.1453605980934</v>
+        <v>-213.17005373</v>
       </c>
       <c r="H27" t="n">
         <v>9</v>
       </c>
       <c r="I27" t="n">
-        <v>198.2532117579581</v>
+        <v>173.5600798512849</v>
       </c>
       <c r="J27" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K27" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L27" t="inlineStr"/>
     </row>
@@ -1657,19 +1657,19 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-213.1421481222368</v>
+        <v>-213.12791229</v>
       </c>
       <c r="H28" t="n">
         <v>9</v>
       </c>
       <c r="I28" t="n">
-        <v>201.4656876145295</v>
+        <v>215.7015198512795</v>
       </c>
       <c r="J28" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K28" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L28" t="inlineStr"/>
     </row>
@@ -1701,19 +1701,19 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>-213.1504876770753</v>
+        <v>-213.15712469</v>
       </c>
       <c r="H29" t="n">
         <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>193.1261327760581</v>
+        <v>186.4891198513021</v>
       </c>
       <c r="J29" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K29" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L29" t="inlineStr"/>
     </row>
@@ -1745,19 +1745,19 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>-213.2021082851187</v>
+        <v>-213.13400064</v>
       </c>
       <c r="H30" t="n">
         <v>9</v>
       </c>
       <c r="I30" t="n">
-        <v>141.5055247326222</v>
+        <v>209.6131698512806</v>
       </c>
       <c r="J30" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K30" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L30" t="inlineStr"/>
     </row>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>-213.3245633351582</v>
+        <v>-213.27197969</v>
       </c>
       <c r="H31" t="n">
         <v>9</v>
       </c>
       <c r="I31" t="n">
-        <v>19.05047469307419</v>
+        <v>71.63411985129642</v>
       </c>
       <c r="J31" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K31" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L31" t="inlineStr"/>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>aug-cc-pVDZ</t>
+          <t>cc-pVDZ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1821,11 +1821,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1833,19 +1833,19 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>-214.7028624898805</v>
+        <v>-215.95799557</v>
       </c>
       <c r="H32" t="n">
         <v>9</v>
       </c>
       <c r="I32" t="n">
-        <v>1247.549051652413</v>
+        <v>40.02308769958063</v>
       </c>
       <c r="J32" t="n">
-        <v>-215.950411541533</v>
+        <v>-215.9980186576996</v>
       </c>
       <c r="K32" t="n">
-        <v>-215.9496895929251</v>
+        <v>-215.9369612176939</v>
       </c>
       <c r="L32" t="inlineStr"/>
     </row>
@@ -1873,17 +1873,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>-215.9891124545286</v>
+        <v>-215.9495007</v>
       </c>
       <c r="H33" t="n">
         <v>9</v>
       </c>
       <c r="I33" t="n">
-        <v>8.906203170994331</v>
+        <v>48.51795769960177</v>
       </c>
       <c r="J33" t="n">
         <v>-215.9980186576996</v>
@@ -1917,17 +1917,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>-215.9831276131487</v>
+        <v>-215.94367574</v>
       </c>
       <c r="H34" t="n">
         <v>9</v>
       </c>
       <c r="I34" t="n">
-        <v>14.89104455086476</v>
+        <v>54.34291769958577</v>
       </c>
       <c r="J34" t="n">
         <v>-215.9980186576996</v>
@@ -1961,17 +1961,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>-215.9727292634677</v>
+        <v>-215.97123346</v>
       </c>
       <c r="H35" t="n">
         <v>9</v>
       </c>
       <c r="I35" t="n">
-        <v>25.289394231919</v>
+        <v>26.78519769958143</v>
       </c>
       <c r="J35" t="n">
         <v>-215.9980186576996</v>
@@ -2005,17 +2005,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>-215.9869314825332</v>
+        <v>-215.93868767</v>
       </c>
       <c r="H36" t="n">
         <v>9</v>
       </c>
       <c r="I36" t="n">
-        <v>11.08717516640922</v>
+        <v>59.33098769958178</v>
       </c>
       <c r="J36" t="n">
         <v>-215.9980186576996</v>
@@ -2049,17 +2049,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>-215.9447736101474</v>
+        <v>-215.99060891</v>
       </c>
       <c r="H37" t="n">
         <v>9</v>
       </c>
       <c r="I37" t="n">
-        <v>53.24504755222392</v>
+        <v>7.409747699597347</v>
       </c>
       <c r="J37" t="n">
         <v>-215.9980186576996</v>
@@ -2085,25 +2085,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>-215.9920418991637</v>
+        <v>-215.95314059</v>
       </c>
       <c r="H38" t="n">
         <v>9</v>
       </c>
       <c r="I38" t="n">
-        <v>5.976758535865656</v>
+        <v>44.87806769958524</v>
       </c>
       <c r="J38" t="n">
         <v>-215.9980186576996</v>
@@ -2137,17 +2137,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>-215.9473070577784</v>
+        <v>-215.94307715</v>
       </c>
       <c r="H39" t="n">
         <v>9</v>
       </c>
       <c r="I39" t="n">
-        <v>50.71159992118623</v>
+        <v>54.9415076995956</v>
       </c>
       <c r="J39" t="n">
         <v>-215.9980186576996</v>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>-215.9466880640767</v>
+        <v>-215.94465647</v>
       </c>
       <c r="H40" t="n">
         <v>9</v>
       </c>
       <c r="I40" t="n">
-        <v>51.33059362290737</v>
+        <v>53.36218769957668</v>
       </c>
       <c r="J40" t="n">
         <v>-215.9980186576996</v>
@@ -2225,17 +2225,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>-215.9668614570415</v>
+        <v>-215.95999558</v>
       </c>
       <c r="H41" t="n">
         <v>9</v>
       </c>
       <c r="I41" t="n">
-        <v>31.15720065804339</v>
+        <v>38.02307769959157</v>
       </c>
       <c r="J41" t="n">
         <v>-215.9980186576996</v>
@@ -2269,17 +2269,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>-215.9581462662541</v>
+        <v>-215.93916488</v>
       </c>
       <c r="H42" t="n">
         <v>9</v>
       </c>
       <c r="I42" t="n">
-        <v>39.87239144552746</v>
+        <v>58.85377769959632</v>
       </c>
       <c r="J42" t="n">
         <v>-215.9980186576996</v>
@@ -2313,17 +2313,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>-215.9427889663834</v>
+        <v>-215.98786327</v>
       </c>
       <c r="H43" t="n">
         <v>9</v>
       </c>
       <c r="I43" t="n">
-        <v>55.2296913162138</v>
+        <v>10.1553876995979</v>
       </c>
       <c r="J43" t="n">
         <v>-215.9980186576996</v>
@@ -2349,25 +2349,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>-215.9922509360108</v>
+        <v>-215.94332876</v>
       </c>
       <c r="H44" t="n">
         <v>9</v>
       </c>
       <c r="I44" t="n">
-        <v>5.767721688783922</v>
+        <v>54.68989769957489</v>
       </c>
       <c r="J44" t="n">
         <v>-215.9980186576996</v>
@@ -2401,17 +2401,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>-215.9409816472209</v>
+        <v>-215.94193614</v>
       </c>
       <c r="H45" t="n">
         <v>9</v>
       </c>
       <c r="I45" t="n">
-        <v>57.03701047869458</v>
+        <v>56.08251769959338</v>
       </c>
       <c r="J45" t="n">
         <v>-215.9980186576996</v>
@@ -2445,17 +2445,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>-215.9593459088263</v>
+        <v>-215.95664195</v>
       </c>
       <c r="H46" t="n">
         <v>9</v>
       </c>
       <c r="I46" t="n">
-        <v>38.67274887332428</v>
+        <v>41.3767076995839</v>
       </c>
       <c r="J46" t="n">
         <v>-215.9980186576996</v>
@@ -2489,17 +2489,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>-215.9557348307425</v>
+        <v>-215.93930513</v>
       </c>
       <c r="H47" t="n">
         <v>9</v>
       </c>
       <c r="I47" t="n">
-        <v>42.2838269571173</v>
+        <v>58.71352769958094</v>
       </c>
       <c r="J47" t="n">
         <v>-215.9980186576996</v>
@@ -2533,17 +2533,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>-215.3953870743604</v>
+        <v>-215.95579101</v>
       </c>
       <c r="H48" t="n">
         <v>9</v>
       </c>
       <c r="I48" t="n">
-        <v>602.6315833392175</v>
+        <v>42.22764769957621</v>
       </c>
       <c r="J48" t="n">
         <v>-215.9980186576996</v>
@@ -2577,17 +2577,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>-215.9592185359257</v>
+        <v>-215.98863974</v>
       </c>
       <c r="H49" t="n">
         <v>9</v>
       </c>
       <c r="I49" t="n">
-        <v>38.80012177384629</v>
+        <v>9.378917699592648</v>
       </c>
       <c r="J49" t="n">
         <v>-215.9980186576996</v>
@@ -2613,25 +2613,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>-215.9927426319096</v>
+        <v>-215.93801958</v>
       </c>
       <c r="H50" t="n">
         <v>9</v>
       </c>
       <c r="I50" t="n">
-        <v>5.27602579003883</v>
+        <v>59.99907769958668</v>
       </c>
       <c r="J50" t="n">
         <v>-215.9980186576996</v>
@@ -2665,17 +2665,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>-215.957734930636</v>
+        <v>-215.94174103</v>
       </c>
       <c r="H51" t="n">
         <v>9</v>
       </c>
       <c r="I51" t="n">
-        <v>40.28372706355299</v>
+        <v>56.27762769958622</v>
       </c>
       <c r="J51" t="n">
         <v>-215.9980186576996</v>
@@ -2709,17 +2709,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>-215.956487242794</v>
+        <v>-215.94457924</v>
       </c>
       <c r="H52" t="n">
         <v>9</v>
       </c>
       <c r="I52" t="n">
-        <v>41.53141490562007</v>
+        <v>53.43941769959315</v>
       </c>
       <c r="J52" t="n">
         <v>-215.9980186576996</v>
@@ -2753,17 +2753,17 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>-215.961898768812</v>
+        <v>-215.94177881</v>
       </c>
       <c r="H53" t="n">
         <v>9</v>
       </c>
       <c r="I53" t="n">
-        <v>36.11988888755491</v>
+        <v>56.23984769960089</v>
       </c>
       <c r="J53" t="n">
         <v>-215.9980186576996</v>
@@ -2797,17 +2797,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>-215.962099538092</v>
+        <v>-215.95561711</v>
       </c>
       <c r="H54" t="n">
         <v>9</v>
       </c>
       <c r="I54" t="n">
-        <v>35.9191196075983</v>
+        <v>42.40154769959759</v>
       </c>
       <c r="J54" t="n">
         <v>-215.9980186576996</v>
@@ -2841,17 +2841,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>-215.960672338181</v>
+        <v>-215.98929442</v>
       </c>
       <c r="H55" t="n">
         <v>9</v>
       </c>
       <c r="I55" t="n">
-        <v>37.34631951854794</v>
+        <v>8.72423769959596</v>
       </c>
       <c r="J55" t="n">
         <v>-215.9980186576996</v>
@@ -2877,25 +2877,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>-215.9920401685626</v>
+        <v>-215.95673708</v>
       </c>
       <c r="H56" t="n">
         <v>9</v>
       </c>
       <c r="I56" t="n">
-        <v>5.978489136992948</v>
+        <v>41.28157769957852</v>
       </c>
       <c r="J56" t="n">
         <v>-215.9980186576996</v>
@@ -2929,17 +2929,17 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>-215.9561682360744</v>
+        <v>-215.94007471</v>
       </c>
       <c r="H57" t="n">
         <v>9</v>
       </c>
       <c r="I57" t="n">
-        <v>41.85042162518471</v>
+        <v>57.94394769958444</v>
       </c>
       <c r="J57" t="n">
         <v>-215.9980186576996</v>
@@ -2973,17 +2973,17 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>-215.9585111292126</v>
+        <v>-215.93755207</v>
       </c>
       <c r="H58" t="n">
         <v>9</v>
       </c>
       <c r="I58" t="n">
-        <v>39.50752848700745</v>
+        <v>60.46658769957958</v>
       </c>
       <c r="J58" t="n">
         <v>-215.9980186576996</v>
@@ -3017,17 +3017,17 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>-215.9589175726923</v>
+        <v>-215.94360394</v>
       </c>
       <c r="H59" t="n">
         <v>9</v>
       </c>
       <c r="I59" t="n">
-        <v>39.10108500727461</v>
+        <v>54.41471769958639</v>
       </c>
       <c r="J59" t="n">
         <v>-215.9980186576996</v>
@@ -3061,17 +3061,17 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>-215.9621729361387</v>
+        <v>-215.94067522</v>
       </c>
       <c r="H60" t="n">
         <v>9</v>
       </c>
       <c r="I60" t="n">
-        <v>35.84572156088939</v>
+        <v>57.34343769958627</v>
       </c>
       <c r="J60" t="n">
         <v>-215.9980186576996</v>
@@ -3105,17 +3105,17 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>-215.9462074712169</v>
+        <v>-215.98668023</v>
       </c>
       <c r="H61" t="n">
         <v>9</v>
       </c>
       <c r="I61" t="n">
-        <v>51.81118648269489</v>
+        <v>11.3384276995987</v>
       </c>
       <c r="J61" t="n">
         <v>-215.9980186576996</v>
@@ -3131,41 +3131,41 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>cc-pVDZ</t>
+          <t>STO-3G</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>(Z)-1-fluoroprop-1-ene</t>
+          <t>but-1-yne</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>-215.9924367471406</v>
+        <v>-153.07525576</v>
       </c>
       <c r="H62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I62" t="n">
-        <v>5.58191055895918</v>
+        <v>232.8457421015742</v>
       </c>
       <c r="J62" t="n">
-        <v>-215.9980186576996</v>
+        <v>-153.3081015021016</v>
       </c>
       <c r="K62" t="n">
-        <v>-215.9369612176939</v>
+        <v>-153.0248949590477</v>
       </c>
       <c r="L62" t="inlineStr"/>
     </row>
@@ -3193,17 +3193,17 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>-153.1770157729154</v>
+        <v>-153.15408424</v>
       </c>
       <c r="H63" t="n">
         <v>10</v>
       </c>
       <c r="I63" t="n">
-        <v>131.085729186168</v>
+        <v>154.0172621015756</v>
       </c>
       <c r="J63" t="n">
         <v>-153.3081015021016</v>
@@ -3237,17 +3237,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>-153.1714470440083</v>
+        <v>-153.0832784</v>
       </c>
       <c r="H64" t="n">
         <v>10</v>
       </c>
       <c r="I64" t="n">
-        <v>136.6544580932896</v>
+        <v>224.823102101567</v>
       </c>
       <c r="J64" t="n">
         <v>-153.3081015021016</v>
@@ -3281,17 +3281,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>-153.1024348637226</v>
+        <v>-153.06506995</v>
       </c>
       <c r="H65" t="n">
         <v>10</v>
       </c>
       <c r="I65" t="n">
-        <v>205.6666383790002</v>
+        <v>243.03155210157</v>
       </c>
       <c r="J65" t="n">
         <v>-153.3081015021016</v>
@@ -3325,17 +3325,17 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>-153.2074197081715</v>
+        <v>-153.02495176</v>
       </c>
       <c r="H66" t="n">
         <v>10</v>
       </c>
       <c r="I66" t="n">
-        <v>100.6817939300504</v>
+        <v>283.1497421015854</v>
       </c>
       <c r="J66" t="n">
         <v>-153.3081015021016</v>
@@ -3369,17 +3369,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>-153.0269021742142</v>
+        <v>-153.24728926</v>
       </c>
       <c r="H67" t="n">
         <v>10</v>
       </c>
       <c r="I67" t="n">
-        <v>281.1993278873501</v>
+        <v>60.81224210157643</v>
       </c>
       <c r="J67" t="n">
         <v>-153.3081015021016</v>
@@ -3405,25 +3405,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>-153.2779418378781</v>
+        <v>-153.0292827878955</v>
       </c>
       <c r="H68" t="n">
         <v>10</v>
       </c>
       <c r="I68" t="n">
-        <v>30.15966422344718</v>
+        <v>278.8187142061247</v>
       </c>
       <c r="J68" t="n">
         <v>-153.3081015021016</v>
@@ -3457,17 +3457,17 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>-153.0292827878955</v>
+        <v>-152.2319134028214</v>
       </c>
       <c r="H69" t="n">
         <v>10</v>
       </c>
       <c r="I69" t="n">
-        <v>278.8187142061247</v>
+        <v>1076.188099280159</v>
       </c>
       <c r="J69" t="n">
         <v>-153.3081015021016</v>
@@ -3501,17 +3501,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>-152.2319134028214</v>
+        <v>-153.0535791993887</v>
       </c>
       <c r="H70" t="n">
         <v>10</v>
       </c>
       <c r="I70" t="n">
-        <v>1076.188099280159</v>
+        <v>254.5223027128714</v>
       </c>
       <c r="J70" t="n">
         <v>-153.3081015021016</v>
@@ -3545,17 +3545,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>-153.0535791993887</v>
+        <v>-152.2746392024372</v>
       </c>
       <c r="H71" t="n">
         <v>10</v>
       </c>
       <c r="I71" t="n">
-        <v>254.5223027128714</v>
+        <v>1033.462299664336</v>
       </c>
       <c r="J71" t="n">
         <v>-153.3081015021016</v>
@@ -3589,17 +3589,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>-152.2746392024372</v>
+        <v>-152.3571751854059</v>
       </c>
       <c r="H72" t="n">
         <v>10</v>
       </c>
       <c r="I72" t="n">
-        <v>1033.462299664336</v>
+        <v>950.926316695643</v>
       </c>
       <c r="J72" t="n">
         <v>-153.3081015021016</v>
@@ -3633,17 +3633,17 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>-152.3571751854059</v>
+        <v>-153.2719284190653</v>
       </c>
       <c r="H73" t="n">
         <v>10</v>
       </c>
       <c r="I73" t="n">
-        <v>950.926316695643</v>
+        <v>36.17308303626032</v>
       </c>
       <c r="J73" t="n">
         <v>-153.3081015021016</v>
@@ -3669,25 +3669,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>-153.2719284190653</v>
+        <v>-152.4366520821549</v>
       </c>
       <c r="H74" t="n">
         <v>10</v>
       </c>
       <c r="I74" t="n">
-        <v>36.17308303626032</v>
+        <v>871.449419946714</v>
       </c>
       <c r="J74" t="n">
         <v>-153.3081015021016</v>
@@ -3721,17 +3721,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>-152.4366520821549</v>
+        <v>-152.4900093831465</v>
       </c>
       <c r="H75" t="n">
         <v>10</v>
       </c>
       <c r="I75" t="n">
-        <v>871.449419946714</v>
+        <v>818.0921189550645</v>
       </c>
       <c r="J75" t="n">
         <v>-153.3081015021016</v>
@@ -3765,17 +3765,17 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>-152.4900093831465</v>
+        <v>-151.3656703749002</v>
       </c>
       <c r="H76" t="n">
         <v>10</v>
       </c>
       <c r="I76" t="n">
-        <v>818.0921189550645</v>
+        <v>1942.431127201417</v>
       </c>
       <c r="J76" t="n">
         <v>-153.3081015021016</v>
@@ -3809,17 +3809,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>-151.3656703749002</v>
+        <v>-151.9685602515355</v>
       </c>
       <c r="H77" t="n">
         <v>10</v>
       </c>
       <c r="I77" t="n">
-        <v>1942.431127201417</v>
+        <v>1339.541250566072</v>
       </c>
       <c r="J77" t="n">
         <v>-153.3081015021016</v>
@@ -3853,17 +3853,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>-151.9685602515355</v>
+        <v>-151.8561303348849</v>
       </c>
       <c r="H78" t="n">
         <v>10</v>
       </c>
       <c r="I78" t="n">
-        <v>1339.541250566072</v>
+        <v>1451.971167216641</v>
       </c>
       <c r="J78" t="n">
         <v>-153.3081015021016</v>
@@ -3897,17 +3897,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>-151.8561303348849</v>
+        <v>-153.2836444531916</v>
       </c>
       <c r="H79" t="n">
         <v>10</v>
       </c>
       <c r="I79" t="n">
-        <v>1451.971167216641</v>
+        <v>24.45704890999423</v>
       </c>
       <c r="J79" t="n">
         <v>-153.3081015021016</v>
@@ -3933,25 +3933,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>-153.2836444531916</v>
+        <v>-151.9734313375461</v>
       </c>
       <c r="H80" t="n">
         <v>10</v>
       </c>
       <c r="I80" t="n">
-        <v>24.45704890999423</v>
+        <v>1334.670164555462</v>
       </c>
       <c r="J80" t="n">
         <v>-153.3081015021016</v>
@@ -3985,17 +3985,17 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>-151.9734313375461</v>
+        <v>-152.3447986549187</v>
       </c>
       <c r="H81" t="n">
         <v>10</v>
       </c>
       <c r="I81" t="n">
-        <v>1334.670164555462</v>
+        <v>963.3028471828311</v>
       </c>
       <c r="J81" t="n">
         <v>-153.3081015021016</v>
@@ -4029,17 +4029,17 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>-152.3447986549187</v>
+        <v>-152.3444799909352</v>
       </c>
       <c r="H82" t="n">
         <v>10</v>
       </c>
       <c r="I82" t="n">
-        <v>963.3028471828311</v>
+        <v>963.621511166366</v>
       </c>
       <c r="J82" t="n">
         <v>-153.3081015021016</v>
@@ -4073,17 +4073,17 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>-152.3444799909352</v>
+        <v>-152.2355941557564</v>
       </c>
       <c r="H83" t="n">
         <v>10</v>
       </c>
       <c r="I83" t="n">
-        <v>963.621511166366</v>
+        <v>1072.507346345162</v>
       </c>
       <c r="J83" t="n">
         <v>-153.3081015021016</v>
@@ -4117,17 +4117,17 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>-152.2355941557564</v>
+        <v>-153.0393110872162</v>
       </c>
       <c r="H84" t="n">
         <v>10</v>
       </c>
       <c r="I84" t="n">
-        <v>1072.507346345162</v>
+        <v>268.7904148854159</v>
       </c>
       <c r="J84" t="n">
         <v>-153.3081015021016</v>
@@ -4161,17 +4161,17 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>-153.0393110872162</v>
+        <v>-153.2804882591629</v>
       </c>
       <c r="H85" t="n">
         <v>10</v>
       </c>
       <c r="I85" t="n">
-        <v>268.7904148854159</v>
+        <v>27.61324293868483</v>
       </c>
       <c r="J85" t="n">
         <v>-153.3081015021016</v>
@@ -4197,25 +4197,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>-153.2804882591629</v>
+        <v>-153.0672036349131</v>
       </c>
       <c r="H86" t="n">
         <v>10</v>
       </c>
       <c r="I86" t="n">
-        <v>27.61324293868483</v>
+        <v>240.897867188437</v>
       </c>
       <c r="J86" t="n">
         <v>-153.3081015021016</v>
@@ -4249,17 +4249,17 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>-153.0672036349131</v>
+        <v>-152.2377072322053</v>
       </c>
       <c r="H87" t="n">
         <v>10</v>
       </c>
       <c r="I87" t="n">
-        <v>240.897867188437</v>
+        <v>1070.394269896326</v>
       </c>
       <c r="J87" t="n">
         <v>-153.3081015021016</v>
@@ -4293,17 +4293,17 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>-152.2377072322053</v>
+        <v>-151.9990808925929</v>
       </c>
       <c r="H88" t="n">
         <v>10</v>
       </c>
       <c r="I88" t="n">
-        <v>1070.394269896326</v>
+        <v>1309.02060950865</v>
       </c>
       <c r="J88" t="n">
         <v>-153.3081015021016</v>
@@ -4337,17 +4337,17 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>-151.9990808925929</v>
+        <v>-153.049883388874</v>
       </c>
       <c r="H89" t="n">
         <v>10</v>
       </c>
       <c r="I89" t="n">
-        <v>1309.02060950865</v>
+        <v>258.2181132275991</v>
       </c>
       <c r="J89" t="n">
         <v>-153.3081015021016</v>
@@ -4381,17 +4381,17 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>-153.049883388874</v>
+        <v>-152.359147115458</v>
       </c>
       <c r="H90" t="n">
         <v>10</v>
       </c>
       <c r="I90" t="n">
-        <v>258.2181132275991</v>
+        <v>948.9543866436065</v>
       </c>
       <c r="J90" t="n">
         <v>-153.3081015021016</v>
@@ -4425,17 +4425,17 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>-152.359147115458</v>
+        <v>-153.2811026101473</v>
       </c>
       <c r="H91" t="n">
         <v>10</v>
       </c>
       <c r="I91" t="n">
-        <v>948.9543866436065</v>
+        <v>26.9988919542925</v>
       </c>
       <c r="J91" t="n">
         <v>-153.3081015021016</v>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>STO-3G</t>
+          <t>aug-cc-pVDZ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4461,31 +4461,31 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>-153.2811026101473</v>
+        <v>-153.7883019965702</v>
       </c>
       <c r="H92" t="n">
         <v>10</v>
       </c>
       <c r="I92" t="n">
-        <v>26.9988919542925</v>
+        <v>1129.640479181148</v>
       </c>
       <c r="J92" t="n">
-        <v>-153.3081015021016</v>
+        <v>-154.9179424757513</v>
       </c>
       <c r="K92" t="n">
-        <v>-153.0248949590477</v>
+        <v>-154.9167852198248</v>
       </c>
       <c r="L92" t="inlineStr"/>
     </row>
@@ -4505,11 +4505,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -4517,13 +4517,13 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>-152.6307807091584</v>
+        <v>-154.1403536040909</v>
       </c>
       <c r="H93" t="n">
         <v>10</v>
       </c>
       <c r="I93" t="n">
-        <v>2287.161766592931</v>
+        <v>777.5888716604413</v>
       </c>
       <c r="J93" t="n">
         <v>-154.9179424757513</v>
@@ -4549,25 +4549,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>-153.7883019965702</v>
+        <v>-153.8484792747023</v>
       </c>
       <c r="H94" t="n">
         <v>10</v>
       </c>
       <c r="I94" t="n">
-        <v>1129.640479181148</v>
+        <v>1069.463201049018</v>
       </c>
       <c r="J94" t="n">
         <v>-154.9179424757513</v>
@@ -4593,25 +4593,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>-154.1403536040909</v>
+        <v>-154.0723245882149</v>
       </c>
       <c r="H95" t="n">
         <v>10</v>
       </c>
       <c r="I95" t="n">
-        <v>777.5888716604413</v>
+        <v>845.6178875363776</v>
       </c>
       <c r="J95" t="n">
         <v>-154.9179424757513</v>
@@ -4645,17 +4645,17 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>-153.8484792747023</v>
+        <v>-154.1052151121582</v>
       </c>
       <c r="H96" t="n">
         <v>10</v>
       </c>
       <c r="I96" t="n">
-        <v>1069.463201049018</v>
+        <v>812.727363593126</v>
       </c>
       <c r="J96" t="n">
         <v>-154.9179424757513</v>
@@ -4681,25 +4681,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>-154.0723245882149</v>
+        <v>-153.9810908348413</v>
       </c>
       <c r="H97" t="n">
         <v>10</v>
       </c>
       <c r="I97" t="n">
-        <v>845.6178875363776</v>
+        <v>936.8516409100494</v>
       </c>
       <c r="J97" t="n">
         <v>-154.9179424757513</v>
@@ -4725,11 +4725,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -4737,13 +4737,13 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>-154.1052151121582</v>
+        <v>-154.0936799418998</v>
       </c>
       <c r="H98" t="n">
         <v>10</v>
       </c>
       <c r="I98" t="n">
-        <v>812.727363593126</v>
+        <v>824.2625338515381</v>
       </c>
       <c r="J98" t="n">
         <v>-154.9179424757513</v>
@@ -4769,25 +4769,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>-153.9810908348413</v>
+        <v>-152.5516160270816</v>
       </c>
       <c r="H99" t="n">
         <v>10</v>
       </c>
       <c r="I99" t="n">
-        <v>936.8516409100494</v>
+        <v>2366.326448669724</v>
       </c>
       <c r="J99" t="n">
         <v>-154.9179424757513</v>
@@ -4813,25 +4813,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>-154.0936799418998</v>
+        <v>-154.0822000866224</v>
       </c>
       <c r="H100" t="n">
         <v>10</v>
       </c>
       <c r="I100" t="n">
-        <v>824.2625338515381</v>
+        <v>835.7423891288818</v>
       </c>
       <c r="J100" t="n">
         <v>-154.9179424757513</v>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>aug-cc-pVDZ</t>
+          <t>cc-pVDZ</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4857,31 +4857,31 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>-152.5516160270816</v>
+        <v>-154.91813296</v>
       </c>
       <c r="H101" t="n">
         <v>10</v>
       </c>
       <c r="I101" t="n">
-        <v>2366.326448669724</v>
+        <v>82.31540423943784</v>
       </c>
       <c r="J101" t="n">
-        <v>-154.9179424757513</v>
+        <v>-155.0004483642394</v>
       </c>
       <c r="K101" t="n">
-        <v>-154.9167852198248</v>
+        <v>-154.9113882737664</v>
       </c>
       <c r="L101" t="inlineStr"/>
     </row>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>aug-cc-pVDZ</t>
+          <t>cc-pVDZ</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4901,31 +4901,31 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>-154.0822000866224</v>
+        <v>-154.9371994097458</v>
       </c>
       <c r="H102" t="n">
         <v>10</v>
       </c>
       <c r="I102" t="n">
-        <v>835.7423891288818</v>
+        <v>63.24895449364476</v>
       </c>
       <c r="J102" t="n">
-        <v>-154.9179424757513</v>
+        <v>-155.0004483642394</v>
       </c>
       <c r="K102" t="n">
-        <v>-154.9167852198248</v>
+        <v>-154.9113882737664</v>
       </c>
       <c r="L102" t="inlineStr"/>
     </row>
@@ -4953,17 +4953,17 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>-154.9604387305679</v>
+        <v>-154.9476789329767</v>
       </c>
       <c r="H103" t="n">
         <v>10</v>
       </c>
       <c r="I103" t="n">
-        <v>40.00963367150234</v>
+        <v>52.76943126278866</v>
       </c>
       <c r="J103" t="n">
         <v>-155.0004483642394</v>
@@ -4997,17 +4997,17 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>-154.9371994097458</v>
+        <v>-154.9746179553749</v>
       </c>
       <c r="H104" t="n">
         <v>10</v>
       </c>
       <c r="I104" t="n">
-        <v>63.24895449364476</v>
+        <v>25.83040886452181</v>
       </c>
       <c r="J104" t="n">
         <v>-155.0004483642394</v>
@@ -5041,17 +5041,17 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>-154.9476789329767</v>
+        <v>-154.1756441030229</v>
       </c>
       <c r="H105" t="n">
         <v>10</v>
       </c>
       <c r="I105" t="n">
-        <v>52.76943126278866</v>
+        <v>824.8042612165136</v>
       </c>
       <c r="J105" t="n">
         <v>-155.0004483642394</v>
@@ -5085,17 +5085,17 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>-154.9746179553749</v>
+        <v>-154.9924580310285</v>
       </c>
       <c r="H106" t="n">
         <v>10</v>
       </c>
       <c r="I106" t="n">
-        <v>25.83040886452181</v>
+        <v>7.99033321089837</v>
       </c>
       <c r="J106" t="n">
         <v>-155.0004483642394</v>
@@ -5121,25 +5121,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>-154.1756441030229</v>
+        <v>-154.9168910292446</v>
       </c>
       <c r="H107" t="n">
         <v>10</v>
       </c>
       <c r="I107" t="n">
-        <v>824.8042612165136</v>
+        <v>83.55733499485041</v>
       </c>
       <c r="J107" t="n">
         <v>-155.0004483642394</v>
@@ -5165,25 +5165,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>-154.9924580310285</v>
+        <v>-154.9126678451285</v>
       </c>
       <c r="H108" t="n">
         <v>10</v>
       </c>
       <c r="I108" t="n">
-        <v>7.99033321089837</v>
+        <v>87.78051911093598</v>
       </c>
       <c r="J108" t="n">
         <v>-155.0004483642394</v>
@@ -5217,17 +5217,17 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>-154.9168910292446</v>
+        <v>-154.3087374891909</v>
       </c>
       <c r="H109" t="n">
         <v>10</v>
       </c>
       <c r="I109" t="n">
-        <v>83.55733499485041</v>
+        <v>691.7108750485568</v>
       </c>
       <c r="J109" t="n">
         <v>-155.0004483642394</v>
@@ -5261,17 +5261,17 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>-154.9126678451285</v>
+        <v>-154.1265950108659</v>
       </c>
       <c r="H110" t="n">
         <v>10</v>
       </c>
       <c r="I110" t="n">
-        <v>87.78051911093598</v>
+        <v>873.8533533735904</v>
       </c>
       <c r="J110" t="n">
         <v>-155.0004483642394</v>
@@ -5305,17 +5305,17 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>-154.3087374891909</v>
+        <v>-154.2105318303757</v>
       </c>
       <c r="H111" t="n">
         <v>10</v>
       </c>
       <c r="I111" t="n">
-        <v>691.7108750485568</v>
+        <v>789.9165338637886</v>
       </c>
       <c r="J111" t="n">
         <v>-155.0004483642394</v>
@@ -5349,17 +5349,17 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>-154.1265950108659</v>
+        <v>-154.9909733297587</v>
       </c>
       <c r="H112" t="n">
         <v>10</v>
       </c>
       <c r="I112" t="n">
-        <v>873.8533533735904</v>
+        <v>9.475034480715294</v>
       </c>
       <c r="J112" t="n">
         <v>-155.0004483642394</v>
@@ -5385,25 +5385,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>-154.2105318303757</v>
+        <v>-154.9236801062594</v>
       </c>
       <c r="H113" t="n">
         <v>10</v>
       </c>
       <c r="I113" t="n">
-        <v>789.9165338637886</v>
+        <v>76.76825798000664</v>
       </c>
       <c r="J113" t="n">
         <v>-155.0004483642394</v>
@@ -5429,25 +5429,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>-154.9909733297587</v>
+        <v>-154.2608204602884</v>
       </c>
       <c r="H114" t="n">
         <v>10</v>
       </c>
       <c r="I114" t="n">
-        <v>9.475034480715294</v>
+        <v>739.6279039510887</v>
       </c>
       <c r="J114" t="n">
         <v>-155.0004483642394</v>
@@ -5481,17 +5481,17 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>-154.9236801062594</v>
+        <v>-154.9180734742404</v>
       </c>
       <c r="H115" t="n">
         <v>10</v>
       </c>
       <c r="I115" t="n">
-        <v>76.76825798000664</v>
+        <v>82.37488999907328</v>
       </c>
       <c r="J115" t="n">
         <v>-155.0004483642394</v>
@@ -5525,17 +5525,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>-154.2608204602884</v>
+        <v>-154.1275624523181</v>
       </c>
       <c r="H116" t="n">
         <v>10</v>
       </c>
       <c r="I116" t="n">
-        <v>739.6279039510887</v>
+        <v>872.8859119213439</v>
       </c>
       <c r="J116" t="n">
         <v>-155.0004483642394</v>
@@ -5569,17 +5569,17 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>-154.9180734742404</v>
+        <v>-154.9165278927681</v>
       </c>
       <c r="H117" t="n">
         <v>10</v>
       </c>
       <c r="I117" t="n">
-        <v>82.37488999907328</v>
+        <v>83.92047147134463</v>
       </c>
       <c r="J117" t="n">
         <v>-155.0004483642394</v>
@@ -5613,17 +5613,17 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>-154.1275624523181</v>
+        <v>-154.9895590821297</v>
       </c>
       <c r="H118" t="n">
         <v>10</v>
       </c>
       <c r="I118" t="n">
-        <v>872.8859119213439</v>
+        <v>10.88928210970153</v>
       </c>
       <c r="J118" t="n">
         <v>-155.0004483642394</v>
@@ -5649,25 +5649,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>-154.9165278927681</v>
+        <v>-154.9123634039216</v>
       </c>
       <c r="H119" t="n">
         <v>10</v>
       </c>
       <c r="I119" t="n">
-        <v>83.92047147134463</v>
+        <v>88.08496031787172</v>
       </c>
       <c r="J119" t="n">
         <v>-155.0004483642394</v>
@@ -5693,25 +5693,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>-154.9895590821297</v>
+        <v>-154.9139583139124</v>
       </c>
       <c r="H120" t="n">
         <v>10</v>
       </c>
       <c r="I120" t="n">
-        <v>10.88928210970153</v>
+        <v>86.49005032708601</v>
       </c>
       <c r="J120" t="n">
         <v>-155.0004483642394</v>
@@ -5745,17 +5745,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>-154.9123634039216</v>
+        <v>-153.9190263904062</v>
       </c>
       <c r="H121" t="n">
         <v>10</v>
       </c>
       <c r="I121" t="n">
-        <v>88.08496031787172</v>
+        <v>1081.421973833244</v>
       </c>
       <c r="J121" t="n">
         <v>-155.0004483642394</v>
@@ -5789,17 +5789,17 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>-154.9139583139124</v>
+        <v>-154.225733955447</v>
       </c>
       <c r="H122" t="n">
         <v>10</v>
       </c>
       <c r="I122" t="n">
-        <v>86.49005032708601</v>
+        <v>774.7144087924198</v>
       </c>
       <c r="J122" t="n">
         <v>-155.0004483642394</v>
@@ -5833,17 +5833,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>-153.9190263904062</v>
+        <v>-154.1709053146757</v>
       </c>
       <c r="H123" t="n">
         <v>10</v>
       </c>
       <c r="I123" t="n">
-        <v>1081.421973833244</v>
+        <v>829.5430495637675</v>
       </c>
       <c r="J123" t="n">
         <v>-155.0004483642394</v>
@@ -5877,17 +5877,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>-154.225733955447</v>
+        <v>-154.9911800855448</v>
       </c>
       <c r="H124" t="n">
         <v>10</v>
       </c>
       <c r="I124" t="n">
-        <v>774.7144087924198</v>
+        <v>9.268278694605669</v>
       </c>
       <c r="J124" t="n">
         <v>-155.0004483642394</v>
@@ -5913,25 +5913,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>-154.1709053146757</v>
+        <v>-154.9163737412194</v>
       </c>
       <c r="H125" t="n">
         <v>10</v>
       </c>
       <c r="I125" t="n">
-        <v>829.5430495637675</v>
+        <v>84.07462302005797</v>
       </c>
       <c r="J125" t="n">
         <v>-155.0004483642394</v>
@@ -5957,25 +5957,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>-154.9911800855448</v>
+        <v>-154.2544363264691</v>
       </c>
       <c r="H126" t="n">
         <v>10</v>
       </c>
       <c r="I126" t="n">
-        <v>9.268278694605669</v>
+        <v>746.0120377702992</v>
       </c>
       <c r="J126" t="n">
         <v>-155.0004483642394</v>
@@ -6009,17 +6009,17 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>-154.9163737412194</v>
+        <v>-154.1524634303498</v>
       </c>
       <c r="H127" t="n">
         <v>10</v>
       </c>
       <c r="I127" t="n">
-        <v>84.07462302005797</v>
+        <v>847.9849338896202</v>
       </c>
       <c r="J127" t="n">
         <v>-155.0004483642394</v>
@@ -6053,17 +6053,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>-154.2544363264691</v>
+        <v>-154.1179874924097</v>
       </c>
       <c r="H128" t="n">
         <v>10</v>
       </c>
       <c r="I128" t="n">
-        <v>746.0120377702992</v>
+        <v>882.4608718297213</v>
       </c>
       <c r="J128" t="n">
         <v>-155.0004483642394</v>
@@ -6097,17 +6097,17 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>-154.1524634303498</v>
+        <v>-154.0297068113391</v>
       </c>
       <c r="H129" t="n">
         <v>10</v>
       </c>
       <c r="I129" t="n">
-        <v>847.9849338896202</v>
+        <v>970.7415529003356</v>
       </c>
       <c r="J129" t="n">
         <v>-155.0004483642394</v>
@@ -6141,17 +6141,17 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>-154.1179874924097</v>
+        <v>-154.9930708100015</v>
       </c>
       <c r="H130" t="n">
         <v>10</v>
       </c>
       <c r="I130" t="n">
-        <v>882.4608718297213</v>
+        <v>7.377554237962158</v>
       </c>
       <c r="J130" t="n">
         <v>-155.0004483642394</v>
@@ -6167,41 +6167,41 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>cc-pVDZ</t>
+          <t>STO-3G</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>but-1-yne</t>
+          <t>buta-1,3-diene</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>-154.0297068113391</v>
+        <v>-153.1357241386908</v>
       </c>
       <c r="H131" t="n">
         <v>10</v>
       </c>
       <c r="I131" t="n">
-        <v>970.7415529003356</v>
+        <v>169.6853031126011</v>
       </c>
       <c r="J131" t="n">
-        <v>-155.0004483642394</v>
+        <v>-153.3054094418034</v>
       </c>
       <c r="K131" t="n">
-        <v>-154.9113882737664</v>
+        <v>-153.0165417465354</v>
       </c>
       <c r="L131" t="inlineStr"/>
     </row>
@@ -6211,41 +6211,41 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>cc-pVDZ</t>
+          <t>STO-3G</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>but-1-yne</t>
+          <t>buta-1,3-diene</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>-154.9930708100015</v>
+        <v>-153.0825559470882</v>
       </c>
       <c r="H132" t="n">
         <v>10</v>
       </c>
       <c r="I132" t="n">
-        <v>7.377554237962158</v>
+        <v>222.8534947151957</v>
       </c>
       <c r="J132" t="n">
-        <v>-155.0004483642394</v>
+        <v>-153.3054094418034</v>
       </c>
       <c r="K132" t="n">
-        <v>-154.9113882737664</v>
+        <v>-153.0165417465354</v>
       </c>
       <c r="L132" t="inlineStr"/>
     </row>
@@ -6273,17 +6273,17 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>-153.1357241386908</v>
+        <v>-153.1700705200813</v>
       </c>
       <c r="H133" t="n">
         <v>10</v>
       </c>
       <c r="I133" t="n">
-        <v>169.6853031126011</v>
+        <v>135.3389217221093</v>
       </c>
       <c r="J133" t="n">
         <v>-153.3054094418034</v>
@@ -6317,17 +6317,17 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>-153.0825559470882</v>
+        <v>-153.1855539197828</v>
       </c>
       <c r="H134" t="n">
         <v>10</v>
       </c>
       <c r="I134" t="n">
-        <v>222.8534947151957</v>
+        <v>119.8555220206572</v>
       </c>
       <c r="J134" t="n">
         <v>-153.3054094418034</v>
@@ -6361,17 +6361,17 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>-153.1700705200813</v>
+        <v>-152.1912761606471</v>
       </c>
       <c r="H135" t="n">
         <v>10</v>
       </c>
       <c r="I135" t="n">
-        <v>135.3389217221093</v>
+        <v>1114.133281156285</v>
       </c>
       <c r="J135" t="n">
         <v>-153.3054094418034</v>
@@ -6405,17 +6405,17 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>-153.1855539197828</v>
+        <v>-153.2736973281175</v>
       </c>
       <c r="H136" t="n">
         <v>10</v>
       </c>
       <c r="I136" t="n">
-        <v>119.8555220206572</v>
+        <v>31.7121136859555</v>
       </c>
       <c r="J136" t="n">
         <v>-153.3054094418034</v>
@@ -6441,25 +6441,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>-152.1912761606471</v>
+        <v>-151.4779430502417</v>
       </c>
       <c r="H137" t="n">
         <v>10</v>
       </c>
       <c r="I137" t="n">
-        <v>1114.133281156285</v>
+        <v>1827.4663915617</v>
       </c>
       <c r="J137" t="n">
         <v>-153.3054094418034</v>
@@ -6485,25 +6485,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>-153.2736973281175</v>
+        <v>-152.1722607199707</v>
       </c>
       <c r="H138" t="n">
         <v>10</v>
       </c>
       <c r="I138" t="n">
-        <v>31.7121136859555</v>
+        <v>1133.148721832754</v>
       </c>
       <c r="J138" t="n">
         <v>-153.3054094418034</v>
@@ -6537,17 +6537,17 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>-151.4779430502417</v>
+        <v>-152.5185784052967</v>
       </c>
       <c r="H139" t="n">
         <v>10</v>
       </c>
       <c r="I139" t="n">
-        <v>1827.4663915617</v>
+        <v>786.8310365067259</v>
       </c>
       <c r="J139" t="n">
         <v>-153.3054094418034</v>
@@ -6581,17 +6581,17 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>-152.1722607199707</v>
+        <v>-153.0335802359963</v>
       </c>
       <c r="H140" t="n">
         <v>10</v>
       </c>
       <c r="I140" t="n">
-        <v>1133.148721832754</v>
+        <v>271.8292058070801</v>
       </c>
       <c r="J140" t="n">
         <v>-153.3054094418034</v>
@@ -6625,17 +6625,17 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>-152.5185784052967</v>
+        <v>-153.0434858295429</v>
       </c>
       <c r="H141" t="n">
         <v>10</v>
       </c>
       <c r="I141" t="n">
-        <v>786.8310365067259</v>
+        <v>261.9236122604889</v>
       </c>
       <c r="J141" t="n">
         <v>-153.3054094418034</v>
@@ -6669,17 +6669,17 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>-153.0335802359963</v>
+        <v>-153.2729045549831</v>
       </c>
       <c r="H142" t="n">
         <v>10</v>
       </c>
       <c r="I142" t="n">
-        <v>271.8292058070801</v>
+        <v>32.50488682027708</v>
       </c>
       <c r="J142" t="n">
         <v>-153.3054094418034</v>
@@ -6705,25 +6705,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>-153.0434858295429</v>
+        <v>-152.2466387535251</v>
       </c>
       <c r="H143" t="n">
         <v>10</v>
       </c>
       <c r="I143" t="n">
-        <v>261.9236122604889</v>
+        <v>1058.770688278287</v>
       </c>
       <c r="J143" t="n">
         <v>-153.3054094418034</v>
@@ -6749,25 +6749,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>-153.2729045549831</v>
+        <v>-150.9927345104938</v>
       </c>
       <c r="H144" t="n">
         <v>10</v>
       </c>
       <c r="I144" t="n">
-        <v>32.50488682027708</v>
+        <v>2312.67493130963</v>
       </c>
       <c r="J144" t="n">
         <v>-153.3054094418034</v>
@@ -6801,17 +6801,17 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>-152.2466387535251</v>
+        <v>-152.301396128385</v>
       </c>
       <c r="H145" t="n">
         <v>10</v>
       </c>
       <c r="I145" t="n">
-        <v>1058.770688278287</v>
+        <v>1004.013313418398</v>
       </c>
       <c r="J145" t="n">
         <v>-153.3054094418034</v>
@@ -6845,17 +6845,17 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>-150.9927345104938</v>
+        <v>-152.2521532075726</v>
       </c>
       <c r="H146" t="n">
         <v>10</v>
       </c>
       <c r="I146" t="n">
-        <v>2312.67493130963</v>
+        <v>1053.256234230844</v>
       </c>
       <c r="J146" t="n">
         <v>-153.3054094418034</v>
@@ -6889,17 +6889,17 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>-152.301396128385</v>
+        <v>-152.5599510049397</v>
       </c>
       <c r="H147" t="n">
         <v>10</v>
       </c>
       <c r="I147" t="n">
-        <v>1004.013313418398</v>
+        <v>745.4584368637143</v>
       </c>
       <c r="J147" t="n">
         <v>-153.3054094418034</v>
@@ -6933,17 +6933,17 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>-152.2521532075726</v>
+        <v>-153.2723894363922</v>
       </c>
       <c r="H148" t="n">
         <v>10</v>
       </c>
       <c r="I148" t="n">
-        <v>1053.256234230844</v>
+        <v>33.02000541117422</v>
       </c>
       <c r="J148" t="n">
         <v>-153.3054094418034</v>
@@ -6969,25 +6969,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>-152.5599510049397</v>
+        <v>-152.2603539718137</v>
       </c>
       <c r="H149" t="n">
         <v>10</v>
       </c>
       <c r="I149" t="n">
-        <v>745.4584368637143</v>
+        <v>1045.055469989734</v>
       </c>
       <c r="J149" t="n">
         <v>-153.3054094418034</v>
@@ -7013,25 +7013,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>-153.2723894363922</v>
+        <v>-152.2549373588304</v>
       </c>
       <c r="H150" t="n">
         <v>10</v>
       </c>
       <c r="I150" t="n">
-        <v>33.02000541117422</v>
+        <v>1050.472082973045</v>
       </c>
       <c r="J150" t="n">
         <v>-153.3054094418034</v>
@@ -7065,17 +7065,17 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>-152.2603539718137</v>
+        <v>-153.0445493061444</v>
       </c>
       <c r="H151" t="n">
         <v>10</v>
       </c>
       <c r="I151" t="n">
-        <v>1045.055469989734</v>
+        <v>260.8601356590157</v>
       </c>
       <c r="J151" t="n">
         <v>-153.3054094418034</v>
@@ -7109,17 +7109,17 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G152" t="n">
-        <v>-152.2549373588304</v>
+        <v>-153.0185693032415</v>
       </c>
       <c r="H152" t="n">
         <v>10</v>
       </c>
       <c r="I152" t="n">
-        <v>1050.472082973045</v>
+        <v>286.8401385618995</v>
       </c>
       <c r="J152" t="n">
         <v>-153.3054094418034</v>
@@ -7153,17 +7153,17 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G153" t="n">
-        <v>-153.0445493061444</v>
+        <v>-153.0307479602722</v>
       </c>
       <c r="H153" t="n">
         <v>10</v>
       </c>
       <c r="I153" t="n">
-        <v>260.8601356590157</v>
+        <v>274.6614815312682</v>
       </c>
       <c r="J153" t="n">
         <v>-153.3054094418034</v>
@@ -7197,17 +7197,17 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>-153.0185693032415</v>
+        <v>-153.2720371935036</v>
       </c>
       <c r="H154" t="n">
         <v>10</v>
       </c>
       <c r="I154" t="n">
-        <v>286.8401385618995</v>
+        <v>33.37224829982688</v>
       </c>
       <c r="J154" t="n">
         <v>-153.3054094418034</v>
@@ -7233,25 +7233,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>-153.0307479602722</v>
+        <v>-152.5203527261951</v>
       </c>
       <c r="H155" t="n">
         <v>10</v>
       </c>
       <c r="I155" t="n">
-        <v>274.6614815312682</v>
+        <v>785.0567156083343</v>
       </c>
       <c r="J155" t="n">
         <v>-153.3054094418034</v>
@@ -7277,25 +7277,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G156" t="n">
-        <v>-153.2720371935036</v>
+        <v>-152.5578242154852</v>
       </c>
       <c r="H156" t="n">
         <v>10</v>
       </c>
       <c r="I156" t="n">
-        <v>33.37224829982688</v>
+        <v>747.5852263182219</v>
       </c>
       <c r="J156" t="n">
         <v>-153.3054094418034</v>
@@ -7329,17 +7329,17 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G157" t="n">
-        <v>-152.5203527261951</v>
+        <v>-153.0179266922524</v>
       </c>
       <c r="H157" t="n">
         <v>10</v>
       </c>
       <c r="I157" t="n">
-        <v>785.0567156083343</v>
+        <v>287.4827495509749</v>
       </c>
       <c r="J157" t="n">
         <v>-153.3054094418034</v>
@@ -7373,17 +7373,17 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>-152.5578242154852</v>
+        <v>-153.02621965425</v>
       </c>
       <c r="H158" t="n">
         <v>10</v>
       </c>
       <c r="I158" t="n">
-        <v>747.5852263182219</v>
+        <v>279.1897875533778</v>
       </c>
       <c r="J158" t="n">
         <v>-153.3054094418034</v>
@@ -7417,17 +7417,17 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G159" t="n">
-        <v>-153.0179266922524</v>
+        <v>-152.162777322356</v>
       </c>
       <c r="H159" t="n">
         <v>10</v>
       </c>
       <c r="I159" t="n">
-        <v>287.4827495509749</v>
+        <v>1142.632119447455</v>
       </c>
       <c r="J159" t="n">
         <v>-153.3054094418034</v>
@@ -7461,17 +7461,17 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>-153.02621965425</v>
+        <v>-153.2633835948676</v>
       </c>
       <c r="H160" t="n">
         <v>10</v>
       </c>
       <c r="I160" t="n">
-        <v>279.1897875533778</v>
+        <v>42.02584693581457</v>
       </c>
       <c r="J160" t="n">
         <v>-153.3054094418034</v>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>STO-3G</t>
+          <t>aug-cc-pVDZ</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -7497,31 +7497,31 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>-152.162777322356</v>
+        <v>-154.9488075532024</v>
       </c>
       <c r="H161" t="n">
         <v>10</v>
       </c>
       <c r="I161" t="n">
-        <v>1142.632119447455</v>
+        <v>1.820885757524593</v>
       </c>
       <c r="J161" t="n">
-        <v>-153.3054094418034</v>
+        <v>-154.9506284389599</v>
       </c>
       <c r="K161" t="n">
-        <v>-153.0165417465354</v>
+        <v>-154.9399130373333</v>
       </c>
       <c r="L161" t="inlineStr"/>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>STO-3G</t>
+          <t>aug-cc-pVDZ</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -7541,31 +7541,31 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G162" t="n">
-        <v>-153.2633835948676</v>
+        <v>-154.9438242507404</v>
       </c>
       <c r="H162" t="n">
         <v>10</v>
       </c>
       <c r="I162" t="n">
-        <v>42.02584693581457</v>
+        <v>6.804188219518892</v>
       </c>
       <c r="J162" t="n">
-        <v>-153.3054094418034</v>
+        <v>-154.9506284389599</v>
       </c>
       <c r="K162" t="n">
-        <v>-153.0165417465354</v>
+        <v>-154.9399130373333</v>
       </c>
       <c r="L162" t="inlineStr"/>
     </row>
@@ -7593,17 +7593,17 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>-154.9488075532024</v>
+        <v>-154.4689745381633</v>
       </c>
       <c r="H163" t="n">
         <v>10</v>
       </c>
       <c r="I163" t="n">
-        <v>1.820885757524593</v>
+        <v>481.653900796573</v>
       </c>
       <c r="J163" t="n">
         <v>-154.9506284389599</v>
@@ -7629,25 +7629,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>-154.9438242507404</v>
+        <v>-153.2907289076241</v>
       </c>
       <c r="H164" t="n">
         <v>10</v>
       </c>
       <c r="I164" t="n">
-        <v>6.804188219518892</v>
+        <v>1659.899531335782</v>
       </c>
       <c r="J164" t="n">
         <v>-154.9506284389599</v>
@@ -7673,25 +7673,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G165" t="n">
-        <v>-154.4689745381633</v>
+        <v>-154.5043398844805</v>
       </c>
       <c r="H165" t="n">
         <v>10</v>
       </c>
       <c r="I165" t="n">
-        <v>481.653900796573</v>
+        <v>446.2885544793949</v>
       </c>
       <c r="J165" t="n">
         <v>-154.9506284389599</v>
@@ -7725,17 +7725,17 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G166" t="n">
-        <v>-153.2907289076241</v>
+        <v>-154.4686442903764</v>
       </c>
       <c r="H166" t="n">
         <v>10</v>
       </c>
       <c r="I166" t="n">
-        <v>1659.899531335782</v>
+        <v>481.9841485834786</v>
       </c>
       <c r="J166" t="n">
         <v>-154.9506284389599</v>
@@ -7769,17 +7769,17 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>-154.5043398844805</v>
+        <v>-154.9399609062344</v>
       </c>
       <c r="H167" t="n">
         <v>10</v>
       </c>
       <c r="I167" t="n">
-        <v>446.2885544793949</v>
+        <v>10.66753272544929</v>
       </c>
       <c r="J167" t="n">
         <v>-154.9506284389599</v>
@@ -7813,17 +7813,17 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G168" t="n">
-        <v>-154.4686442903764</v>
+        <v>-154.9475255907902</v>
       </c>
       <c r="H168" t="n">
         <v>10</v>
       </c>
       <c r="I168" t="n">
-        <v>481.9841485834786</v>
+        <v>3.102848169646677</v>
       </c>
       <c r="J168" t="n">
         <v>-154.9506284389599</v>
@@ -7849,25 +7849,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G169" t="n">
-        <v>-154.9399609062344</v>
+        <v>-154.1604878868675</v>
       </c>
       <c r="H169" t="n">
         <v>10</v>
       </c>
       <c r="I169" t="n">
-        <v>10.66753272544929</v>
+        <v>790.140552092339</v>
       </c>
       <c r="J169" t="n">
         <v>-154.9506284389599</v>
@@ -7893,25 +7893,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G170" t="n">
-        <v>-154.9475255907902</v>
+        <v>-153.153376547367</v>
       </c>
       <c r="H170" t="n">
         <v>10</v>
       </c>
       <c r="I170" t="n">
-        <v>3.102848169646677</v>
+        <v>1797.251891592907</v>
       </c>
       <c r="J170" t="n">
         <v>-154.9506284389599</v>
@@ -7945,17 +7945,17 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>-154.1604878868675</v>
+        <v>-154.5230638947714</v>
       </c>
       <c r="H171" t="n">
         <v>10</v>
       </c>
       <c r="I171" t="n">
-        <v>790.140552092339</v>
+        <v>427.564544188499</v>
       </c>
       <c r="J171" t="n">
         <v>-154.9506284389599</v>
@@ -7989,17 +7989,17 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>-153.153376547367</v>
+        <v>-154.305877222469</v>
       </c>
       <c r="H172" t="n">
         <v>10</v>
       </c>
       <c r="I172" t="n">
-        <v>1797.251891592907</v>
+        <v>644.7512164909313</v>
       </c>
       <c r="J172" t="n">
         <v>-154.9506284389599</v>
@@ -8033,17 +8033,17 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>-154.5230638947714</v>
+        <v>-154.4690160198077</v>
       </c>
       <c r="H173" t="n">
         <v>10</v>
       </c>
       <c r="I173" t="n">
-        <v>427.564544188499</v>
+        <v>481.6124191521567</v>
       </c>
       <c r="J173" t="n">
         <v>-154.9506284389599</v>
@@ -8069,25 +8069,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>-154.305877222469</v>
+        <v>-154.1685204078196</v>
       </c>
       <c r="H174" t="n">
         <v>10</v>
       </c>
       <c r="I174" t="n">
-        <v>644.7512164909313</v>
+        <v>782.1080311402966</v>
       </c>
       <c r="J174" t="n">
         <v>-154.9506284389599</v>
@@ -8113,25 +8113,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>-154.4690160198077</v>
+        <v>-153.6477628265835</v>
       </c>
       <c r="H175" t="n">
         <v>10</v>
       </c>
       <c r="I175" t="n">
-        <v>481.6124191521567</v>
+        <v>1302.865612376422</v>
       </c>
       <c r="J175" t="n">
         <v>-154.9506284389599</v>
@@ -8165,17 +8165,17 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>-154.1685204078196</v>
+        <v>-154.9401073107348</v>
       </c>
       <c r="H176" t="n">
         <v>10</v>
       </c>
       <c r="I176" t="n">
-        <v>782.1080311402966</v>
+        <v>10.52112822509343</v>
       </c>
       <c r="J176" t="n">
         <v>-154.9506284389599</v>
@@ -8209,17 +8209,17 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G177" t="n">
-        <v>-153.6477628265835</v>
+        <v>-154.4311851621608</v>
       </c>
       <c r="H177" t="n">
         <v>10</v>
       </c>
       <c r="I177" t="n">
-        <v>1302.865612376422</v>
+        <v>519.443276799052</v>
       </c>
       <c r="J177" t="n">
         <v>-154.9506284389599</v>
@@ -8253,17 +8253,17 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G178" t="n">
-        <v>-154.9401073107348</v>
+        <v>-154.4804480292407</v>
       </c>
       <c r="H178" t="n">
         <v>10</v>
       </c>
       <c r="I178" t="n">
-        <v>10.52112822509343</v>
+        <v>470.1804097191484</v>
       </c>
       <c r="J178" t="n">
         <v>-154.9506284389599</v>
@@ -8289,25 +8289,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>-154.4311851621608</v>
+        <v>-154.433529233188</v>
       </c>
       <c r="H179" t="n">
         <v>10</v>
       </c>
       <c r="I179" t="n">
-        <v>519.443276799052</v>
+        <v>517.0992057718422</v>
       </c>
       <c r="J179" t="n">
         <v>-154.9506284389599</v>
@@ -8333,25 +8333,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G180" t="n">
-        <v>-154.4804480292407</v>
+        <v>-154.4284944202545</v>
       </c>
       <c r="H180" t="n">
         <v>10</v>
       </c>
       <c r="I180" t="n">
-        <v>470.1804097191484</v>
+        <v>522.1340187053443</v>
       </c>
       <c r="J180" t="n">
         <v>-154.9506284389599</v>
@@ -8385,17 +8385,17 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>-154.433529233188</v>
+        <v>-154.4685976123411</v>
       </c>
       <c r="H181" t="n">
         <v>10</v>
       </c>
       <c r="I181" t="n">
-        <v>517.0992057718422</v>
+        <v>482.0308266187681</v>
       </c>
       <c r="J181" t="n">
         <v>-154.9506284389599</v>
@@ -8429,17 +8429,17 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>-154.4284944202545</v>
+        <v>-154.9465329751051</v>
       </c>
       <c r="H182" t="n">
         <v>10</v>
       </c>
       <c r="I182" t="n">
-        <v>522.1340187053443</v>
+        <v>4.095463854753234</v>
       </c>
       <c r="J182" t="n">
         <v>-154.9506284389599</v>
@@ -8473,17 +8473,17 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>-154.4685976123411</v>
+        <v>-164.5766676544592</v>
       </c>
       <c r="H183" t="n">
         <v>10</v>
       </c>
       <c r="I183" t="n">
-        <v>482.0308266187681</v>
+        <v>-9626.039215499304</v>
       </c>
       <c r="J183" t="n">
         <v>-154.9506284389599</v>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>aug-cc-pVDZ</t>
+          <t>cc-pVDZ</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -8509,31 +8509,31 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>-154.9465329751051</v>
+        <v>-154.9828572449146</v>
       </c>
       <c r="H184" t="n">
         <v>10</v>
       </c>
       <c r="I184" t="n">
-        <v>4.095463854753234</v>
+        <v>32.59370623322866</v>
       </c>
       <c r="J184" t="n">
-        <v>-154.9506284389599</v>
+        <v>-155.0154509511478</v>
       </c>
       <c r="K184" t="n">
-        <v>-154.9399130373333</v>
+        <v>-154.933920403517</v>
       </c>
       <c r="L184" t="inlineStr"/>
     </row>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>aug-cc-pVDZ</t>
+          <t>cc-pVDZ</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -8553,31 +8553,31 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>-164.5766676544592</v>
+        <v>-154.9728386518885</v>
       </c>
       <c r="H185" t="n">
         <v>10</v>
       </c>
       <c r="I185" t="n">
-        <v>-9626.039215499304</v>
+        <v>42.61229925924681</v>
       </c>
       <c r="J185" t="n">
-        <v>-154.9506284389599</v>
+        <v>-155.0154509511478</v>
       </c>
       <c r="K185" t="n">
-        <v>-154.9399130373333</v>
+        <v>-154.933920403517</v>
       </c>
       <c r="L185" t="inlineStr"/>
     </row>
@@ -8605,17 +8605,17 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G186" t="n">
-        <v>-154.9828572449146</v>
+        <v>-154.96930026494</v>
       </c>
       <c r="H186" t="n">
         <v>10</v>
       </c>
       <c r="I186" t="n">
-        <v>32.59370623322866</v>
+        <v>46.15068620773854</v>
       </c>
       <c r="J186" t="n">
         <v>-155.0154509511478</v>
@@ -8649,17 +8649,17 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>-154.9728386518885</v>
+        <v>-154.9943678069919</v>
       </c>
       <c r="H187" t="n">
         <v>10</v>
       </c>
       <c r="I187" t="n">
-        <v>42.61229925924681</v>
+        <v>21.08314415590939</v>
       </c>
       <c r="J187" t="n">
         <v>-155.0154509511478</v>
@@ -8693,17 +8693,17 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>-154.96930026494</v>
+        <v>-154.0099647675274</v>
       </c>
       <c r="H188" t="n">
         <v>10</v>
       </c>
       <c r="I188" t="n">
-        <v>46.15068620773854</v>
+        <v>1005.486183620405</v>
       </c>
       <c r="J188" t="n">
         <v>-155.0154509511478</v>
@@ -8737,17 +8737,17 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G189" t="n">
-        <v>-154.9943678069919</v>
+        <v>-155.0072537721249</v>
       </c>
       <c r="H189" t="n">
         <v>10</v>
       </c>
       <c r="I189" t="n">
-        <v>21.08314415590939</v>
+        <v>8.197179022886303</v>
       </c>
       <c r="J189" t="n">
         <v>-155.0154509511478</v>
@@ -8773,25 +8773,25 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>-154.0099647675274</v>
+        <v>-154.5216029992076</v>
       </c>
       <c r="H190" t="n">
         <v>10</v>
       </c>
       <c r="I190" t="n">
-        <v>1005.486183620405</v>
+        <v>493.8479519402108</v>
       </c>
       <c r="J190" t="n">
         <v>-155.0154509511478</v>
@@ -8817,25 +8817,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G191" t="n">
-        <v>-155.0072537721249</v>
+        <v>-154.955759414188</v>
       </c>
       <c r="H191" t="n">
         <v>10</v>
       </c>
       <c r="I191" t="n">
-        <v>8.197179022886303</v>
+        <v>59.69153695974683</v>
       </c>
       <c r="J191" t="n">
         <v>-155.0154509511478</v>
@@ -8869,17 +8869,17 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G192" t="n">
-        <v>-154.5216029992076</v>
+        <v>-154.2495660081191</v>
       </c>
       <c r="H192" t="n">
         <v>10</v>
       </c>
       <c r="I192" t="n">
-        <v>493.8479519402108</v>
+        <v>765.8849430287091</v>
       </c>
       <c r="J192" t="n">
         <v>-155.0154509511478</v>
@@ -8913,17 +8913,17 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G193" t="n">
-        <v>-154.955759414188</v>
+        <v>-154.9423798434264</v>
       </c>
       <c r="H193" t="n">
         <v>10</v>
       </c>
       <c r="I193" t="n">
-        <v>59.69153695974683</v>
+        <v>73.07110772143233</v>
       </c>
       <c r="J193" t="n">
         <v>-155.0154509511478</v>
@@ -8957,17 +8957,17 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G194" t="n">
-        <v>-154.2495660081191</v>
+        <v>-154.1234010517957</v>
       </c>
       <c r="H194" t="n">
         <v>10</v>
       </c>
       <c r="I194" t="n">
-        <v>765.8849430287091</v>
+        <v>892.0498993521164</v>
       </c>
       <c r="J194" t="n">
         <v>-155.0154509511478</v>
@@ -9001,17 +9001,17 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G195" t="n">
-        <v>-154.9423798434264</v>
+        <v>-155.0072179491773</v>
       </c>
       <c r="H195" t="n">
         <v>10</v>
       </c>
       <c r="I195" t="n">
-        <v>73.07110772143233</v>
+        <v>8.233001970438636</v>
       </c>
       <c r="J195" t="n">
         <v>-155.0154509511478</v>
@@ -9037,25 +9037,25 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G196" t="n">
-        <v>-154.1234010517957</v>
+        <v>-153.8618972276274</v>
       </c>
       <c r="H196" t="n">
         <v>10</v>
       </c>
       <c r="I196" t="n">
-        <v>892.0498993521164</v>
+        <v>1153.553723520361</v>
       </c>
       <c r="J196" t="n">
         <v>-155.0154509511478</v>
@@ -9081,25 +9081,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G197" t="n">
-        <v>-155.0072179491773</v>
+        <v>-154.9410086202933</v>
       </c>
       <c r="H197" t="n">
         <v>10</v>
       </c>
       <c r="I197" t="n">
-        <v>8.233001970438636</v>
+        <v>74.44233085448104</v>
       </c>
       <c r="J197" t="n">
         <v>-155.0154509511478</v>
@@ -9133,17 +9133,17 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G198" t="n">
-        <v>-153.8618972276274</v>
+        <v>-154.2140950329367</v>
       </c>
       <c r="H198" t="n">
         <v>10</v>
       </c>
       <c r="I198" t="n">
-        <v>1153.553723520361</v>
+        <v>801.3559182111294</v>
       </c>
       <c r="J198" t="n">
         <v>-155.0154509511478</v>
@@ -9177,17 +9177,17 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G199" t="n">
-        <v>-154.9410086202933</v>
+        <v>-154.2023495894866</v>
       </c>
       <c r="H199" t="n">
         <v>10</v>
       </c>
       <c r="I199" t="n">
-        <v>74.44233085448104</v>
+        <v>813.1013616612108</v>
       </c>
       <c r="J199" t="n">
         <v>-155.0154509511478</v>
@@ -9221,17 +9221,17 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G200" t="n">
-        <v>-154.2140950329367</v>
+        <v>-154.2660968446507</v>
       </c>
       <c r="H200" t="n">
         <v>10</v>
       </c>
       <c r="I200" t="n">
-        <v>801.3559182111294</v>
+        <v>749.3541064970941</v>
       </c>
       <c r="J200" t="n">
         <v>-155.0154509511478</v>
@@ -9265,17 +9265,17 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G201" t="n">
-        <v>-154.2023495894866</v>
+        <v>-155.0063190205414</v>
       </c>
       <c r="H201" t="n">
         <v>10</v>
       </c>
       <c r="I201" t="n">
-        <v>813.1013616612108</v>
+        <v>9.131930606372407</v>
       </c>
       <c r="J201" t="n">
         <v>-155.0154509511478</v>
@@ -9301,25 +9301,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G202" t="n">
-        <v>-154.2660968446507</v>
+        <v>-154.0376337493756</v>
       </c>
       <c r="H202" t="n">
         <v>10</v>
       </c>
       <c r="I202" t="n">
-        <v>749.3541064970941</v>
+        <v>977.8172017721545</v>
       </c>
       <c r="J202" t="n">
         <v>-155.0154509511478</v>
@@ -9345,25 +9345,25 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G203" t="n">
-        <v>-155.0063190205414</v>
+        <v>-154.9572276804694</v>
       </c>
       <c r="H203" t="n">
         <v>10</v>
       </c>
       <c r="I203" t="n">
-        <v>9.131930606372407</v>
+        <v>58.22327067841115</v>
       </c>
       <c r="J203" t="n">
         <v>-155.0154509511478</v>
@@ -9397,17 +9397,17 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G204" t="n">
-        <v>-154.0376337493756</v>
+        <v>-154.0686668026786</v>
       </c>
       <c r="H204" t="n">
         <v>10</v>
       </c>
       <c r="I204" t="n">
-        <v>977.8172017721545</v>
+        <v>946.7841484691917</v>
       </c>
       <c r="J204" t="n">
         <v>-155.0154509511478</v>
@@ -9441,17 +9441,17 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G205" t="n">
-        <v>-154.9572276804694</v>
+        <v>-154.5199058494725</v>
       </c>
       <c r="H205" t="n">
         <v>10</v>
       </c>
       <c r="I205" t="n">
-        <v>58.22327067841115</v>
+        <v>495.5451016752477</v>
       </c>
       <c r="J205" t="n">
         <v>-155.0154509511478</v>
@@ -9485,17 +9485,17 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G206" t="n">
-        <v>-154.0686668026786</v>
+        <v>-154.5185769124535</v>
       </c>
       <c r="H206" t="n">
         <v>10</v>
       </c>
       <c r="I206" t="n">
-        <v>946.7841484691917</v>
+        <v>496.8740386942727</v>
       </c>
       <c r="J206" t="n">
         <v>-155.0154509511478</v>
@@ -9529,17 +9529,17 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G207" t="n">
-        <v>-154.5199058494725</v>
+        <v>-155.0077217756853</v>
       </c>
       <c r="H207" t="n">
         <v>10</v>
       </c>
       <c r="I207" t="n">
-        <v>495.5451016752477</v>
+        <v>7.729175462486637</v>
       </c>
       <c r="J207" t="n">
         <v>-155.0154509511478</v>
@@ -9565,25 +9565,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G208" t="n">
-        <v>-154.5185769124535</v>
+        <v>-154.1615220618183</v>
       </c>
       <c r="H208" t="n">
         <v>10</v>
       </c>
       <c r="I208" t="n">
-        <v>496.8740386942727</v>
+        <v>853.9288893294383</v>
       </c>
       <c r="J208" t="n">
         <v>-155.0154509511478</v>
@@ -9609,25 +9609,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G209" t="n">
-        <v>-155.0077217756853</v>
+        <v>-154.0535367301257</v>
       </c>
       <c r="H209" t="n">
         <v>10</v>
       </c>
       <c r="I209" t="n">
-        <v>7.729175462486637</v>
+        <v>961.9142210220843</v>
       </c>
       <c r="J209" t="n">
         <v>-155.0154509511478</v>
@@ -9661,17 +9661,17 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G210" t="n">
-        <v>-154.1615220618183</v>
+        <v>-153.7385544493961</v>
       </c>
       <c r="H210" t="n">
         <v>10</v>
       </c>
       <c r="I210" t="n">
-        <v>853.9288893294383</v>
+        <v>1276.896501751708</v>
       </c>
       <c r="J210" t="n">
         <v>-155.0154509511478</v>
@@ -9705,17 +9705,17 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G211" t="n">
-        <v>-154.0535367301257</v>
+        <v>-153.7263205808158</v>
       </c>
       <c r="H211" t="n">
         <v>10</v>
       </c>
       <c r="I211" t="n">
-        <v>961.9142210220843</v>
+        <v>1289.130370331975</v>
       </c>
       <c r="J211" t="n">
         <v>-155.0154509511478</v>
@@ -9749,17 +9749,17 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G212" t="n">
-        <v>-153.7385544493961</v>
+        <v>-154.5494403032813</v>
       </c>
       <c r="H212" t="n">
         <v>10</v>
       </c>
       <c r="I212" t="n">
-        <v>1276.896501751708</v>
+        <v>466.0106478664829</v>
       </c>
       <c r="J212" t="n">
         <v>-155.0154509511478</v>
@@ -9793,17 +9793,17 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G213" t="n">
-        <v>-153.7263205808158</v>
+        <v>-155.0072144416225</v>
       </c>
       <c r="H213" t="n">
         <v>10</v>
       </c>
       <c r="I213" t="n">
-        <v>1289.130370331975</v>
+        <v>8.23650952531807</v>
       </c>
       <c r="J213" t="n">
         <v>-155.0154509511478</v>
@@ -9819,43 +9819,45 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>cc-pVDZ</t>
+          <t>STO-3G</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>buta-1,3-diene</t>
+          <t>ethane</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G214" t="n">
-        <v>-154.5494403032813</v>
+        <v>-78.45196026902894</v>
       </c>
       <c r="H214" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I214" t="n">
-        <v>466.0106478664829</v>
+        <v>-3.005041094212402</v>
       </c>
       <c r="J214" t="n">
-        <v>-155.0154509511478</v>
+        <v>-78.44895522793473</v>
       </c>
       <c r="K214" t="n">
-        <v>-154.933920403517</v>
-      </c>
-      <c r="L214" t="inlineStr"/>
+        <v>-78.30581623656136</v>
+      </c>
+      <c r="L214" t="n">
+        <v>-78.45323232971093</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
@@ -9863,43 +9865,45 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>cc-pVDZ</t>
+          <t>STO-3G</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>buta-1,3-diene</t>
+          <t>ethane</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G215" t="n">
-        <v>-155.0072144416225</v>
+        <v>-78.45228458153218</v>
       </c>
       <c r="H215" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I215" t="n">
-        <v>8.23650952531807</v>
+        <v>-3.32935359745079</v>
       </c>
       <c r="J215" t="n">
-        <v>-155.0154509511478</v>
+        <v>-78.44895522793473</v>
       </c>
       <c r="K215" t="n">
-        <v>-154.933920403517</v>
-      </c>
-      <c r="L215" t="inlineStr"/>
+        <v>-78.30581623656136</v>
+      </c>
+      <c r="L215" t="n">
+        <v>-78.45323232971093</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
@@ -9925,17 +9929,17 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>-78.45196026902894</v>
+        <v>-78.45244225817562</v>
       </c>
       <c r="H216" t="n">
         <v>8</v>
       </c>
       <c r="I216" t="n">
-        <v>-3.005041094212402</v>
+        <v>-3.487030240890476</v>
       </c>
       <c r="J216" t="n">
         <v>-78.44895522793473</v>
@@ -9971,17 +9975,17 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G217" t="n">
-        <v>-78.45228458153218</v>
+        <v>-78.4519487833831</v>
       </c>
       <c r="H217" t="n">
         <v>8</v>
       </c>
       <c r="I217" t="n">
-        <v>-3.32935359745079</v>
+        <v>-2.993555448369989</v>
       </c>
       <c r="J217" t="n">
         <v>-78.44895522793473</v>
@@ -10017,17 +10021,17 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G218" t="n">
-        <v>-78.45244225817562</v>
+        <v>-78.45103206369764</v>
       </c>
       <c r="H218" t="n">
         <v>8</v>
       </c>
       <c r="I218" t="n">
-        <v>-3.487030240890476</v>
+        <v>-2.076835762906626</v>
       </c>
       <c r="J218" t="n">
         <v>-78.44895522793473</v>
@@ -10063,17 +10067,17 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G219" t="n">
-        <v>-78.4519487833831</v>
+        <v>-78.45084519677899</v>
       </c>
       <c r="H219" t="n">
         <v>8</v>
       </c>
       <c r="I219" t="n">
-        <v>-2.993555448369989</v>
+        <v>-1.889968844253076</v>
       </c>
       <c r="J219" t="n">
         <v>-78.44895522793473</v>
@@ -10101,25 +10105,25 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G220" t="n">
-        <v>-78.45103206369764</v>
+        <v>-78.451003025067</v>
       </c>
       <c r="H220" t="n">
         <v>8</v>
       </c>
       <c r="I220" t="n">
-        <v>-2.076835762906626</v>
+        <v>-2.04779713226344</v>
       </c>
       <c r="J220" t="n">
         <v>-78.44895522793473</v>
@@ -10147,25 +10151,25 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G221" t="n">
-        <v>-78.45084519677899</v>
+        <v>-78.45180484524627</v>
       </c>
       <c r="H221" t="n">
         <v>8</v>
       </c>
       <c r="I221" t="n">
-        <v>-1.889968844253076</v>
+        <v>-2.849617311539987</v>
       </c>
       <c r="J221" t="n">
         <v>-78.44895522793473</v>
@@ -10201,17 +10205,17 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G222" t="n">
-        <v>-78.451003025067</v>
+        <v>-78.45230285960164</v>
       </c>
       <c r="H222" t="n">
         <v>8</v>
       </c>
       <c r="I222" t="n">
-        <v>-2.04779713226344</v>
+        <v>-3.347631666912321</v>
       </c>
       <c r="J222" t="n">
         <v>-78.44895522793473</v>
@@ -10247,17 +10251,17 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G223" t="n">
-        <v>-78.45180484524627</v>
+        <v>-78.45125327478137</v>
       </c>
       <c r="H223" t="n">
         <v>8</v>
       </c>
       <c r="I223" t="n">
-        <v>-2.849617311539987</v>
+        <v>-2.298046846632928</v>
       </c>
       <c r="J223" t="n">
         <v>-78.44895522793473</v>
@@ -10293,17 +10297,17 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G224" t="n">
-        <v>-78.45230285960164</v>
+        <v>-78.45098619000125</v>
       </c>
       <c r="H224" t="n">
         <v>8</v>
       </c>
       <c r="I224" t="n">
-        <v>-3.347631666912321</v>
+        <v>-2.030962066513098</v>
       </c>
       <c r="J224" t="n">
         <v>-78.44895522793473</v>
@@ -10339,17 +10343,17 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G225" t="n">
-        <v>-78.45125327478137</v>
+        <v>-78.45129476263865</v>
       </c>
       <c r="H225" t="n">
         <v>8</v>
       </c>
       <c r="I225" t="n">
-        <v>-2.298046846632928</v>
+        <v>-2.339534703921231</v>
       </c>
       <c r="J225" t="n">
         <v>-78.44895522793473</v>
@@ -10377,25 +10381,25 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G226" t="n">
-        <v>-78.45098619000125</v>
+        <v>-78.45092299128842</v>
       </c>
       <c r="H226" t="n">
         <v>8</v>
       </c>
       <c r="I226" t="n">
-        <v>-2.030962066513098</v>
+        <v>-1.967763353690088</v>
       </c>
       <c r="J226" t="n">
         <v>-78.44895522793473</v>
@@ -10423,25 +10427,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G227" t="n">
-        <v>-78.45129476263865</v>
+        <v>-78.45119224568596</v>
       </c>
       <c r="H227" t="n">
         <v>8</v>
       </c>
       <c r="I227" t="n">
-        <v>-2.339534703921231</v>
+        <v>-2.237017751227199</v>
       </c>
       <c r="J227" t="n">
         <v>-78.44895522793473</v>
@@ -10477,17 +10481,17 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G228" t="n">
-        <v>-78.45092299128842</v>
+        <v>-78.4508099090957</v>
       </c>
       <c r="H228" t="n">
         <v>8</v>
       </c>
       <c r="I228" t="n">
-        <v>-1.967763353690088</v>
+        <v>-1.854681160963878</v>
       </c>
       <c r="J228" t="n">
         <v>-78.44895522793473</v>
@@ -10523,17 +10527,17 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G229" t="n">
-        <v>-78.45119224568596</v>
+        <v>-78.4517986241586</v>
       </c>
       <c r="H229" t="n">
         <v>8</v>
       </c>
       <c r="I229" t="n">
-        <v>-2.237017751227199</v>
+        <v>-2.843396223866534</v>
       </c>
       <c r="J229" t="n">
         <v>-78.44895522793473</v>
@@ -10561,25 +10565,25 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G230" t="n">
-        <v>-78.4508099090957</v>
+        <v>-78.45105137304746</v>
       </c>
       <c r="H230" t="n">
         <v>8</v>
       </c>
       <c r="I230" t="n">
-        <v>-1.854681160963878</v>
+        <v>-2.096145112730596</v>
       </c>
       <c r="J230" t="n">
         <v>-78.44895522793473</v>
@@ -10607,25 +10611,25 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G231" t="n">
-        <v>-78.4517986241586</v>
+        <v>-78.45097882394616</v>
       </c>
       <c r="H231" t="n">
         <v>8</v>
       </c>
       <c r="I231" t="n">
-        <v>-2.843396223866534</v>
+        <v>-2.023596011426321</v>
       </c>
       <c r="J231" t="n">
         <v>-78.44895522793473</v>
@@ -10661,17 +10665,17 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G232" t="n">
-        <v>-78.45105137304746</v>
+        <v>-78.45105229101422</v>
       </c>
       <c r="H232" t="n">
         <v>8</v>
       </c>
       <c r="I232" t="n">
-        <v>-2.096145112730596</v>
+        <v>-2.097063079489203</v>
       </c>
       <c r="J232" t="n">
         <v>-78.44895522793473</v>
@@ -10707,17 +10711,17 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G233" t="n">
-        <v>-78.45097882394616</v>
+        <v>-78.45068550173808</v>
       </c>
       <c r="H233" t="n">
         <v>8</v>
       </c>
       <c r="I233" t="n">
-        <v>-2.023596011426321</v>
+        <v>-1.730273803346449</v>
       </c>
       <c r="J233" t="n">
         <v>-78.44895522793473</v>
@@ -10745,25 +10749,25 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G234" t="n">
-        <v>-78.45105229101422</v>
+        <v>-78.45134280809079</v>
       </c>
       <c r="H234" t="n">
         <v>8</v>
       </c>
       <c r="I234" t="n">
-        <v>-2.097063079489203</v>
+        <v>-2.387580156053559</v>
       </c>
       <c r="J234" t="n">
         <v>-78.44895522793473</v>
@@ -10791,25 +10795,25 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G235" t="n">
-        <v>-78.45068550173808</v>
+        <v>-78.45117878732135</v>
       </c>
       <c r="H235" t="n">
         <v>8</v>
       </c>
       <c r="I235" t="n">
-        <v>-1.730273803346449</v>
+        <v>-2.223559386621332</v>
       </c>
       <c r="J235" t="n">
         <v>-78.44895522793473</v>
@@ -10845,17 +10849,17 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G236" t="n">
-        <v>-78.45134280809079</v>
+        <v>-78.45137478893351</v>
       </c>
       <c r="H236" t="n">
         <v>8</v>
       </c>
       <c r="I236" t="n">
-        <v>-2.387580156053559</v>
+        <v>-2.419560998774273</v>
       </c>
       <c r="J236" t="n">
         <v>-78.44895522793473</v>
@@ -10891,17 +10895,17 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G237" t="n">
-        <v>-78.45117878732135</v>
+        <v>-78.45061780340897</v>
       </c>
       <c r="H237" t="n">
         <v>8</v>
       </c>
       <c r="I237" t="n">
-        <v>-2.223559386621332</v>
+        <v>-1.66257547424209</v>
       </c>
       <c r="J237" t="n">
         <v>-78.44895522793473</v>
@@ -10924,40 +10928,38 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>ethane</t>
+          <t>fluoroform</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E238" t="n">
+        <v>1</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>CCSD</t>
+        </is>
+      </c>
+      <c r="G238" t="n">
+        <v>-332.2246365681235</v>
+      </c>
+      <c r="H238" t="n">
         <v>5</v>
       </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>ML_exact</t>
-        </is>
-      </c>
-      <c r="G238" t="n">
-        <v>-78.45137478893351</v>
-      </c>
-      <c r="H238" t="n">
-        <v>8</v>
-      </c>
       <c r="I238" t="n">
-        <v>-2.419560998774273</v>
+        <v>-2.941598056793282</v>
       </c>
       <c r="J238" t="n">
-        <v>-78.44895522793473</v>
+        <v>-332.2216949700667</v>
       </c>
       <c r="K238" t="n">
-        <v>-78.30581623656136</v>
-      </c>
-      <c r="L238" t="n">
-        <v>-78.45323232971093</v>
-      </c>
+        <v>-332.0975924899263</v>
+      </c>
+      <c r="L238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
@@ -10970,40 +10972,38 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>ethane</t>
+          <t>fluoroform</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E239" t="n">
+        <v>1</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>-332.2246307453493</v>
+      </c>
+      <c r="H239" t="n">
         <v>5</v>
       </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>MP2</t>
-        </is>
-      </c>
-      <c r="G239" t="n">
-        <v>-78.45061780340897</v>
-      </c>
-      <c r="H239" t="n">
-        <v>8</v>
-      </c>
       <c r="I239" t="n">
-        <v>-1.66257547424209</v>
+        <v>-2.935775282594477</v>
       </c>
       <c r="J239" t="n">
-        <v>-78.44895522793473</v>
+        <v>-332.2216949700667</v>
       </c>
       <c r="K239" t="n">
-        <v>-78.30581623656136</v>
-      </c>
-      <c r="L239" t="n">
-        <v>-78.45323232971093</v>
-      </c>
+        <v>-332.0975924899263</v>
+      </c>
+      <c r="L239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
@@ -11029,17 +11029,17 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G240" t="n">
-        <v>-332.2246365681235</v>
+        <v>-332.22442506618</v>
       </c>
       <c r="H240" t="n">
         <v>5</v>
       </c>
       <c r="I240" t="n">
-        <v>-2.941598056793282</v>
+        <v>-2.730096113339187</v>
       </c>
       <c r="J240" t="n">
         <v>-332.2216949700667</v>
@@ -11073,17 +11073,17 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G241" t="n">
-        <v>-332.2246307453493</v>
+        <v>-332.2244710473527</v>
       </c>
       <c r="H241" t="n">
         <v>5</v>
       </c>
       <c r="I241" t="n">
-        <v>-2.935775282594477</v>
+        <v>-2.7760772860006</v>
       </c>
       <c r="J241" t="n">
         <v>-332.2216949700667</v>
@@ -11117,17 +11117,17 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G242" t="n">
-        <v>-332.22442506618</v>
+        <v>-332.2246224829088</v>
       </c>
       <c r="H242" t="n">
         <v>5</v>
       </c>
       <c r="I242" t="n">
-        <v>-2.730096113339187</v>
+        <v>-2.92751284212045</v>
       </c>
       <c r="J242" t="n">
         <v>-332.2216949700667</v>
@@ -11161,17 +11161,17 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G243" t="n">
-        <v>-332.2244710473527</v>
+        <v>-332.2240364957947</v>
       </c>
       <c r="H243" t="n">
         <v>5</v>
       </c>
       <c r="I243" t="n">
-        <v>-2.7760772860006</v>
+        <v>-2.341525728070337</v>
       </c>
       <c r="J243" t="n">
         <v>-332.2216949700667</v>
@@ -11197,25 +11197,25 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G244" t="n">
-        <v>-332.2246224829088</v>
+        <v>-332.224676388053</v>
       </c>
       <c r="H244" t="n">
         <v>5</v>
       </c>
       <c r="I244" t="n">
-        <v>-2.92751284212045</v>
+        <v>-2.981417986347878</v>
       </c>
       <c r="J244" t="n">
         <v>-332.2216949700667</v>
@@ -11241,25 +11241,25 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G245" t="n">
-        <v>-332.2240364957947</v>
+        <v>-332.2251305982015</v>
       </c>
       <c r="H245" t="n">
         <v>5</v>
       </c>
       <c r="I245" t="n">
-        <v>-2.341525728070337</v>
+        <v>-3.435628134809576</v>
       </c>
       <c r="J245" t="n">
         <v>-332.2216949700667</v>
@@ -11293,17 +11293,17 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G246" t="n">
-        <v>-332.224676388053</v>
+        <v>-332.2249345028254</v>
       </c>
       <c r="H246" t="n">
         <v>5</v>
       </c>
       <c r="I246" t="n">
-        <v>-2.981417986347878</v>
+        <v>-3.23953275869826</v>
       </c>
       <c r="J246" t="n">
         <v>-332.2216949700667</v>
@@ -11337,17 +11337,17 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G247" t="n">
-        <v>-332.2251305982015</v>
+        <v>-332.2246195686212</v>
       </c>
       <c r="H247" t="n">
         <v>5</v>
       </c>
       <c r="I247" t="n">
-        <v>-3.435628134809576</v>
+        <v>-2.924598554557178</v>
       </c>
       <c r="J247" t="n">
         <v>-332.2216949700667</v>
@@ -11381,17 +11381,17 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G248" t="n">
-        <v>-332.2249345028254</v>
+        <v>-332.2249202894409</v>
       </c>
       <c r="H248" t="n">
         <v>5</v>
       </c>
       <c r="I248" t="n">
-        <v>-3.23953275869826</v>
+        <v>-3.225319374223545</v>
       </c>
       <c r="J248" t="n">
         <v>-332.2216949700667</v>
@@ -11425,17 +11425,17 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G249" t="n">
-        <v>-332.2246195686212</v>
+        <v>-332.2237835069325</v>
       </c>
       <c r="H249" t="n">
         <v>5</v>
       </c>
       <c r="I249" t="n">
-        <v>-2.924598554557178</v>
+        <v>-2.088536865812785</v>
       </c>
       <c r="J249" t="n">
         <v>-332.2216949700667</v>
@@ -11461,25 +11461,25 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>-332.2249202894409</v>
+        <v>-332.2247230941931</v>
       </c>
       <c r="H250" t="n">
         <v>5</v>
       </c>
       <c r="I250" t="n">
-        <v>-3.225319374223545</v>
+        <v>-3.028124126387866</v>
       </c>
       <c r="J250" t="n">
         <v>-332.2216949700667</v>
@@ -11505,25 +11505,25 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>-332.2237835069325</v>
+        <v>-332.2249892256363</v>
       </c>
       <c r="H251" t="n">
         <v>5</v>
       </c>
       <c r="I251" t="n">
-        <v>-2.088536865812785</v>
+        <v>-3.294255569642246</v>
       </c>
       <c r="J251" t="n">
         <v>-332.2216949700667</v>
@@ -11557,17 +11557,17 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>-332.2247230941931</v>
+        <v>-332.2247979015166</v>
       </c>
       <c r="H252" t="n">
         <v>5</v>
       </c>
       <c r="I252" t="n">
-        <v>-3.028124126387866</v>
+        <v>-3.102931449916468</v>
       </c>
       <c r="J252" t="n">
         <v>-332.2216949700667</v>
@@ -11601,17 +11601,17 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>-332.2249892256363</v>
+        <v>-332.2248094077499</v>
       </c>
       <c r="H253" t="n">
         <v>5</v>
       </c>
       <c r="I253" t="n">
-        <v>-3.294255569642246</v>
+        <v>-3.114437683279903</v>
       </c>
       <c r="J253" t="n">
         <v>-332.2216949700667</v>
@@ -11645,17 +11645,17 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G254" t="n">
-        <v>-332.2247979015166</v>
+        <v>-332.2248433300495</v>
       </c>
       <c r="H254" t="n">
         <v>5</v>
       </c>
       <c r="I254" t="n">
-        <v>-3.102931449916468</v>
+        <v>-3.148359982844795</v>
       </c>
       <c r="J254" t="n">
         <v>-332.2216949700667</v>
@@ -11689,17 +11689,17 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>-332.2248094077499</v>
+        <v>-332.2243650958763</v>
       </c>
       <c r="H255" t="n">
         <v>5</v>
       </c>
       <c r="I255" t="n">
-        <v>-3.114437683279903</v>
+        <v>-2.670125809629553</v>
       </c>
       <c r="J255" t="n">
         <v>-332.2216949700667</v>
@@ -11725,25 +11725,25 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>-332.2248433300495</v>
+        <v>-332.2248500701731</v>
       </c>
       <c r="H256" t="n">
         <v>5</v>
       </c>
       <c r="I256" t="n">
-        <v>-3.148359982844795</v>
+        <v>-3.155100106482678</v>
       </c>
       <c r="J256" t="n">
         <v>-332.2216949700667</v>
@@ -11769,25 +11769,25 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G257" t="n">
-        <v>-332.2243650958763</v>
+        <v>-332.2248193754481</v>
       </c>
       <c r="H257" t="n">
         <v>5</v>
       </c>
       <c r="I257" t="n">
-        <v>-2.670125809629553</v>
+        <v>-3.124405381470297</v>
       </c>
       <c r="J257" t="n">
         <v>-332.2216949700667</v>
@@ -11821,17 +11821,17 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G258" t="n">
-        <v>-332.2248500701731</v>
+        <v>-332.2250752968361</v>
       </c>
       <c r="H258" t="n">
         <v>5</v>
       </c>
       <c r="I258" t="n">
-        <v>-3.155100106482678</v>
+        <v>-3.380326769388375</v>
       </c>
       <c r="J258" t="n">
         <v>-332.2216949700667</v>
@@ -11865,17 +11865,17 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G259" t="n">
-        <v>-332.2248193754481</v>
+        <v>-332.2249500221382</v>
       </c>
       <c r="H259" t="n">
         <v>5</v>
       </c>
       <c r="I259" t="n">
-        <v>-3.124405381470297</v>
+        <v>-3.255052071494902</v>
       </c>
       <c r="J259" t="n">
         <v>-332.2216949700667</v>
@@ -11909,17 +11909,17 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G260" t="n">
-        <v>-332.2250752968361</v>
+        <v>-332.2247981413528</v>
       </c>
       <c r="H260" t="n">
         <v>5</v>
       </c>
       <c r="I260" t="n">
-        <v>-3.380326769388375</v>
+        <v>-3.103171286170436</v>
       </c>
       <c r="J260" t="n">
         <v>-332.2216949700667</v>
@@ -11953,17 +11953,17 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G261" t="n">
-        <v>-332.2249500221382</v>
+        <v>-332.2241428665708</v>
       </c>
       <c r="H261" t="n">
         <v>5</v>
       </c>
       <c r="I261" t="n">
-        <v>-3.255052071494902</v>
+        <v>-2.447896504179425</v>
       </c>
       <c r="J261" t="n">
         <v>-332.2216949700667</v>
@@ -11989,25 +11989,25 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G262" t="n">
-        <v>-332.2247981413528</v>
+        <v>-332.2249277911654</v>
       </c>
       <c r="H262" t="n">
         <v>5</v>
       </c>
       <c r="I262" t="n">
-        <v>-3.103171286170436</v>
+        <v>-3.232821098720251</v>
       </c>
       <c r="J262" t="n">
         <v>-332.2216949700667</v>
@@ -12033,25 +12033,25 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G263" t="n">
-        <v>-332.2241428665708</v>
+        <v>-332.2251275965907</v>
       </c>
       <c r="H263" t="n">
         <v>5</v>
       </c>
       <c r="I263" t="n">
-        <v>-2.447896504179425</v>
+        <v>-3.432626523988347</v>
       </c>
       <c r="J263" t="n">
         <v>-332.2216949700667</v>
@@ -12085,17 +12085,17 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G264" t="n">
-        <v>-332.2249277911654</v>
+        <v>-332.2249630125604</v>
       </c>
       <c r="H264" t="n">
         <v>5</v>
       </c>
       <c r="I264" t="n">
-        <v>-3.232821098720251</v>
+        <v>-3.268042493743906</v>
       </c>
       <c r="J264" t="n">
         <v>-332.2216949700667</v>
@@ -12129,17 +12129,17 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G265" t="n">
-        <v>-332.2251275965907</v>
+        <v>-332.2248289997194</v>
       </c>
       <c r="H265" t="n">
         <v>5</v>
       </c>
       <c r="I265" t="n">
-        <v>-3.432626523988347</v>
+        <v>-3.134029652699155</v>
       </c>
       <c r="J265" t="n">
         <v>-332.2216949700667</v>
@@ -12173,17 +12173,17 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G266" t="n">
-        <v>-332.2249630125604</v>
+        <v>-332.2248642431461</v>
       </c>
       <c r="H266" t="n">
         <v>5</v>
       </c>
       <c r="I266" t="n">
-        <v>-3.268042493743906</v>
+        <v>-3.169273079436152</v>
       </c>
       <c r="J266" t="n">
         <v>-332.2216949700667</v>
@@ -12217,17 +12217,17 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G267" t="n">
-        <v>-332.2248289997194</v>
+        <v>-332.2240040230492</v>
       </c>
       <c r="H267" t="n">
         <v>5</v>
       </c>
       <c r="I267" t="n">
-        <v>-3.134029652699155</v>
+        <v>-2.309052982525372</v>
       </c>
       <c r="J267" t="n">
         <v>-332.2216949700667</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>STO-3G</t>
+          <t>cc-pVDZ</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -12253,31 +12253,31 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G268" t="n">
-        <v>-332.2248642431461</v>
+        <v>-336.8260363693874</v>
       </c>
       <c r="H268" t="n">
         <v>5</v>
       </c>
       <c r="I268" t="n">
-        <v>-3.169273079436152</v>
+        <v>-1.60436881020587</v>
       </c>
       <c r="J268" t="n">
-        <v>-332.2216949700667</v>
+        <v>-336.8244320005772</v>
       </c>
       <c r="K268" t="n">
-        <v>-332.0975924899263</v>
+        <v>-336.7867835322212</v>
       </c>
       <c r="L268" t="inlineStr"/>
     </row>
@@ -12287,7 +12287,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>STO-3G</t>
+          <t>cc-pVDZ</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -12297,31 +12297,31 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G269" t="n">
-        <v>-332.2240040230492</v>
+        <v>-336.8260349315088</v>
       </c>
       <c r="H269" t="n">
         <v>5</v>
       </c>
       <c r="I269" t="n">
-        <v>-2.309052982525372</v>
+        <v>-1.602930931653646</v>
       </c>
       <c r="J269" t="n">
-        <v>-332.2216949700667</v>
+        <v>-336.8244320005772</v>
       </c>
       <c r="K269" t="n">
-        <v>-332.0975924899263</v>
+        <v>-336.7867835322212</v>
       </c>
       <c r="L269" t="inlineStr"/>
     </row>
@@ -12341,25 +12341,25 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G270" t="n">
-        <v>-336.8260363693874</v>
+        <v>-336.8260355655501</v>
       </c>
       <c r="H270" t="n">
         <v>5</v>
       </c>
       <c r="I270" t="n">
-        <v>-1.60436881020587</v>
+        <v>-1.603564972924687</v>
       </c>
       <c r="J270" t="n">
         <v>-336.8244320005772</v>
@@ -12385,11 +12385,11 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -12397,13 +12397,13 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>-336.8260349315088</v>
+        <v>-336.8260602705358</v>
       </c>
       <c r="H271" t="n">
         <v>5</v>
       </c>
       <c r="I271" t="n">
-        <v>-1.602930931653646</v>
+        <v>-1.628269958587225</v>
       </c>
       <c r="J271" t="n">
         <v>-336.8244320005772</v>
@@ -12419,43 +12419,45 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>cc-pVDZ</t>
+          <t>STO-3G</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>fluoroform</t>
+          <t>methanol</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G272" t="n">
-        <v>-336.8260355655501</v>
+        <v>-113.662465407226</v>
       </c>
       <c r="H272" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I272" t="n">
-        <v>-1.603564972924687</v>
+        <v>-1.699912164056627</v>
       </c>
       <c r="J272" t="n">
-        <v>-336.8244320005772</v>
+        <v>-113.660765495062</v>
       </c>
       <c r="K272" t="n">
-        <v>-336.7867835322212</v>
-      </c>
-      <c r="L272" t="inlineStr"/>
+        <v>-113.5447589109086</v>
+      </c>
+      <c r="L272" t="n">
+        <v>-113.6626087137703</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
@@ -12463,43 +12465,45 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>cc-pVDZ</t>
+          <t>STO-3G</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>fluoroform</t>
+          <t>methanol</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G273" t="n">
-        <v>-336.8260602705358</v>
+        <v>-113.6624868064293</v>
       </c>
       <c r="H273" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I273" t="n">
-        <v>-1.628269958587225</v>
+        <v>-1.721311367376188</v>
       </c>
       <c r="J273" t="n">
-        <v>-336.8244320005772</v>
+        <v>-113.660765495062</v>
       </c>
       <c r="K273" t="n">
-        <v>-336.7867835322212</v>
-      </c>
-      <c r="L273" t="inlineStr"/>
+        <v>-113.5447589109086</v>
+      </c>
+      <c r="L273" t="n">
+        <v>-113.6626087137703</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
@@ -12525,17 +12529,17 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G274" t="n">
-        <v>-113.662465407226</v>
+        <v>-113.6624880300175</v>
       </c>
       <c r="H274" t="n">
         <v>6</v>
       </c>
       <c r="I274" t="n">
-        <v>-1.699912164056627</v>
+        <v>-1.722534955561628</v>
       </c>
       <c r="J274" t="n">
         <v>-113.660765495062</v>
@@ -12571,17 +12575,17 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G275" t="n">
-        <v>-113.6624868064293</v>
+        <v>-113.662529006638</v>
       </c>
       <c r="H275" t="n">
         <v>6</v>
       </c>
       <c r="I275" t="n">
-        <v>-1.721311367376188</v>
+        <v>-1.76351157601573</v>
       </c>
       <c r="J275" t="n">
         <v>-113.660765495062</v>
@@ -12617,17 +12621,17 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G276" t="n">
-        <v>-113.6624880300175</v>
+        <v>-113.6625658140582</v>
       </c>
       <c r="H276" t="n">
         <v>6</v>
       </c>
       <c r="I276" t="n">
-        <v>-1.722534955561628</v>
+        <v>-1.800318996217243</v>
       </c>
       <c r="J276" t="n">
         <v>-113.660765495062</v>
@@ -12655,25 +12659,25 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G277" t="n">
-        <v>-113.662529006638</v>
+        <v>-113.6625710272076</v>
       </c>
       <c r="H277" t="n">
         <v>6</v>
       </c>
       <c r="I277" t="n">
-        <v>-1.76351157601573</v>
+        <v>-1.8055321456103</v>
       </c>
       <c r="J277" t="n">
         <v>-113.660765495062</v>
@@ -12701,25 +12705,25 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G278" t="n">
-        <v>-113.6625658140582</v>
+        <v>-113.662560752718</v>
       </c>
       <c r="H278" t="n">
         <v>6</v>
       </c>
       <c r="I278" t="n">
-        <v>-1.800318996217243</v>
+        <v>-1.795257656041827</v>
       </c>
       <c r="J278" t="n">
         <v>-113.660765495062</v>
@@ -12755,17 +12759,17 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G279" t="n">
-        <v>-113.6625710272076</v>
+        <v>-113.6625647001974</v>
       </c>
       <c r="H279" t="n">
         <v>6</v>
       </c>
       <c r="I279" t="n">
-        <v>-1.8055321456103</v>
+        <v>-1.799205135469606</v>
       </c>
       <c r="J279" t="n">
         <v>-113.660765495062</v>
@@ -12801,17 +12805,17 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G280" t="n">
-        <v>-113.662560752718</v>
+        <v>-113.6625437333032</v>
       </c>
       <c r="H280" t="n">
         <v>6</v>
       </c>
       <c r="I280" t="n">
-        <v>-1.795257656041827</v>
+        <v>-1.778238241243457</v>
       </c>
       <c r="J280" t="n">
         <v>-113.660765495062</v>
@@ -12847,17 +12851,17 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G281" t="n">
-        <v>-113.6625647001974</v>
+        <v>-113.6625601893481</v>
       </c>
       <c r="H281" t="n">
         <v>6</v>
       </c>
       <c r="I281" t="n">
-        <v>-1.799205135469606</v>
+        <v>-1.794694286147092</v>
       </c>
       <c r="J281" t="n">
         <v>-113.660765495062</v>
@@ -12885,25 +12889,25 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G282" t="n">
-        <v>-113.6625437333032</v>
+        <v>-113.6625479048084</v>
       </c>
       <c r="H282" t="n">
         <v>6</v>
       </c>
       <c r="I282" t="n">
-        <v>-1.778238241243457</v>
+        <v>-1.782409746439839</v>
       </c>
       <c r="J282" t="n">
         <v>-113.660765495062</v>
@@ -12931,25 +12935,25 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G283" t="n">
-        <v>-113.6625601893481</v>
+        <v>-113.6625624986648</v>
       </c>
       <c r="H283" t="n">
         <v>6</v>
       </c>
       <c r="I283" t="n">
-        <v>-1.794694286147092</v>
+        <v>-1.797003602817426</v>
       </c>
       <c r="J283" t="n">
         <v>-113.660765495062</v>
@@ -12985,17 +12989,17 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G284" t="n">
-        <v>-113.6625479048084</v>
+        <v>-113.6625700252463</v>
       </c>
       <c r="H284" t="n">
         <v>6</v>
       </c>
       <c r="I284" t="n">
-        <v>-1.782409746439839</v>
+        <v>-1.804530184372766</v>
       </c>
       <c r="J284" t="n">
         <v>-113.660765495062</v>
@@ -13031,17 +13035,17 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G285" t="n">
-        <v>-113.6625624986648</v>
+        <v>-113.6625657413047</v>
       </c>
       <c r="H285" t="n">
         <v>6</v>
       </c>
       <c r="I285" t="n">
-        <v>-1.797003602817426</v>
+        <v>-1.800246242723347</v>
       </c>
       <c r="J285" t="n">
         <v>-113.660765495062</v>
@@ -13077,17 +13081,17 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G286" t="n">
-        <v>-113.6625700252463</v>
+        <v>-113.6625601119439</v>
       </c>
       <c r="H286" t="n">
         <v>6</v>
       </c>
       <c r="I286" t="n">
-        <v>-1.804530184372766</v>
+        <v>-1.794616881952038</v>
       </c>
       <c r="J286" t="n">
         <v>-113.660765495062</v>
@@ -13115,25 +13119,25 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G287" t="n">
-        <v>-113.6625657413047</v>
+        <v>-113.6625502308704</v>
       </c>
       <c r="H287" t="n">
         <v>6</v>
       </c>
       <c r="I287" t="n">
-        <v>-1.800246242723347</v>
+        <v>-1.784735808413984</v>
       </c>
       <c r="J287" t="n">
         <v>-113.660765495062</v>
@@ -13161,25 +13165,25 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G288" t="n">
-        <v>-113.6625601119439</v>
+        <v>-113.6625663277787</v>
       </c>
       <c r="H288" t="n">
         <v>6</v>
       </c>
       <c r="I288" t="n">
-        <v>-1.794616881952038</v>
+        <v>-1.800832716767786</v>
       </c>
       <c r="J288" t="n">
         <v>-113.660765495062</v>
@@ -13215,17 +13219,17 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G289" t="n">
-        <v>-113.6625502308704</v>
+        <v>-113.6625684815751</v>
       </c>
       <c r="H289" t="n">
         <v>6</v>
       </c>
       <c r="I289" t="n">
-        <v>-1.784735808413984</v>
+        <v>-1.802986513084193</v>
       </c>
       <c r="J289" t="n">
         <v>-113.660765495062</v>
@@ -13261,17 +13265,17 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G290" t="n">
-        <v>-113.6625663277787</v>
+        <v>-113.662569827856</v>
       </c>
       <c r="H290" t="n">
         <v>6</v>
       </c>
       <c r="I290" t="n">
-        <v>-1.800832716767786</v>
+        <v>-1.804332794009156</v>
       </c>
       <c r="J290" t="n">
         <v>-113.660765495062</v>
@@ -13307,17 +13311,17 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G291" t="n">
-        <v>-113.6625684815751</v>
+        <v>-113.6625550727545</v>
       </c>
       <c r="H291" t="n">
         <v>6</v>
       </c>
       <c r="I291" t="n">
-        <v>-1.802986513084193</v>
+        <v>-1.789577692520083</v>
       </c>
       <c r="J291" t="n">
         <v>-113.660765495062</v>
@@ -13345,25 +13349,25 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G292" t="n">
-        <v>-113.662569827856</v>
+        <v>-113.6625602992152</v>
       </c>
       <c r="H292" t="n">
         <v>6</v>
       </c>
       <c r="I292" t="n">
-        <v>-1.804332794009156</v>
+        <v>-1.794804153220753</v>
       </c>
       <c r="J292" t="n">
         <v>-113.660765495062</v>
@@ -13391,25 +13395,25 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G293" t="n">
-        <v>-113.6625550727545</v>
+        <v>-113.6625603727529</v>
       </c>
       <c r="H293" t="n">
         <v>6</v>
       </c>
       <c r="I293" t="n">
-        <v>-1.789577692520083</v>
+        <v>-1.794877690926455</v>
       </c>
       <c r="J293" t="n">
         <v>-113.660765495062</v>
@@ -13445,17 +13449,17 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G294" t="n">
-        <v>-113.6625602992152</v>
+        <v>-113.6625716349185</v>
       </c>
       <c r="H294" t="n">
         <v>6</v>
       </c>
       <c r="I294" t="n">
-        <v>-1.794804153220753</v>
+        <v>-1.806139856554978</v>
       </c>
       <c r="J294" t="n">
         <v>-113.660765495062</v>
@@ -13491,17 +13495,17 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G295" t="n">
-        <v>-113.6625603727529</v>
+        <v>-113.6625638130971</v>
       </c>
       <c r="H295" t="n">
         <v>6</v>
       </c>
       <c r="I295" t="n">
-        <v>-1.794877690926455</v>
+        <v>-1.79831803517061</v>
       </c>
       <c r="J295" t="n">
         <v>-113.660765495062</v>
@@ -13537,17 +13541,17 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G296" t="n">
-        <v>-113.6625716349185</v>
+        <v>-113.6625610067019</v>
       </c>
       <c r="H296" t="n">
         <v>6</v>
       </c>
       <c r="I296" t="n">
-        <v>-1.806139856554978</v>
+        <v>-1.79551163996905</v>
       </c>
       <c r="J296" t="n">
         <v>-113.660765495062</v>
@@ -13570,40 +13574,38 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>methanol</t>
+          <t>prop-2-en-1-ol</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G297" t="n">
-        <v>-113.6625638130971</v>
+        <v>-189.6808205163561</v>
       </c>
       <c r="H297" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I297" t="n">
-        <v>-1.79831803517061</v>
+        <v>46.19523674443826</v>
       </c>
       <c r="J297" t="n">
-        <v>-113.660765495062</v>
+        <v>-189.7270157531005</v>
       </c>
       <c r="K297" t="n">
-        <v>-113.5447589109086</v>
-      </c>
-      <c r="L297" t="n">
-        <v>-113.6626087137703</v>
-      </c>
+        <v>-189.4804271888057</v>
+      </c>
+      <c r="L297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
@@ -13616,40 +13618,38 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>methanol</t>
+          <t>prop-2-en-1-ol</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G298" t="n">
-        <v>-113.6625610067019</v>
+        <v>-189.6143465310523</v>
       </c>
       <c r="H298" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I298" t="n">
-        <v>-1.79551163996905</v>
+        <v>112.6692220482255</v>
       </c>
       <c r="J298" t="n">
-        <v>-113.660765495062</v>
+        <v>-189.7270157531005</v>
       </c>
       <c r="K298" t="n">
-        <v>-113.5447589109086</v>
-      </c>
-      <c r="L298" t="n">
-        <v>-113.6626087137703</v>
-      </c>
+        <v>-189.4804271888057</v>
+      </c>
+      <c r="L298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
@@ -13675,17 +13675,17 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G299" t="n">
-        <v>-189.6808205163561</v>
+        <v>-189.6031336104605</v>
       </c>
       <c r="H299" t="n">
         <v>10</v>
       </c>
       <c r="I299" t="n">
-        <v>46.19523674443826</v>
+        <v>123.8821426400136</v>
       </c>
       <c r="J299" t="n">
         <v>-189.7270157531005</v>
@@ -13719,17 +13719,17 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G300" t="n">
-        <v>-189.6143465310523</v>
+        <v>-189.5769119101616</v>
       </c>
       <c r="H300" t="n">
         <v>10</v>
       </c>
       <c r="I300" t="n">
-        <v>112.6692220482255</v>
+        <v>150.1038429388473</v>
       </c>
       <c r="J300" t="n">
         <v>-189.7270157531005</v>
@@ -13763,17 +13763,17 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G301" t="n">
-        <v>-189.6031336104605</v>
+        <v>-188.8520013562317</v>
       </c>
       <c r="H301" t="n">
         <v>10</v>
       </c>
       <c r="I301" t="n">
-        <v>123.8821426400136</v>
+        <v>875.0143968688349</v>
       </c>
       <c r="J301" t="n">
         <v>-189.7270157531005</v>
@@ -13807,17 +13807,17 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G302" t="n">
-        <v>-189.5769119101616</v>
+        <v>-189.7120631697455</v>
       </c>
       <c r="H302" t="n">
         <v>10</v>
       </c>
       <c r="I302" t="n">
-        <v>150.1038429388473</v>
+        <v>14.95258335495464</v>
       </c>
       <c r="J302" t="n">
         <v>-189.7270157531005</v>
@@ -13843,25 +13843,25 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G303" t="n">
-        <v>-188.8520013562317</v>
+        <v>-189.518883282987</v>
       </c>
       <c r="H303" t="n">
         <v>10</v>
       </c>
       <c r="I303" t="n">
-        <v>875.0143968688349</v>
+        <v>208.132470113469</v>
       </c>
       <c r="J303" t="n">
         <v>-189.7270157531005</v>
@@ -13887,25 +13887,25 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G304" t="n">
-        <v>-189.7120631697455</v>
+        <v>-189.5285622451023</v>
       </c>
       <c r="H304" t="n">
         <v>10</v>
       </c>
       <c r="I304" t="n">
-        <v>14.95258335495464</v>
+        <v>198.4535079982379</v>
       </c>
       <c r="J304" t="n">
         <v>-189.7270157531005</v>
@@ -13939,17 +13939,17 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G305" t="n">
-        <v>-189.518883282987</v>
+        <v>-189.5014081997568</v>
       </c>
       <c r="H305" t="n">
         <v>10</v>
       </c>
       <c r="I305" t="n">
-        <v>208.132470113469</v>
+        <v>225.6075533436501</v>
       </c>
       <c r="J305" t="n">
         <v>-189.7270157531005</v>
@@ -13983,17 +13983,17 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G306" t="n">
-        <v>-189.5285622451023</v>
+        <v>-189.5268304577797</v>
       </c>
       <c r="H306" t="n">
         <v>10</v>
       </c>
       <c r="I306" t="n">
-        <v>198.4535079982379</v>
+        <v>200.1852953208072</v>
       </c>
       <c r="J306" t="n">
         <v>-189.7270157531005</v>
@@ -14027,17 +14027,17 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G307" t="n">
-        <v>-189.5014081997568</v>
+        <v>-189.5282989439489</v>
       </c>
       <c r="H307" t="n">
         <v>10</v>
       </c>
       <c r="I307" t="n">
-        <v>225.6075533436501</v>
+        <v>198.7168091515628</v>
       </c>
       <c r="J307" t="n">
         <v>-189.7270157531005</v>
@@ -14071,17 +14071,17 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G308" t="n">
-        <v>-189.5268304577797</v>
+        <v>-189.7090767448711</v>
       </c>
       <c r="H308" t="n">
         <v>10</v>
       </c>
       <c r="I308" t="n">
-        <v>200.1852953208072</v>
+        <v>17.93900822934802</v>
       </c>
       <c r="J308" t="n">
         <v>-189.7270157531005</v>
@@ -14107,25 +14107,25 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G309" t="n">
-        <v>-189.5282989439489</v>
+        <v>-189.4953906383641</v>
       </c>
       <c r="H309" t="n">
         <v>10</v>
       </c>
       <c r="I309" t="n">
-        <v>198.7168091515628</v>
+        <v>231.6251147363459</v>
       </c>
       <c r="J309" t="n">
         <v>-189.7270157531005</v>
@@ -14151,25 +14151,25 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>-189.7090767448711</v>
+        <v>-189.524292952043</v>
       </c>
       <c r="H310" t="n">
         <v>10</v>
       </c>
       <c r="I310" t="n">
-        <v>17.93900822934802</v>
+        <v>202.7228010574618</v>
       </c>
       <c r="J310" t="n">
         <v>-189.7270157531005</v>
@@ -14203,17 +14203,17 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>-189.4953906383641</v>
+        <v>-189.535138180474</v>
       </c>
       <c r="H311" t="n">
         <v>10</v>
       </c>
       <c r="I311" t="n">
-        <v>231.6251147363459</v>
+        <v>191.877572626538</v>
       </c>
       <c r="J311" t="n">
         <v>-189.7270157531005</v>
@@ -14247,17 +14247,17 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G312" t="n">
-        <v>-189.524292952043</v>
+        <v>-188.8723347083925</v>
       </c>
       <c r="H312" t="n">
         <v>10</v>
       </c>
       <c r="I312" t="n">
-        <v>202.7228010574618</v>
+        <v>854.6810447079451</v>
       </c>
       <c r="J312" t="n">
         <v>-189.7270157531005</v>
@@ -14291,17 +14291,17 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G313" t="n">
-        <v>-189.535138180474</v>
+        <v>-188.8735615062697</v>
       </c>
       <c r="H313" t="n">
         <v>10</v>
       </c>
       <c r="I313" t="n">
-        <v>191.877572626538</v>
+        <v>853.4542468308359</v>
       </c>
       <c r="J313" t="n">
         <v>-189.7270157531005</v>
@@ -14335,17 +14335,17 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G314" t="n">
-        <v>-188.8723347083925</v>
+        <v>-189.7107457557645</v>
       </c>
       <c r="H314" t="n">
         <v>10</v>
       </c>
       <c r="I314" t="n">
-        <v>854.6810447079451</v>
+        <v>16.26999733599632</v>
       </c>
       <c r="J314" t="n">
         <v>-189.7270157531005</v>
@@ -14371,25 +14371,25 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G315" t="n">
-        <v>-188.8735615062697</v>
+        <v>-189.5250776033889</v>
       </c>
       <c r="H315" t="n">
         <v>10</v>
       </c>
       <c r="I315" t="n">
-        <v>853.4542468308359</v>
+        <v>201.9381497116228</v>
       </c>
       <c r="J315" t="n">
         <v>-189.7270157531005</v>
@@ -14415,25 +14415,25 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G316" t="n">
-        <v>-189.7107457557645</v>
+        <v>-189.4969202256459</v>
       </c>
       <c r="H316" t="n">
         <v>10</v>
       </c>
       <c r="I316" t="n">
-        <v>16.26999733599632</v>
+        <v>230.09552745458</v>
       </c>
       <c r="J316" t="n">
         <v>-189.7270157531005</v>
@@ -14467,17 +14467,17 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G317" t="n">
-        <v>-189.5250776033889</v>
+        <v>-189.4977761056279</v>
       </c>
       <c r="H317" t="n">
         <v>10</v>
       </c>
       <c r="I317" t="n">
-        <v>201.9381497116228</v>
+        <v>229.239647472582</v>
       </c>
       <c r="J317" t="n">
         <v>-189.7270157531005</v>
@@ -14511,17 +14511,17 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G318" t="n">
-        <v>-189.4969202256459</v>
+        <v>-189.4941653785411</v>
       </c>
       <c r="H318" t="n">
         <v>10</v>
       </c>
       <c r="I318" t="n">
-        <v>230.09552745458</v>
+        <v>232.850374559348</v>
       </c>
       <c r="J318" t="n">
         <v>-189.7270157531005</v>
@@ -14555,17 +14555,17 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G319" t="n">
-        <v>-189.4977761056279</v>
+        <v>-188.2617589485396</v>
       </c>
       <c r="H319" t="n">
         <v>10</v>
       </c>
       <c r="I319" t="n">
-        <v>229.239647472582</v>
+        <v>1465.256804560852</v>
       </c>
       <c r="J319" t="n">
         <v>-189.7270157531005</v>
@@ -14599,17 +14599,17 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G320" t="n">
-        <v>-189.4941653785411</v>
+        <v>-189.7114958132647</v>
       </c>
       <c r="H320" t="n">
         <v>10</v>
       </c>
       <c r="I320" t="n">
-        <v>232.850374559348</v>
+        <v>15.51993983576949</v>
       </c>
       <c r="J320" t="n">
         <v>-189.7270157531005</v>
@@ -14635,25 +14635,25 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G321" t="n">
-        <v>-188.2617589485396</v>
+        <v>-189.5210193298893</v>
       </c>
       <c r="H321" t="n">
         <v>10</v>
       </c>
       <c r="I321" t="n">
-        <v>1465.256804560852</v>
+        <v>205.9964232112179</v>
       </c>
       <c r="J321" t="n">
         <v>-189.7270157531005</v>
@@ -14679,25 +14679,25 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G322" t="n">
-        <v>-189.7114958132647</v>
+        <v>-189.5239469397676</v>
       </c>
       <c r="H322" t="n">
         <v>10</v>
       </c>
       <c r="I322" t="n">
-        <v>15.51993983576949</v>
+        <v>203.0688133328908</v>
       </c>
       <c r="J322" t="n">
         <v>-189.7270157531005</v>
@@ -14731,17 +14731,17 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G323" t="n">
-        <v>-189.5210193298893</v>
+        <v>-188.5096926436997</v>
       </c>
       <c r="H323" t="n">
         <v>10</v>
       </c>
       <c r="I323" t="n">
-        <v>205.9964232112179</v>
+        <v>1217.323109400752</v>
       </c>
       <c r="J323" t="n">
         <v>-189.7270157531005</v>
@@ -14775,17 +14775,17 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G324" t="n">
-        <v>-189.5239469397676</v>
+        <v>-188.4868484899191</v>
       </c>
       <c r="H324" t="n">
         <v>10</v>
       </c>
       <c r="I324" t="n">
-        <v>203.0688133328908</v>
+        <v>1240.167263181377</v>
       </c>
       <c r="J324" t="n">
         <v>-189.7270157531005</v>
@@ -14819,17 +14819,17 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G325" t="n">
-        <v>-188.5096926436997</v>
+        <v>-188.5297595444494</v>
       </c>
       <c r="H325" t="n">
         <v>10</v>
       </c>
       <c r="I325" t="n">
-        <v>1217.323109400752</v>
+        <v>1197.256208651083</v>
       </c>
       <c r="J325" t="n">
         <v>-189.7270157531005</v>
@@ -14863,17 +14863,17 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G326" t="n">
-        <v>-188.4868484899191</v>
+        <v>-189.7115870741756</v>
       </c>
       <c r="H326" t="n">
         <v>10</v>
       </c>
       <c r="I326" t="n">
-        <v>1240.167263181377</v>
+        <v>15.42867892493405</v>
       </c>
       <c r="J326" t="n">
         <v>-189.7270157531005</v>
@@ -14889,7 +14889,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>STO-3G</t>
+          <t>aug-cc-pVDZ</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -14899,31 +14899,31 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G327" t="n">
-        <v>-188.5297595444494</v>
+        <v>-191.9519974141113</v>
       </c>
       <c r="H327" t="n">
         <v>10</v>
       </c>
       <c r="I327" t="n">
-        <v>1197.256208651083</v>
+        <v>1.774551367020649</v>
       </c>
       <c r="J327" t="n">
-        <v>-189.7270157531005</v>
+        <v>-191.9537719654783</v>
       </c>
       <c r="K327" t="n">
-        <v>-189.4804271888057</v>
+        <v>-191.9516344755187</v>
       </c>
       <c r="L327" t="inlineStr"/>
     </row>
@@ -14933,7 +14933,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>STO-3G</t>
+          <t>aug-cc-pVDZ</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -14943,31 +14943,31 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G328" t="n">
-        <v>-189.7115870741756</v>
+        <v>-191.1634841176429</v>
       </c>
       <c r="H328" t="n">
         <v>10</v>
       </c>
       <c r="I328" t="n">
-        <v>15.42867892493405</v>
+        <v>790.2878478354296</v>
       </c>
       <c r="J328" t="n">
-        <v>-189.7270157531005</v>
+        <v>-191.9537719654783</v>
       </c>
       <c r="K328" t="n">
-        <v>-189.4804271888057</v>
+        <v>-191.9516344755187</v>
       </c>
       <c r="L328" t="inlineStr"/>
     </row>
@@ -14987,11 +14987,11 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -14999,13 +14999,13 @@
         </is>
       </c>
       <c r="G329" t="n">
-        <v>-191.9519974141113</v>
+        <v>-191.0731092276205</v>
       </c>
       <c r="H329" t="n">
         <v>10</v>
       </c>
       <c r="I329" t="n">
-        <v>1.774551367020649</v>
+        <v>880.6627378578469</v>
       </c>
       <c r="J329" t="n">
         <v>-191.9537719654783</v>
@@ -15031,25 +15031,25 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G330" t="n">
-        <v>-191.1634841176429</v>
+        <v>-191.149782554133</v>
       </c>
       <c r="H330" t="n">
         <v>10</v>
       </c>
       <c r="I330" t="n">
-        <v>790.2878478354296</v>
+        <v>803.9894113453556</v>
       </c>
       <c r="J330" t="n">
         <v>-191.9537719654783</v>
@@ -15075,25 +15075,25 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>-191.0731092276205</v>
+        <v>-191.9516573003273</v>
       </c>
       <c r="H331" t="n">
         <v>10</v>
       </c>
       <c r="I331" t="n">
-        <v>880.6627378578469</v>
+        <v>2.114665150998007</v>
       </c>
       <c r="J331" t="n">
         <v>-191.9537719654783</v>
@@ -15119,25 +15119,25 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G332" t="n">
-        <v>-191.149782554133</v>
+        <v>-191.2452709160886</v>
       </c>
       <c r="H332" t="n">
         <v>10</v>
       </c>
       <c r="I332" t="n">
-        <v>803.9894113453556</v>
+        <v>708.5010493897244</v>
       </c>
       <c r="J332" t="n">
         <v>-191.9537719654783</v>
@@ -15171,17 +15171,17 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>-191.9516573003273</v>
+        <v>-190.9183003641962</v>
       </c>
       <c r="H333" t="n">
         <v>10</v>
       </c>
       <c r="I333" t="n">
-        <v>2.114665150998007</v>
+        <v>1035.471601282154</v>
       </c>
       <c r="J333" t="n">
         <v>-191.9537719654783</v>
@@ -15215,17 +15215,17 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G334" t="n">
-        <v>-191.2452709160886</v>
+        <v>-191.2200076349744</v>
       </c>
       <c r="H334" t="n">
         <v>10</v>
       </c>
       <c r="I334" t="n">
-        <v>708.5010493897244</v>
+        <v>733.7643305039592</v>
       </c>
       <c r="J334" t="n">
         <v>-191.9537719654783</v>
@@ -15259,17 +15259,17 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G335" t="n">
-        <v>-190.9183003641962</v>
+        <v>-191.9516742432006</v>
       </c>
       <c r="H335" t="n">
         <v>10</v>
       </c>
       <c r="I335" t="n">
-        <v>1035.471601282154</v>
+        <v>2.097722277710545</v>
       </c>
       <c r="J335" t="n">
         <v>-191.9537719654783</v>
@@ -15295,25 +15295,25 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>-191.2200076349744</v>
+        <v>-191.1458496642358</v>
       </c>
       <c r="H336" t="n">
         <v>10</v>
       </c>
       <c r="I336" t="n">
-        <v>733.7643305039592</v>
+        <v>807.92230124257</v>
       </c>
       <c r="J336" t="n">
         <v>-191.9537719654783</v>
@@ -15339,25 +15339,25 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G337" t="n">
-        <v>-191.9516742432006</v>
+        <v>-191.2428047671126</v>
       </c>
       <c r="H337" t="n">
         <v>10</v>
       </c>
       <c r="I337" t="n">
-        <v>2.097722277710545</v>
+        <v>710.9671983657222</v>
       </c>
       <c r="J337" t="n">
         <v>-191.9537719654783</v>
@@ -15391,17 +15391,17 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G338" t="n">
-        <v>-191.1458496642358</v>
+        <v>-191.9518400899062</v>
       </c>
       <c r="H338" t="n">
         <v>10</v>
       </c>
       <c r="I338" t="n">
-        <v>807.92230124257</v>
+        <v>1.931875572097397</v>
       </c>
       <c r="J338" t="n">
         <v>-191.9537719654783</v>
@@ -15427,25 +15427,25 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G339" t="n">
-        <v>-191.2428047671126</v>
+        <v>-191.9516652011622</v>
       </c>
       <c r="H339" t="n">
         <v>10</v>
       </c>
       <c r="I339" t="n">
-        <v>710.9671983657222</v>
+        <v>2.106764316124554</v>
       </c>
       <c r="J339" t="n">
         <v>-191.9537719654783</v>
@@ -15471,25 +15471,25 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G340" t="n">
-        <v>-191.9518400899062</v>
+        <v>-191.9516657338321</v>
       </c>
       <c r="H340" t="n">
         <v>10</v>
       </c>
       <c r="I340" t="n">
-        <v>1.931875572097397</v>
+        <v>2.106231646223478</v>
       </c>
       <c r="J340" t="n">
         <v>-191.9537719654783</v>
@@ -15523,17 +15523,17 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G341" t="n">
-        <v>-191.9516652011622</v>
+        <v>-191.1482922822166</v>
       </c>
       <c r="H341" t="n">
         <v>10</v>
       </c>
       <c r="I341" t="n">
-        <v>2.106764316124554</v>
+        <v>805.4796832617512</v>
       </c>
       <c r="J341" t="n">
         <v>-191.9537719654783</v>
@@ -15549,7 +15549,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>aug-cc-pVDZ</t>
+          <t>cc-pVDZ</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -15559,31 +15559,31 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G342" t="n">
-        <v>-191.9516657338321</v>
+        <v>-191.9534485891146</v>
       </c>
       <c r="H342" t="n">
         <v>10</v>
       </c>
       <c r="I342" t="n">
-        <v>2.106231646223478</v>
+        <v>44.03229792816887</v>
       </c>
       <c r="J342" t="n">
-        <v>-191.9537719654783</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K342" t="n">
-        <v>-191.9516344755187</v>
+        <v>-191.9364953941601</v>
       </c>
       <c r="L342" t="inlineStr"/>
     </row>
@@ -15593,7 +15593,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>aug-cc-pVDZ</t>
+          <t>cc-pVDZ</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -15603,31 +15603,31 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>LUCJ(L=5)</t>
+          <t>LUCJ(L=1)</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G343" t="n">
-        <v>-191.1482922822166</v>
+        <v>-191.9738633977651</v>
       </c>
       <c r="H343" t="n">
         <v>10</v>
       </c>
       <c r="I343" t="n">
-        <v>805.4796832617512</v>
+        <v>23.61748927771146</v>
       </c>
       <c r="J343" t="n">
-        <v>-191.9537719654783</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K343" t="n">
-        <v>-191.9516344755187</v>
+        <v>-191.9364953941601</v>
       </c>
       <c r="L343" t="inlineStr"/>
     </row>
@@ -15655,20 +15655,20 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G344" t="n">
-        <v>-191.9534485891146</v>
+        <v>-191.9745863201936</v>
       </c>
       <c r="H344" t="n">
         <v>10</v>
       </c>
       <c r="I344" t="n">
-        <v>44.03229792811203</v>
+        <v>22.89456684914626</v>
       </c>
       <c r="J344" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K344" t="n">
         <v>-191.9364953941601</v>
@@ -15699,20 +15699,20 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G345" t="n">
-        <v>-191.9738633977651</v>
+        <v>-191.9750639772247</v>
       </c>
       <c r="H345" t="n">
         <v>10</v>
       </c>
       <c r="I345" t="n">
-        <v>23.61748927765461</v>
+        <v>22.41690981807665</v>
       </c>
       <c r="J345" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K345" t="n">
         <v>-191.9364953941601</v>
@@ -15743,20 +15743,20 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G346" t="n">
-        <v>-191.9745863201936</v>
+        <v>-191.9380213720039</v>
       </c>
       <c r="H346" t="n">
         <v>10</v>
       </c>
       <c r="I346" t="n">
-        <v>22.89456684908941</v>
+        <v>59.45951503886704</v>
       </c>
       <c r="J346" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K346" t="n">
         <v>-191.9364953941601</v>
@@ -15787,20 +15787,20 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G347" t="n">
-        <v>-191.9750639772247</v>
+        <v>-191.9921307417835</v>
       </c>
       <c r="H347" t="n">
         <v>10</v>
       </c>
       <c r="I347" t="n">
-        <v>22.4169098180198</v>
+        <v>5.350145259313877</v>
       </c>
       <c r="J347" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K347" t="n">
         <v>-191.9364953941601</v>
@@ -15823,28 +15823,28 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G348" t="n">
-        <v>-191.9380213720039</v>
+        <v>-191.9388807858837</v>
       </c>
       <c r="H348" t="n">
         <v>10</v>
       </c>
       <c r="I348" t="n">
-        <v>59.4595150388102</v>
+        <v>58.60010115904402</v>
       </c>
       <c r="J348" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K348" t="n">
         <v>-191.9364953941601</v>
@@ -15867,28 +15867,28 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>LUCJ(L=1)</t>
+          <t>LUCJ(L=2)</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G349" t="n">
-        <v>-191.9921307417835</v>
+        <v>-191.9560428619665</v>
       </c>
       <c r="H349" t="n">
         <v>10</v>
       </c>
       <c r="I349" t="n">
-        <v>5.350145259257033</v>
+        <v>41.43802507624628</v>
       </c>
       <c r="J349" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K349" t="n">
         <v>-191.9364953941601</v>
@@ -15919,20 +15919,20 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G350" t="n">
-        <v>-191.9388807858837</v>
+        <v>-191.3904179244482</v>
       </c>
       <c r="H350" t="n">
         <v>10</v>
       </c>
       <c r="I350" t="n">
-        <v>58.60010115898717</v>
+        <v>607.0629625945401</v>
       </c>
       <c r="J350" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K350" t="n">
         <v>-191.9364953941601</v>
@@ -15963,20 +15963,20 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G351" t="n">
-        <v>-191.9560428619665</v>
+        <v>-191.9529233348009</v>
       </c>
       <c r="H351" t="n">
         <v>10</v>
       </c>
       <c r="I351" t="n">
-        <v>41.43802507618943</v>
+        <v>44.55755224191194</v>
       </c>
       <c r="J351" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K351" t="n">
         <v>-191.9364953941601</v>
@@ -16007,20 +16007,20 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G352" t="n">
-        <v>-191.3904179244482</v>
+        <v>-191.9499334950364</v>
       </c>
       <c r="H352" t="n">
         <v>10</v>
       </c>
       <c r="I352" t="n">
-        <v>607.0629625944832</v>
+        <v>47.54739200635072</v>
       </c>
       <c r="J352" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K352" t="n">
         <v>-191.9364953941601</v>
@@ -16051,20 +16051,20 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G353" t="n">
-        <v>-191.9529233348009</v>
+        <v>-191.9928188383286</v>
       </c>
       <c r="H353" t="n">
         <v>10</v>
       </c>
       <c r="I353" t="n">
-        <v>44.55755224185509</v>
+        <v>4.662048714152434</v>
       </c>
       <c r="J353" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K353" t="n">
         <v>-191.9364953941601</v>
@@ -16087,28 +16087,28 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G354" t="n">
-        <v>-191.9499334950364</v>
+        <v>-191.9386763487821</v>
       </c>
       <c r="H354" t="n">
         <v>10</v>
       </c>
       <c r="I354" t="n">
-        <v>47.54739200629388</v>
+        <v>58.80453826065946</v>
       </c>
       <c r="J354" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K354" t="n">
         <v>-191.9364953941601</v>
@@ -16131,28 +16131,28 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>LUCJ(L=2)</t>
+          <t>LUCJ(L=3)</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G355" t="n">
-        <v>-191.9928188383286</v>
+        <v>-191.9394960360387</v>
       </c>
       <c r="H355" t="n">
         <v>10</v>
       </c>
       <c r="I355" t="n">
-        <v>4.66204871409559</v>
+        <v>57.98485100402218</v>
       </c>
       <c r="J355" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K355" t="n">
         <v>-191.9364953941601</v>
@@ -16183,20 +16183,20 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G356" t="n">
-        <v>-191.9386763487821</v>
+        <v>-191.1432948626463</v>
       </c>
       <c r="H356" t="n">
         <v>10</v>
       </c>
       <c r="I356" t="n">
-        <v>58.80453826060261</v>
+        <v>854.186024396455</v>
       </c>
       <c r="J356" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K356" t="n">
         <v>-191.9364953941601</v>
@@ -16227,20 +16227,20 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G357" t="n">
-        <v>-191.9394960360387</v>
+        <v>-191.9385272046664</v>
       </c>
       <c r="H357" t="n">
         <v>10</v>
       </c>
       <c r="I357" t="n">
-        <v>57.98485100396533</v>
+        <v>58.95368237636944</v>
       </c>
       <c r="J357" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K357" t="n">
         <v>-191.9364953941601</v>
@@ -16271,20 +16271,20 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G358" t="n">
-        <v>-191.1432948626463</v>
+        <v>-191.9373741140392</v>
       </c>
       <c r="H358" t="n">
         <v>10</v>
       </c>
       <c r="I358" t="n">
-        <v>854.1860243963981</v>
+        <v>60.1067730035254</v>
       </c>
       <c r="J358" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K358" t="n">
         <v>-191.9364953941601</v>
@@ -16315,20 +16315,20 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G359" t="n">
-        <v>-191.9385272046664</v>
+        <v>-191.9924951145691</v>
       </c>
       <c r="H359" t="n">
         <v>10</v>
       </c>
       <c r="I359" t="n">
-        <v>58.9536823763126</v>
+        <v>4.985772473645511</v>
       </c>
       <c r="J359" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K359" t="n">
         <v>-191.9364953941601</v>
@@ -16351,28 +16351,28 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G360" t="n">
-        <v>-191.9373741140392</v>
+        <v>-191.9504784195769</v>
       </c>
       <c r="H360" t="n">
         <v>10</v>
       </c>
       <c r="I360" t="n">
-        <v>60.10677300346856</v>
+        <v>47.00246746588732</v>
       </c>
       <c r="J360" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K360" t="n">
         <v>-191.9364953941601</v>
@@ -16395,28 +16395,28 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>LUCJ(L=3)</t>
+          <t>LUCJ(L=4)</t>
         </is>
       </c>
       <c r="E361" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G361" t="n">
-        <v>-191.9924951145691</v>
+        <v>-191.3808576902583</v>
       </c>
       <c r="H361" t="n">
         <v>10</v>
       </c>
       <c r="I361" t="n">
-        <v>4.985772473588668</v>
+        <v>616.6231967844453</v>
       </c>
       <c r="J361" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K361" t="n">
         <v>-191.9364953941601</v>
@@ -16447,20 +16447,20 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G362" t="n">
-        <v>-191.9504784195769</v>
+        <v>-191.2741421909589</v>
       </c>
       <c r="H362" t="n">
         <v>10</v>
       </c>
       <c r="I362" t="n">
-        <v>47.00246746583048</v>
+        <v>723.3386960838573</v>
       </c>
       <c r="J362" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K362" t="n">
         <v>-191.9364953941601</v>
@@ -16491,20 +16491,20 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G363" t="n">
-        <v>-191.3808576902583</v>
+        <v>-191.939355331488</v>
       </c>
       <c r="H363" t="n">
         <v>10</v>
       </c>
       <c r="I363" t="n">
-        <v>616.6231967843885</v>
+        <v>58.12555555476706</v>
       </c>
       <c r="J363" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K363" t="n">
         <v>-191.9364953941601</v>
@@ -16535,20 +16535,20 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G364" t="n">
-        <v>-191.2741421909589</v>
+        <v>-191.0265516609469</v>
       </c>
       <c r="H364" t="n">
         <v>10</v>
       </c>
       <c r="I364" t="n">
-        <v>723.3386960838004</v>
+        <v>970.9292260958762</v>
       </c>
       <c r="J364" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K364" t="n">
         <v>-191.9364953941601</v>
@@ -16579,20 +16579,20 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G365" t="n">
-        <v>-191.939355331488</v>
+        <v>-191.9920153168911</v>
       </c>
       <c r="H365" t="n">
         <v>10</v>
       </c>
       <c r="I365" t="n">
-        <v>58.12555555471022</v>
+        <v>5.465570151699239</v>
       </c>
       <c r="J365" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K365" t="n">
         <v>-191.9364953941601</v>
@@ -16615,28 +16615,28 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>CCSD</t>
         </is>
       </c>
       <c r="G366" t="n">
-        <v>-191.0265516609469</v>
+        <v>-191.9523804301191</v>
       </c>
       <c r="H366" t="n">
         <v>10</v>
       </c>
       <c r="I366" t="n">
-        <v>970.9292260958193</v>
+        <v>45.10045692362041</v>
       </c>
       <c r="J366" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K366" t="n">
         <v>-191.9364953941601</v>
@@ -16659,28 +16659,28 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>LUCJ(L=4)</t>
+          <t>LUCJ(L=5)</t>
         </is>
       </c>
       <c r="E367" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>zeroes</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="G367" t="n">
-        <v>-191.9920153168911</v>
+        <v>-191.938076270761</v>
       </c>
       <c r="H367" t="n">
         <v>10</v>
       </c>
       <c r="I367" t="n">
-        <v>5.465570151642396</v>
+        <v>59.40461628179605</v>
       </c>
       <c r="J367" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K367" t="n">
         <v>-191.9364953941601</v>
@@ -16711,20 +16711,20 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>CCSD</t>
+          <t>ML_exact</t>
         </is>
       </c>
       <c r="G368" t="n">
-        <v>-191.9523804301191</v>
+        <v>-191.1229725889993</v>
       </c>
       <c r="H368" t="n">
         <v>10</v>
       </c>
       <c r="I368" t="n">
-        <v>45.10045692356357</v>
+        <v>874.5082980434233</v>
       </c>
       <c r="J368" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K368" t="n">
         <v>-191.9364953941601</v>
@@ -16755,20 +16755,20 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="G369" t="n">
-        <v>-191.938076270761</v>
+        <v>-191.9543641774467</v>
       </c>
       <c r="H369" t="n">
         <v>10</v>
       </c>
       <c r="I369" t="n">
-        <v>59.40461628173921</v>
+        <v>43.1167095960916</v>
       </c>
       <c r="J369" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K369" t="n">
         <v>-191.9364953941601</v>
@@ -16799,20 +16799,20 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>ML_exact</t>
+          <t>random</t>
         </is>
       </c>
       <c r="G370" t="n">
-        <v>-191.1229725889993</v>
+        <v>-191.9399783754006</v>
       </c>
       <c r="H370" t="n">
         <v>10</v>
       </c>
       <c r="I370" t="n">
-        <v>874.5082980433665</v>
+        <v>57.50251164212727</v>
       </c>
       <c r="J370" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K370" t="n">
         <v>-191.9364953941601</v>
@@ -16843,113 +16843,25 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>zeroes</t>
         </is>
       </c>
       <c r="G371" t="n">
-        <v>-191.9543641774467</v>
+        <v>-191.9921928770854</v>
       </c>
       <c r="H371" t="n">
         <v>10</v>
       </c>
       <c r="I371" t="n">
-        <v>43.11670959603475</v>
+        <v>5.288009957354234</v>
       </c>
       <c r="J371" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K371" t="n">
         <v>-191.9364953941601</v>
       </c>
       <c r="L371" t="inlineStr"/>
-    </row>
-    <row r="372">
-      <c r="A372" s="1" t="n">
-        <v>370</v>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>cc-pVDZ</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>prop-2-en-1-ol</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>LUCJ(L=5)</t>
-        </is>
-      </c>
-      <c r="E372" t="n">
-        <v>5</v>
-      </c>
-      <c r="F372" t="inlineStr">
-        <is>
-          <t>random</t>
-        </is>
-      </c>
-      <c r="G372" t="n">
-        <v>-191.9399783754006</v>
-      </c>
-      <c r="H372" t="n">
-        <v>10</v>
-      </c>
-      <c r="I372" t="n">
-        <v>57.50251164207043</v>
-      </c>
-      <c r="J372" t="n">
-        <v>-191.9974808870427</v>
-      </c>
-      <c r="K372" t="n">
-        <v>-191.9364953941601</v>
-      </c>
-      <c r="L372" t="inlineStr"/>
-    </row>
-    <row r="373">
-      <c r="A373" s="1" t="n">
-        <v>371</v>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>cc-pVDZ</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>prop-2-en-1-ol</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>LUCJ(L=5)</t>
-        </is>
-      </c>
-      <c r="E373" t="n">
-        <v>5</v>
-      </c>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>zeroes</t>
-        </is>
-      </c>
-      <c r="G373" t="n">
-        <v>-191.9921928770854</v>
-      </c>
-      <c r="H373" t="n">
-        <v>10</v>
-      </c>
-      <c r="I373" t="n">
-        <v>5.28800995729739</v>
-      </c>
-      <c r="J373" t="n">
-        <v>-191.9974808870427</v>
-      </c>
-      <c r="K373" t="n">
-        <v>-191.9364953941601</v>
-      </c>
-      <c r="L373" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
+++ b/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
@@ -519,13 +519,13 @@
         <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>174.6675498513071</v>
+        <v>174.6675498512786</v>
       </c>
       <c r="J2" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K2" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L2" t="inlineStr"/>
     </row>
@@ -563,13 +563,13 @@
         <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>161.9892498513309</v>
+        <v>161.9892498513025</v>
       </c>
       <c r="J3" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K3" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L3" t="inlineStr"/>
     </row>
@@ -607,13 +607,13 @@
         <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>148.4081798513159</v>
+        <v>148.4081798512875</v>
       </c>
       <c r="J4" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K4" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L4" t="inlineStr"/>
     </row>
@@ -651,13 +651,13 @@
         <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>87.87446985132874</v>
+        <v>87.87446985130032</v>
       </c>
       <c r="J5" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K5" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L5" t="inlineStr"/>
     </row>
@@ -695,13 +695,13 @@
         <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>183.2405498513197</v>
+        <v>183.2405498512912</v>
       </c>
       <c r="J6" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K6" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L6" t="inlineStr"/>
     </row>
@@ -739,13 +739,13 @@
         <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>78.88592985131027</v>
+        <v>78.88592985128184</v>
       </c>
       <c r="J7" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K7" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L7" t="inlineStr"/>
     </row>
@@ -783,13 +783,13 @@
         <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>208.2775198513218</v>
+        <v>208.2775198512934</v>
       </c>
       <c r="J8" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K8" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L8" t="inlineStr"/>
     </row>
@@ -827,13 +827,13 @@
         <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>203.7836098513139</v>
+        <v>203.7836098512855</v>
       </c>
       <c r="J9" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K9" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L9" t="inlineStr"/>
     </row>
@@ -871,13 +871,13 @@
         <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>205.4438198513253</v>
+        <v>205.4438198512969</v>
       </c>
       <c r="J10" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K10" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L10" t="inlineStr"/>
     </row>
@@ -915,13 +915,13 @@
         <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>196.5911898513184</v>
+        <v>196.59118985129</v>
       </c>
       <c r="J11" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K11" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L11" t="inlineStr"/>
     </row>
@@ -959,13 +959,13 @@
         <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>179.3521498513257</v>
+        <v>179.3521498512973</v>
       </c>
       <c r="J12" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K12" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L12" t="inlineStr"/>
     </row>
@@ -1003,13 +1003,13 @@
         <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>47.68020985130761</v>
+        <v>47.68020985127919</v>
       </c>
       <c r="J13" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K13" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L13" t="inlineStr"/>
     </row>
@@ -1047,13 +1047,13 @@
         <v>9</v>
       </c>
       <c r="I14" t="n">
-        <v>212.929899851332</v>
+        <v>212.9298998513036</v>
       </c>
       <c r="J14" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K14" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L14" t="inlineStr"/>
     </row>
@@ -1091,13 +1091,13 @@
         <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>212.0808798513281</v>
+        <v>212.0808798512996</v>
       </c>
       <c r="J15" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K15" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L15" t="inlineStr"/>
     </row>
@@ -1135,13 +1135,13 @@
         <v>9</v>
       </c>
       <c r="I16" t="n">
-        <v>201.4672698513209</v>
+        <v>201.4672698512925</v>
       </c>
       <c r="J16" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K16" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L16" t="inlineStr"/>
     </row>
@@ -1179,13 +1179,13 @@
         <v>9</v>
       </c>
       <c r="I17" t="n">
-        <v>202.7135898513279</v>
+        <v>202.7135898512995</v>
       </c>
       <c r="J17" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K17" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L17" t="inlineStr"/>
     </row>
@@ -1223,13 +1223,13 @@
         <v>9</v>
       </c>
       <c r="I18" t="n">
-        <v>206.2314398513081</v>
+        <v>206.2314398512797</v>
       </c>
       <c r="J18" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K18" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L18" t="inlineStr"/>
     </row>
@@ -1267,13 +1267,13 @@
         <v>9</v>
       </c>
       <c r="I19" t="n">
-        <v>40.9675598513104</v>
+        <v>40.96755985128198</v>
       </c>
       <c r="J19" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K19" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L19" t="inlineStr"/>
     </row>
@@ -1311,13 +1311,13 @@
         <v>9</v>
       </c>
       <c r="I20" t="n">
-        <v>213.8370098513178</v>
+        <v>213.8370098512894</v>
       </c>
       <c r="J20" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K20" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L20" t="inlineStr"/>
     </row>
@@ -1355,13 +1355,13 @@
         <v>9</v>
       </c>
       <c r="I21" t="n">
-        <v>203.2361698513228</v>
+        <v>203.2361698512943</v>
       </c>
       <c r="J21" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K21" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L21" t="inlineStr"/>
     </row>
@@ -1399,13 +1399,13 @@
         <v>9</v>
       </c>
       <c r="I22" t="n">
-        <v>217.9480198513204</v>
+        <v>217.948019851292</v>
       </c>
       <c r="J22" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K22" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L22" t="inlineStr"/>
     </row>
@@ -1443,13 +1443,13 @@
         <v>9</v>
       </c>
       <c r="I23" t="n">
-        <v>216.5417398513227</v>
+        <v>216.5417398512943</v>
       </c>
       <c r="J23" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K23" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L23" t="inlineStr"/>
     </row>
@@ -1487,13 +1487,13 @@
         <v>9</v>
       </c>
       <c r="I24" t="n">
-        <v>207.1036798513148</v>
+        <v>207.1036798512864</v>
       </c>
       <c r="J24" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K24" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L24" t="inlineStr"/>
     </row>
@@ -1531,13 +1531,13 @@
         <v>9</v>
       </c>
       <c r="I25" t="n">
-        <v>43.38156985130581</v>
+        <v>43.38156985127739</v>
       </c>
       <c r="J25" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K25" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L25" t="inlineStr"/>
     </row>
@@ -1575,13 +1575,13 @@
         <v>9</v>
       </c>
       <c r="I26" t="n">
-        <v>209.8763998513107</v>
+        <v>209.8763998512823</v>
       </c>
       <c r="J26" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K26" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L26" t="inlineStr"/>
     </row>
@@ -1619,13 +1619,13 @@
         <v>9</v>
       </c>
       <c r="I27" t="n">
-        <v>173.5600798513133</v>
+        <v>173.5600798512849</v>
       </c>
       <c r="J27" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K27" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L27" t="inlineStr"/>
     </row>
@@ -1663,13 +1663,13 @@
         <v>9</v>
       </c>
       <c r="I28" t="n">
-        <v>215.7015198513079</v>
+        <v>215.7015198512795</v>
       </c>
       <c r="J28" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K28" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L28" t="inlineStr"/>
     </row>
@@ -1707,13 +1707,13 @@
         <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>186.4891198513305</v>
+        <v>186.4891198513021</v>
       </c>
       <c r="J29" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K29" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L29" t="inlineStr"/>
     </row>
@@ -1751,13 +1751,13 @@
         <v>9</v>
       </c>
       <c r="I30" t="n">
-        <v>209.6131698513091</v>
+        <v>209.6131698512806</v>
       </c>
       <c r="J30" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K30" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L30" t="inlineStr"/>
     </row>
@@ -1795,13 +1795,13 @@
         <v>9</v>
       </c>
       <c r="I31" t="n">
-        <v>71.63411985132484</v>
+        <v>71.63411985129642</v>
       </c>
       <c r="J31" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K31" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L31" t="inlineStr"/>
     </row>
@@ -5859,10 +5859,10 @@
         <v>4</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J122" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K122" t="n">
         <v>-56.20522331321214</v>
@@ -5905,10 +5905,10 @@
         <v>4</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J123" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K123" t="n">
         <v>-56.20522331321214</v>
@@ -5951,10 +5951,10 @@
         <v>4</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J124" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K124" t="n">
         <v>-56.20522331321214</v>
@@ -5997,10 +5997,10 @@
         <v>4</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J125" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K125" t="n">
         <v>-56.20522331321214</v>
@@ -6043,10 +6043,10 @@
         <v>4</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J126" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K126" t="n">
         <v>-56.20522331321214</v>
@@ -6089,10 +6089,10 @@
         <v>4</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.002214823126678311</v>
+        <v>-0.002214823119572884</v>
       </c>
       <c r="J127" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K127" t="n">
         <v>-56.20522331321214</v>
@@ -6135,10 +6135,10 @@
         <v>4</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J128" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K128" t="n">
         <v>-56.20522331321214</v>
@@ -6181,10 +6181,10 @@
         <v>4</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J129" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K129" t="n">
         <v>-56.20522331321214</v>
@@ -6227,10 +6227,10 @@
         <v>4</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J130" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K130" t="n">
         <v>-56.20522331321214</v>
@@ -6273,10 +6273,10 @@
         <v>4</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J131" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K131" t="n">
         <v>-56.20522331321214</v>
@@ -6319,10 +6319,10 @@
         <v>4</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J132" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K132" t="n">
         <v>-56.20522331321214</v>
@@ -6365,10 +6365,10 @@
         <v>4</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.002224823127505715</v>
+        <v>-0.002224823120400288</v>
       </c>
       <c r="J133" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K133" t="n">
         <v>-56.20522331321214</v>
@@ -6411,10 +6411,10 @@
         <v>4</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J134" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K134" t="n">
         <v>-56.20522331321214</v>
@@ -6457,10 +6457,10 @@
         <v>4</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J135" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K135" t="n">
         <v>-56.20522331321214</v>
@@ -6503,10 +6503,10 @@
         <v>4</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J136" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K136" t="n">
         <v>-56.20522331321214</v>
@@ -6549,10 +6549,10 @@
         <v>4</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J137" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K137" t="n">
         <v>-56.20522331321214</v>
@@ -6595,10 +6595,10 @@
         <v>4</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J138" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K138" t="n">
         <v>-56.20522331321214</v>
@@ -6641,10 +6641,10 @@
         <v>4</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.002214823126678311</v>
+        <v>-0.002214823119572884</v>
       </c>
       <c r="J139" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K139" t="n">
         <v>-56.20522331321214</v>
@@ -6687,10 +6687,10 @@
         <v>4</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J140" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K140" t="n">
         <v>-56.20522331321214</v>
@@ -6733,10 +6733,10 @@
         <v>4</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J141" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K141" t="n">
         <v>-56.20522331321214</v>
@@ -6779,10 +6779,10 @@
         <v>4</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J142" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K142" t="n">
         <v>-56.20522331321214</v>
@@ -6825,10 +6825,10 @@
         <v>4</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J143" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K143" t="n">
         <v>-56.20522331321214</v>
@@ -6871,10 +6871,10 @@
         <v>4</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J144" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K144" t="n">
         <v>-56.20522331321214</v>
@@ -6917,10 +6917,10 @@
         <v>4</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.002234823128333119</v>
+        <v>-0.002234823121227691</v>
       </c>
       <c r="J145" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K145" t="n">
         <v>-56.20522331321214</v>
@@ -6963,10 +6963,10 @@
         <v>4</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J146" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K146" t="n">
         <v>-56.20522331321214</v>
@@ -7009,10 +7009,10 @@
         <v>4</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J147" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K147" t="n">
         <v>-56.20522331321214</v>
@@ -7055,10 +7055,10 @@
         <v>4</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J148" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K148" t="n">
         <v>-56.20522331321214</v>
@@ -7101,10 +7101,10 @@
         <v>4</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J149" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K149" t="n">
         <v>-56.20522331321214</v>
@@ -7147,10 +7147,10 @@
         <v>4</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.002244823122055095</v>
+        <v>-0.002244823114949668</v>
       </c>
       <c r="J150" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K150" t="n">
         <v>-56.20522331321214</v>
@@ -7193,10 +7193,10 @@
         <v>4</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.002214823126678311</v>
+        <v>-0.002214823119572884</v>
       </c>
       <c r="J151" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K151" t="n">
         <v>-56.20522331321214</v>
@@ -43839,10 +43839,10 @@
         <v>10</v>
       </c>
       <c r="I962" t="n">
-        <v>59.27484704270114</v>
+        <v>59.27484704275798</v>
       </c>
       <c r="J962" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K962" t="n">
         <v>-191.9364953941601</v>
@@ -43883,10 +43883,10 @@
         <v>10</v>
       </c>
       <c r="I963" t="n">
-        <v>53.05039704271053</v>
+        <v>53.05039704276737</v>
       </c>
       <c r="J963" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K963" t="n">
         <v>-191.9364953941601</v>
@@ -43927,10 +43927,10 @@
         <v>10</v>
       </c>
       <c r="I964" t="n">
-        <v>48.88530704272398</v>
+        <v>48.88530704278082</v>
       </c>
       <c r="J964" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K964" t="n">
         <v>-191.9364953941601</v>
@@ -43971,10 +43971,10 @@
         <v>10</v>
       </c>
       <c r="I965" t="n">
-        <v>35.66605704270387</v>
+        <v>35.66605704276071</v>
       </c>
       <c r="J965" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K965" t="n">
         <v>-191.9364953941601</v>
@@ -44015,10 +44015,10 @@
         <v>10</v>
       </c>
       <c r="I966" t="n">
-        <v>60.02949704270577</v>
+        <v>60.02949704276261</v>
       </c>
       <c r="J966" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K966" t="n">
         <v>-191.9364953941601</v>
@@ -44059,10 +44059,10 @@
         <v>10</v>
       </c>
       <c r="I967" t="n">
-        <v>10.13858704271797</v>
+        <v>10.13858704277482</v>
       </c>
       <c r="J967" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K967" t="n">
         <v>-191.9364953941601</v>
@@ -44103,10 +44103,10 @@
         <v>10</v>
       </c>
       <c r="I968" t="n">
-        <v>58.67554704272493</v>
+        <v>58.67554704278177</v>
       </c>
       <c r="J968" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K968" t="n">
         <v>-191.9364953941601</v>
@@ -44147,10 +44147,10 @@
         <v>10</v>
       </c>
       <c r="I969" t="n">
-        <v>59.38197704270465</v>
+        <v>59.38197704276149</v>
       </c>
       <c r="J969" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K969" t="n">
         <v>-191.9364953941601</v>
@@ -44191,10 +44191,10 @@
         <v>10</v>
       </c>
       <c r="I970" t="n">
-        <v>60.85676704270782</v>
+        <v>60.85676704276466</v>
       </c>
       <c r="J970" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K970" t="n">
         <v>-191.9364953941601</v>
@@ -44235,10 +44235,10 @@
         <v>10</v>
       </c>
       <c r="I971" t="n">
-        <v>58.72972704270296</v>
+        <v>58.72972704275981</v>
       </c>
       <c r="J971" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K971" t="n">
         <v>-191.9364953941601</v>
@@ -44279,10 +44279,10 @@
         <v>10</v>
       </c>
       <c r="I972" t="n">
-        <v>59.41868704272224</v>
+        <v>59.41868704277908</v>
       </c>
       <c r="J972" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K972" t="n">
         <v>-191.9364953941601</v>
@@ -44323,10 +44323,10 @@
         <v>10</v>
       </c>
       <c r="I973" t="n">
-        <v>28.09511704271017</v>
+        <v>28.09511704276701</v>
       </c>
       <c r="J973" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K973" t="n">
         <v>-191.9364953941601</v>
@@ -44367,10 +44367,10 @@
         <v>10</v>
       </c>
       <c r="I974" t="n">
-        <v>59.78808704270477</v>
+        <v>59.78808704276162</v>
       </c>
       <c r="J974" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K974" t="n">
         <v>-191.9364953941601</v>
@@ -44411,10 +44411,10 @@
         <v>10</v>
       </c>
       <c r="I975" t="n">
-        <v>58.48213704271643</v>
+        <v>58.48213704277327</v>
       </c>
       <c r="J975" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K975" t="n">
         <v>-191.9364953941601</v>
@@ -44455,10 +44455,10 @@
         <v>10</v>
       </c>
       <c r="I976" t="n">
-        <v>59.53605704272036</v>
+        <v>59.5360570427772</v>
       </c>
       <c r="J976" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K976" t="n">
         <v>-191.9364953941601</v>
@@ -44499,10 +44499,10 @@
         <v>10</v>
       </c>
       <c r="I977" t="n">
-        <v>58.63267704270925</v>
+        <v>58.63267704276609</v>
       </c>
       <c r="J977" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K977" t="n">
         <v>-191.9364953941601</v>
@@ -44543,10 +44543,10 @@
         <v>10</v>
       </c>
       <c r="I978" t="n">
-        <v>58.47426704272607</v>
+        <v>58.47426704278291</v>
       </c>
       <c r="J978" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K978" t="n">
         <v>-191.9364953941601</v>
@@ -44587,10 +44587,10 @@
         <v>10</v>
       </c>
       <c r="I979" t="n">
-        <v>12.03113704272596</v>
+        <v>12.0311370427828</v>
       </c>
       <c r="J979" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K979" t="n">
         <v>-191.9364953941601</v>
@@ -44631,10 +44631,10 @@
         <v>10</v>
       </c>
       <c r="I980" t="n">
-        <v>60.07416704269986</v>
+        <v>60.0741670427567</v>
       </c>
       <c r="J980" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K980" t="n">
         <v>-191.9364953941601</v>
@@ -44675,10 +44675,10 @@
         <v>10</v>
       </c>
       <c r="I981" t="n">
-        <v>58.09547704271267</v>
+        <v>58.09547704276952</v>
       </c>
       <c r="J981" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K981" t="n">
         <v>-191.9364953941601</v>
@@ -44719,10 +44719,10 @@
         <v>10</v>
       </c>
       <c r="I982" t="n">
-        <v>59.42787704270813</v>
+        <v>59.42787704276498</v>
       </c>
       <c r="J982" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K982" t="n">
         <v>-191.9364953941601</v>
@@ -44763,10 +44763,10 @@
         <v>10</v>
       </c>
       <c r="I983" t="n">
-        <v>60.19296704272392</v>
+        <v>60.19296704278077</v>
       </c>
       <c r="J983" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K983" t="n">
         <v>-191.9364953941601</v>
@@ -44807,10 +44807,10 @@
         <v>10</v>
       </c>
       <c r="I984" t="n">
-        <v>58.05750704271873</v>
+        <v>58.05750704277557</v>
       </c>
       <c r="J984" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K984" t="n">
         <v>-191.9364953941601</v>
@@ -44851,10 +44851,10 @@
         <v>10</v>
       </c>
       <c r="I985" t="n">
-        <v>33.19160704270985</v>
+        <v>33.19160704276669</v>
       </c>
       <c r="J985" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K985" t="n">
         <v>-191.9364953941601</v>
@@ -44895,10 +44895,10 @@
         <v>10</v>
       </c>
       <c r="I986" t="n">
-        <v>46.22118704270406</v>
+        <v>46.2211870427609</v>
       </c>
       <c r="J986" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K986" t="n">
         <v>-191.9364953941601</v>
@@ -44939,10 +44939,10 @@
         <v>10</v>
       </c>
       <c r="I987" t="n">
-        <v>60.0499370427201</v>
+        <v>60.04993704277695</v>
       </c>
       <c r="J987" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K987" t="n">
         <v>-191.9364953941601</v>
@@ -44983,10 +44983,10 @@
         <v>10</v>
       </c>
       <c r="I988" t="n">
-        <v>59.32542704272237</v>
+        <v>59.32542704277921</v>
       </c>
       <c r="J988" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K988" t="n">
         <v>-191.9364953941601</v>
@@ -45027,10 +45027,10 @@
         <v>10</v>
       </c>
       <c r="I989" t="n">
-        <v>59.61435704270457</v>
+        <v>59.61435704276141</v>
       </c>
       <c r="J989" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K989" t="n">
         <v>-191.9364953941601</v>
@@ -45071,10 +45071,10 @@
         <v>10</v>
       </c>
       <c r="I990" t="n">
-        <v>60.47604704272658</v>
+        <v>60.47604704278342</v>
       </c>
       <c r="J990" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K990" t="n">
         <v>-191.9364953941601</v>
@@ -45115,10 +45115,10 @@
         <v>10</v>
       </c>
       <c r="I991" t="n">
-        <v>30.66599704271766</v>
+        <v>30.66599704277451</v>
       </c>
       <c r="J991" t="n">
-        <v>-191.9974808870427</v>
+        <v>-191.9974808870428</v>
       </c>
       <c r="K991" t="n">
         <v>-191.9364953941601</v>

--- a/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
+++ b/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
@@ -519,13 +519,13 @@
         <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>174.6675498512786</v>
+        <v>174.6675498513071</v>
       </c>
       <c r="J2" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K2" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L2" t="inlineStr"/>
     </row>
@@ -563,13 +563,13 @@
         <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>161.9892498513025</v>
+        <v>161.9892498513309</v>
       </c>
       <c r="J3" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K3" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L3" t="inlineStr"/>
     </row>
@@ -607,13 +607,13 @@
         <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>148.4081798512875</v>
+        <v>148.4081798513159</v>
       </c>
       <c r="J4" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K4" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L4" t="inlineStr"/>
     </row>
@@ -651,13 +651,13 @@
         <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>87.87446985130032</v>
+        <v>87.87446985132874</v>
       </c>
       <c r="J5" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K5" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L5" t="inlineStr"/>
     </row>
@@ -695,13 +695,13 @@
         <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>183.2405498512912</v>
+        <v>183.2405498513197</v>
       </c>
       <c r="J6" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K6" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L6" t="inlineStr"/>
     </row>
@@ -739,13 +739,13 @@
         <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>78.88592985128184</v>
+        <v>78.88592985131027</v>
       </c>
       <c r="J7" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K7" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L7" t="inlineStr"/>
     </row>
@@ -783,13 +783,13 @@
         <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>208.2775198512934</v>
+        <v>208.2775198513218</v>
       </c>
       <c r="J8" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K8" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L8" t="inlineStr"/>
     </row>
@@ -827,13 +827,13 @@
         <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>203.7836098512855</v>
+        <v>203.7836098513139</v>
       </c>
       <c r="J9" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K9" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L9" t="inlineStr"/>
     </row>
@@ -871,13 +871,13 @@
         <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>205.4438198512969</v>
+        <v>205.4438198513253</v>
       </c>
       <c r="J10" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K10" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L10" t="inlineStr"/>
     </row>
@@ -915,13 +915,13 @@
         <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>196.59118985129</v>
+        <v>196.5911898513184</v>
       </c>
       <c r="J11" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K11" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L11" t="inlineStr"/>
     </row>
@@ -959,13 +959,13 @@
         <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>179.3521498512973</v>
+        <v>179.3521498513257</v>
       </c>
       <c r="J12" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K12" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L12" t="inlineStr"/>
     </row>
@@ -1003,13 +1003,13 @@
         <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>47.68020985127919</v>
+        <v>47.68020985130761</v>
       </c>
       <c r="J13" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K13" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L13" t="inlineStr"/>
     </row>
@@ -1047,13 +1047,13 @@
         <v>9</v>
       </c>
       <c r="I14" t="n">
-        <v>212.9298998513036</v>
+        <v>212.929899851332</v>
       </c>
       <c r="J14" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K14" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L14" t="inlineStr"/>
     </row>
@@ -1091,13 +1091,13 @@
         <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>212.0808798512996</v>
+        <v>212.0808798513281</v>
       </c>
       <c r="J15" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K15" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L15" t="inlineStr"/>
     </row>
@@ -1135,13 +1135,13 @@
         <v>9</v>
       </c>
       <c r="I16" t="n">
-        <v>201.4672698512925</v>
+        <v>201.4672698513209</v>
       </c>
       <c r="J16" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K16" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L16" t="inlineStr"/>
     </row>
@@ -1179,13 +1179,13 @@
         <v>9</v>
       </c>
       <c r="I17" t="n">
-        <v>202.7135898512995</v>
+        <v>202.7135898513279</v>
       </c>
       <c r="J17" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K17" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L17" t="inlineStr"/>
     </row>
@@ -1223,13 +1223,13 @@
         <v>9</v>
       </c>
       <c r="I18" t="n">
-        <v>206.2314398512797</v>
+        <v>206.2314398513081</v>
       </c>
       <c r="J18" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K18" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L18" t="inlineStr"/>
     </row>
@@ -1267,13 +1267,13 @@
         <v>9</v>
       </c>
       <c r="I19" t="n">
-        <v>40.96755985128198</v>
+        <v>40.9675598513104</v>
       </c>
       <c r="J19" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K19" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L19" t="inlineStr"/>
     </row>
@@ -1311,13 +1311,13 @@
         <v>9</v>
       </c>
       <c r="I20" t="n">
-        <v>213.8370098512894</v>
+        <v>213.8370098513178</v>
       </c>
       <c r="J20" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K20" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L20" t="inlineStr"/>
     </row>
@@ -1355,13 +1355,13 @@
         <v>9</v>
       </c>
       <c r="I21" t="n">
-        <v>203.2361698512943</v>
+        <v>203.2361698513228</v>
       </c>
       <c r="J21" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K21" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L21" t="inlineStr"/>
     </row>
@@ -1399,13 +1399,13 @@
         <v>9</v>
       </c>
       <c r="I22" t="n">
-        <v>217.948019851292</v>
+        <v>217.9480198513204</v>
       </c>
       <c r="J22" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K22" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L22" t="inlineStr"/>
     </row>
@@ -1443,13 +1443,13 @@
         <v>9</v>
       </c>
       <c r="I23" t="n">
-        <v>216.5417398512943</v>
+        <v>216.5417398513227</v>
       </c>
       <c r="J23" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K23" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L23" t="inlineStr"/>
     </row>
@@ -1487,13 +1487,13 @@
         <v>9</v>
       </c>
       <c r="I24" t="n">
-        <v>207.1036798512864</v>
+        <v>207.1036798513148</v>
       </c>
       <c r="J24" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K24" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L24" t="inlineStr"/>
     </row>
@@ -1531,13 +1531,13 @@
         <v>9</v>
       </c>
       <c r="I25" t="n">
-        <v>43.38156985127739</v>
+        <v>43.38156985130581</v>
       </c>
       <c r="J25" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K25" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L25" t="inlineStr"/>
     </row>
@@ -1575,13 +1575,13 @@
         <v>9</v>
       </c>
       <c r="I26" t="n">
-        <v>209.8763998512823</v>
+        <v>209.8763998513107</v>
       </c>
       <c r="J26" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K26" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L26" t="inlineStr"/>
     </row>
@@ -1619,13 +1619,13 @@
         <v>9</v>
       </c>
       <c r="I27" t="n">
-        <v>173.5600798512849</v>
+        <v>173.5600798513133</v>
       </c>
       <c r="J27" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K27" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L27" t="inlineStr"/>
     </row>
@@ -1663,13 +1663,13 @@
         <v>9</v>
       </c>
       <c r="I28" t="n">
-        <v>215.7015198512795</v>
+        <v>215.7015198513079</v>
       </c>
       <c r="J28" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K28" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L28" t="inlineStr"/>
     </row>
@@ -1707,13 +1707,13 @@
         <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>186.4891198513021</v>
+        <v>186.4891198513305</v>
       </c>
       <c r="J29" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K29" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L29" t="inlineStr"/>
     </row>
@@ -1751,13 +1751,13 @@
         <v>9</v>
       </c>
       <c r="I30" t="n">
-        <v>209.6131698512806</v>
+        <v>209.6131698513091</v>
       </c>
       <c r="J30" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K30" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L30" t="inlineStr"/>
     </row>
@@ -1795,13 +1795,13 @@
         <v>9</v>
       </c>
       <c r="I31" t="n">
-        <v>71.63411985129642</v>
+        <v>71.63411985132484</v>
       </c>
       <c r="J31" t="n">
         <v>-213.3436138098513</v>
       </c>
       <c r="K31" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="L31" t="inlineStr"/>
     </row>
@@ -5859,10 +5859,10 @@
         <v>4</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J122" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K122" t="n">
         <v>-56.20522331321214</v>
@@ -5905,10 +5905,10 @@
         <v>4</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J123" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K123" t="n">
         <v>-56.20522331321214</v>
@@ -5951,10 +5951,10 @@
         <v>4</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J124" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K124" t="n">
         <v>-56.20522331321214</v>
@@ -5997,10 +5997,10 @@
         <v>4</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J125" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K125" t="n">
         <v>-56.20522331321214</v>
@@ -6043,10 +6043,10 @@
         <v>4</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J126" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K126" t="n">
         <v>-56.20522331321214</v>
@@ -6089,10 +6089,10 @@
         <v>4</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.002214823119572884</v>
+        <v>-0.002214823126678311</v>
       </c>
       <c r="J127" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K127" t="n">
         <v>-56.20522331321214</v>
@@ -6135,10 +6135,10 @@
         <v>4</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J128" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K128" t="n">
         <v>-56.20522331321214</v>
@@ -6181,10 +6181,10 @@
         <v>4</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J129" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K129" t="n">
         <v>-56.20522331321214</v>
@@ -6227,10 +6227,10 @@
         <v>4</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J130" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K130" t="n">
         <v>-56.20522331321214</v>
@@ -6273,10 +6273,10 @@
         <v>4</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J131" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K131" t="n">
         <v>-56.20522331321214</v>
@@ -6319,10 +6319,10 @@
         <v>4</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J132" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K132" t="n">
         <v>-56.20522331321214</v>
@@ -6365,10 +6365,10 @@
         <v>4</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.002224823120400288</v>
+        <v>-0.002224823127505715</v>
       </c>
       <c r="J133" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K133" t="n">
         <v>-56.20522331321214</v>
@@ -6411,10 +6411,10 @@
         <v>4</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J134" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K134" t="n">
         <v>-56.20522331321214</v>
@@ -6457,10 +6457,10 @@
         <v>4</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J135" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K135" t="n">
         <v>-56.20522331321214</v>
@@ -6503,10 +6503,10 @@
         <v>4</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J136" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K136" t="n">
         <v>-56.20522331321214</v>
@@ -6549,10 +6549,10 @@
         <v>4</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J137" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K137" t="n">
         <v>-56.20522331321214</v>
@@ -6595,10 +6595,10 @@
         <v>4</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J138" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K138" t="n">
         <v>-56.20522331321214</v>
@@ -6641,10 +6641,10 @@
         <v>4</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.002214823119572884</v>
+        <v>-0.002214823126678311</v>
       </c>
       <c r="J139" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K139" t="n">
         <v>-56.20522331321214</v>
@@ -6687,10 +6687,10 @@
         <v>4</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J140" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K140" t="n">
         <v>-56.20522331321214</v>
@@ -6733,10 +6733,10 @@
         <v>4</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J141" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K141" t="n">
         <v>-56.20522331321214</v>
@@ -6779,10 +6779,10 @@
         <v>4</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J142" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K142" t="n">
         <v>-56.20522331321214</v>
@@ -6825,10 +6825,10 @@
         <v>4</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J143" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K143" t="n">
         <v>-56.20522331321214</v>
@@ -6871,10 +6871,10 @@
         <v>4</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J144" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K144" t="n">
         <v>-56.20522331321214</v>
@@ -6917,10 +6917,10 @@
         <v>4</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.002234823121227691</v>
+        <v>-0.002234823128333119</v>
       </c>
       <c r="J145" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K145" t="n">
         <v>-56.20522331321214</v>
@@ -6963,10 +6963,10 @@
         <v>4</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J146" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K146" t="n">
         <v>-56.20522331321214</v>
@@ -7009,10 +7009,10 @@
         <v>4</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J147" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K147" t="n">
         <v>-56.20522331321214</v>
@@ -7055,10 +7055,10 @@
         <v>4</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J148" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K148" t="n">
         <v>-56.20522331321214</v>
@@ -7101,10 +7101,10 @@
         <v>4</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J149" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K149" t="n">
         <v>-56.20522331321214</v>
@@ -7147,10 +7147,10 @@
         <v>4</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.002244823114949668</v>
+        <v>-0.002244823122055095</v>
       </c>
       <c r="J150" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K150" t="n">
         <v>-56.20522331321214</v>
@@ -7193,10 +7193,10 @@
         <v>4</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.002214823119572884</v>
+        <v>-0.002214823126678311</v>
       </c>
       <c r="J151" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="K151" t="n">
         <v>-56.20522331321214</v>
@@ -43839,10 +43839,10 @@
         <v>10</v>
       </c>
       <c r="I962" t="n">
-        <v>59.27484704275798</v>
+        <v>59.27484704270114</v>
       </c>
       <c r="J962" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K962" t="n">
         <v>-191.9364953941601</v>
@@ -43883,10 +43883,10 @@
         <v>10</v>
       </c>
       <c r="I963" t="n">
-        <v>53.05039704276737</v>
+        <v>53.05039704271053</v>
       </c>
       <c r="J963" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K963" t="n">
         <v>-191.9364953941601</v>
@@ -43927,10 +43927,10 @@
         <v>10</v>
       </c>
       <c r="I964" t="n">
-        <v>48.88530704278082</v>
+        <v>48.88530704272398</v>
       </c>
       <c r="J964" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K964" t="n">
         <v>-191.9364953941601</v>
@@ -43971,10 +43971,10 @@
         <v>10</v>
       </c>
       <c r="I965" t="n">
-        <v>35.66605704276071</v>
+        <v>35.66605704270387</v>
       </c>
       <c r="J965" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K965" t="n">
         <v>-191.9364953941601</v>
@@ -44015,10 +44015,10 @@
         <v>10</v>
       </c>
       <c r="I966" t="n">
-        <v>60.02949704276261</v>
+        <v>60.02949704270577</v>
       </c>
       <c r="J966" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K966" t="n">
         <v>-191.9364953941601</v>
@@ -44059,10 +44059,10 @@
         <v>10</v>
       </c>
       <c r="I967" t="n">
-        <v>10.13858704277482</v>
+        <v>10.13858704271797</v>
       </c>
       <c r="J967" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K967" t="n">
         <v>-191.9364953941601</v>
@@ -44103,10 +44103,10 @@
         <v>10</v>
       </c>
       <c r="I968" t="n">
-        <v>58.67554704278177</v>
+        <v>58.67554704272493</v>
       </c>
       <c r="J968" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K968" t="n">
         <v>-191.9364953941601</v>
@@ -44147,10 +44147,10 @@
         <v>10</v>
       </c>
       <c r="I969" t="n">
-        <v>59.38197704276149</v>
+        <v>59.38197704270465</v>
       </c>
       <c r="J969" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K969" t="n">
         <v>-191.9364953941601</v>
@@ -44191,10 +44191,10 @@
         <v>10</v>
       </c>
       <c r="I970" t="n">
-        <v>60.85676704276466</v>
+        <v>60.85676704270782</v>
       </c>
       <c r="J970" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K970" t="n">
         <v>-191.9364953941601</v>
@@ -44235,10 +44235,10 @@
         <v>10</v>
       </c>
       <c r="I971" t="n">
-        <v>58.72972704275981</v>
+        <v>58.72972704270296</v>
       </c>
       <c r="J971" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K971" t="n">
         <v>-191.9364953941601</v>
@@ -44279,10 +44279,10 @@
         <v>10</v>
       </c>
       <c r="I972" t="n">
-        <v>59.41868704277908</v>
+        <v>59.41868704272224</v>
       </c>
       <c r="J972" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K972" t="n">
         <v>-191.9364953941601</v>
@@ -44323,10 +44323,10 @@
         <v>10</v>
       </c>
       <c r="I973" t="n">
-        <v>28.09511704276701</v>
+        <v>28.09511704271017</v>
       </c>
       <c r="J973" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K973" t="n">
         <v>-191.9364953941601</v>
@@ -44367,10 +44367,10 @@
         <v>10</v>
       </c>
       <c r="I974" t="n">
-        <v>59.78808704276162</v>
+        <v>59.78808704270477</v>
       </c>
       <c r="J974" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K974" t="n">
         <v>-191.9364953941601</v>
@@ -44411,10 +44411,10 @@
         <v>10</v>
       </c>
       <c r="I975" t="n">
-        <v>58.48213704277327</v>
+        <v>58.48213704271643</v>
       </c>
       <c r="J975" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K975" t="n">
         <v>-191.9364953941601</v>
@@ -44455,10 +44455,10 @@
         <v>10</v>
       </c>
       <c r="I976" t="n">
-        <v>59.5360570427772</v>
+        <v>59.53605704272036</v>
       </c>
       <c r="J976" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K976" t="n">
         <v>-191.9364953941601</v>
@@ -44499,10 +44499,10 @@
         <v>10</v>
       </c>
       <c r="I977" t="n">
-        <v>58.63267704276609</v>
+        <v>58.63267704270925</v>
       </c>
       <c r="J977" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K977" t="n">
         <v>-191.9364953941601</v>
@@ -44543,10 +44543,10 @@
         <v>10</v>
       </c>
       <c r="I978" t="n">
-        <v>58.47426704278291</v>
+        <v>58.47426704272607</v>
       </c>
       <c r="J978" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K978" t="n">
         <v>-191.9364953941601</v>
@@ -44587,10 +44587,10 @@
         <v>10</v>
       </c>
       <c r="I979" t="n">
-        <v>12.0311370427828</v>
+        <v>12.03113704272596</v>
       </c>
       <c r="J979" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K979" t="n">
         <v>-191.9364953941601</v>
@@ -44631,10 +44631,10 @@
         <v>10</v>
       </c>
       <c r="I980" t="n">
-        <v>60.0741670427567</v>
+        <v>60.07416704269986</v>
       </c>
       <c r="J980" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K980" t="n">
         <v>-191.9364953941601</v>
@@ -44675,10 +44675,10 @@
         <v>10</v>
       </c>
       <c r="I981" t="n">
-        <v>58.09547704276952</v>
+        <v>58.09547704271267</v>
       </c>
       <c r="J981" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K981" t="n">
         <v>-191.9364953941601</v>
@@ -44719,10 +44719,10 @@
         <v>10</v>
       </c>
       <c r="I982" t="n">
-        <v>59.42787704276498</v>
+        <v>59.42787704270813</v>
       </c>
       <c r="J982" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K982" t="n">
         <v>-191.9364953941601</v>
@@ -44763,10 +44763,10 @@
         <v>10</v>
       </c>
       <c r="I983" t="n">
-        <v>60.19296704278077</v>
+        <v>60.19296704272392</v>
       </c>
       <c r="J983" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K983" t="n">
         <v>-191.9364953941601</v>
@@ -44807,10 +44807,10 @@
         <v>10</v>
       </c>
       <c r="I984" t="n">
-        <v>58.05750704277557</v>
+        <v>58.05750704271873</v>
       </c>
       <c r="J984" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K984" t="n">
         <v>-191.9364953941601</v>
@@ -44851,10 +44851,10 @@
         <v>10</v>
       </c>
       <c r="I985" t="n">
-        <v>33.19160704276669</v>
+        <v>33.19160704270985</v>
       </c>
       <c r="J985" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K985" t="n">
         <v>-191.9364953941601</v>
@@ -44895,10 +44895,10 @@
         <v>10</v>
       </c>
       <c r="I986" t="n">
-        <v>46.2211870427609</v>
+        <v>46.22118704270406</v>
       </c>
       <c r="J986" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K986" t="n">
         <v>-191.9364953941601</v>
@@ -44939,10 +44939,10 @@
         <v>10</v>
       </c>
       <c r="I987" t="n">
-        <v>60.04993704277695</v>
+        <v>60.0499370427201</v>
       </c>
       <c r="J987" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K987" t="n">
         <v>-191.9364953941601</v>
@@ -44983,10 +44983,10 @@
         <v>10</v>
       </c>
       <c r="I988" t="n">
-        <v>59.32542704277921</v>
+        <v>59.32542704272237</v>
       </c>
       <c r="J988" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K988" t="n">
         <v>-191.9364953941601</v>
@@ -45027,10 +45027,10 @@
         <v>10</v>
       </c>
       <c r="I989" t="n">
-        <v>59.61435704276141</v>
+        <v>59.61435704270457</v>
       </c>
       <c r="J989" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K989" t="n">
         <v>-191.9364953941601</v>
@@ -45071,10 +45071,10 @@
         <v>10</v>
       </c>
       <c r="I990" t="n">
-        <v>60.47604704278342</v>
+        <v>60.47604704272658</v>
       </c>
       <c r="J990" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K990" t="n">
         <v>-191.9364953941601</v>
@@ -45115,10 +45115,10 @@
         <v>10</v>
       </c>
       <c r="I991" t="n">
-        <v>30.66599704277451</v>
+        <v>30.66599704271766</v>
       </c>
       <c r="J991" t="n">
-        <v>-191.9974808870428</v>
+        <v>-191.9974808870427</v>
       </c>
       <c r="K991" t="n">
         <v>-191.9364953941601</v>

--- a/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
+++ b/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
@@ -530,7 +530,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K2" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
@@ -577,7 +577,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K3" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
@@ -624,7 +624,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K4" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
@@ -671,7 +671,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K5" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
@@ -718,7 +718,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K6" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
@@ -765,7 +765,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K7" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
@@ -812,7 +812,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K8" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
@@ -859,7 +859,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K9" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
@@ -906,7 +906,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K10" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
@@ -953,7 +953,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K11" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
@@ -1000,7 +1000,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K12" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
@@ -1047,7 +1047,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K13" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
@@ -1094,7 +1094,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K14" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
@@ -1141,7 +1141,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K15" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
@@ -1188,7 +1188,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K16" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
@@ -1235,7 +1235,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K17" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
@@ -1282,7 +1282,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K18" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
@@ -1329,7 +1329,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K19" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
@@ -1376,7 +1376,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K20" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
@@ -1423,7 +1423,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K21" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
@@ -1470,7 +1470,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K22" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
@@ -1517,7 +1517,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K23" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
@@ -1564,7 +1564,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K24" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
@@ -1611,7 +1611,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K25" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
@@ -1658,7 +1658,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K26" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
@@ -1705,7 +1705,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K27" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
@@ -1752,7 +1752,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K28" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
@@ -1799,7 +1799,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K29" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
@@ -1846,7 +1846,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K30" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
@@ -1893,7 +1893,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="K31" t="n">
-        <v>-213.1164694544959</v>
+        <v>-213.116469454496</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="n">
@@ -6227,7 +6227,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J122" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K122" t="n">
         <v>-56.20522331321214</v>
@@ -6276,7 +6276,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J123" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K123" t="n">
         <v>-56.20522331321214</v>
@@ -6325,7 +6325,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J124" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K124" t="n">
         <v>-56.20522331321214</v>
@@ -6374,7 +6374,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J125" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K125" t="n">
         <v>-56.20522331321214</v>
@@ -6423,7 +6423,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J126" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K126" t="n">
         <v>-56.20522331321214</v>
@@ -6472,7 +6472,7 @@
         <v>-301.3674892665321</v>
       </c>
       <c r="J127" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K127" t="n">
         <v>-56.20522331321214</v>
@@ -6521,7 +6521,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J128" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K128" t="n">
         <v>-56.20522331321214</v>
@@ -6570,7 +6570,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J129" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K129" t="n">
         <v>-56.20522331321214</v>
@@ -6619,7 +6619,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J130" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K130" t="n">
         <v>-56.20522331321214</v>
@@ -6668,7 +6668,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J131" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K131" t="n">
         <v>-56.20522331321214</v>
@@ -6717,7 +6717,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J132" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K132" t="n">
         <v>-56.20522331321214</v>
@@ -6766,7 +6766,7 @@
         <v>-301.3674992665329</v>
       </c>
       <c r="J133" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K133" t="n">
         <v>-56.20522331321214</v>
@@ -6815,7 +6815,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J134" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K134" t="n">
         <v>-56.20522331321214</v>
@@ -6864,7 +6864,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J135" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K135" t="n">
         <v>-56.20522331321214</v>
@@ -6913,7 +6913,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J136" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K136" t="n">
         <v>-56.20522331321214</v>
@@ -6962,7 +6962,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J137" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K137" t="n">
         <v>-56.20522331321214</v>
@@ -7011,7 +7011,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J138" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K138" t="n">
         <v>-56.20522331321214</v>
@@ -7060,7 +7060,7 @@
         <v>-301.3674892665321</v>
       </c>
       <c r="J139" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K139" t="n">
         <v>-56.20522331321214</v>
@@ -7109,7 +7109,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J140" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K140" t="n">
         <v>-56.20522331321214</v>
@@ -7158,7 +7158,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J141" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K141" t="n">
         <v>-56.20522331321214</v>
@@ -7207,7 +7207,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J142" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K142" t="n">
         <v>-56.20522331321214</v>
@@ -7256,7 +7256,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J143" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K143" t="n">
         <v>-56.20522331321214</v>
@@ -7305,7 +7305,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J144" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K144" t="n">
         <v>-56.20522331321214</v>
@@ -7354,7 +7354,7 @@
         <v>-301.3675092665338</v>
       </c>
       <c r="J145" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K145" t="n">
         <v>-56.20522331321214</v>
@@ -7403,7 +7403,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J146" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K146" t="n">
         <v>-56.20522331321214</v>
@@ -7452,7 +7452,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J147" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K147" t="n">
         <v>-56.20522331321214</v>
@@ -7501,7 +7501,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J148" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K148" t="n">
         <v>-56.20522331321214</v>
@@ -7550,7 +7550,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J149" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K149" t="n">
         <v>-56.20522331321214</v>
@@ -7599,7 +7599,7 @@
         <v>-301.3675192665275</v>
       </c>
       <c r="J150" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K150" t="n">
         <v>-56.20522331321214</v>
@@ -7648,7 +7648,7 @@
         <v>-301.3674892665321</v>
       </c>
       <c r="J151" t="n">
-        <v>-56.20530663517687</v>
+        <v>-56.20530663517688</v>
       </c>
       <c r="K151" t="n">
         <v>-56.20522331321214</v>

--- a/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
+++ b/machine_learning/injection/DDLUCJ-experiment-pipeline/repostprocess.xlsx
@@ -547,7 +547,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J2" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
@@ -557,11 +557,11 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>52.47680550405676</v>
+        <v>52.47680550408518</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>-174.6675498512786</v>
+        <v>-174.6675498513071</v>
       </c>
       <c r="Q2" t="n">
         <v>-191.3796957923353</v>
@@ -604,7 +604,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J3" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
@@ -614,11 +614,11 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>65.15510550403292</v>
+        <v>65.15510550406134</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>-161.9892498513025</v>
+        <v>-161.9892498513309</v>
       </c>
       <c r="Q3" t="n">
         <v>-178.7013957923591</v>
@@ -661,7 +661,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J4" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
@@ -671,11 +671,11 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>78.73617550404788</v>
+        <v>78.7361755040763</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>-148.4081798512875</v>
+        <v>-148.4081798513159</v>
       </c>
       <c r="Q4" t="n">
         <v>-165.1203257923441</v>
@@ -718,7 +718,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J5" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
@@ -728,11 +728,11 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>139.2698855040351</v>
+        <v>139.2698855040635</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>-87.87446985130032</v>
+        <v>-87.87446985132874</v>
       </c>
       <c r="Q5" t="n">
         <v>-104.586615792357</v>
@@ -775,7 +775,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J6" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
@@ -785,11 +785,11 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>43.90380550404416</v>
+        <v>43.90380550407258</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>-183.2405498512912</v>
+        <v>-183.2405498513197</v>
       </c>
       <c r="Q6" t="n">
         <v>-199.9526957923479</v>
@@ -832,7 +832,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J7" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
@@ -842,11 +842,11 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>148.2584255040535</v>
+        <v>148.258425504082</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>-78.88592985128184</v>
+        <v>-78.88592985131027</v>
       </c>
       <c r="Q7" t="n">
         <v>-95.59807579233848</v>
@@ -889,7 +889,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J8" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
@@ -899,11 +899,11 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>18.866835504042</v>
+        <v>18.86683550407042</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>-208.2775198512934</v>
+        <v>-208.2775198513218</v>
       </c>
       <c r="Q8" t="n">
         <v>-224.98966579235</v>
@@ -946,7 +946,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J9" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
@@ -956,11 +956,11 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>23.36074550404987</v>
+        <v>23.3607455040783</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>-203.7836098512855</v>
+        <v>-203.7836098513139</v>
       </c>
       <c r="Q9" t="n">
         <v>-220.4957557923422</v>
@@ -1003,7 +1003,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J10" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
@@ -1013,11 +1013,11 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>21.7005355040385</v>
+        <v>21.70053550406692</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>-205.4438198512969</v>
+        <v>-205.4438198513253</v>
       </c>
       <c r="Q10" t="n">
         <v>-222.1559657923535</v>
@@ -1060,7 +1060,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J11" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
@@ -1070,11 +1070,11 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>30.55316550404541</v>
+        <v>30.55316550407383</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>-196.59118985129</v>
+        <v>-196.5911898513184</v>
       </c>
       <c r="Q11" t="n">
         <v>-213.3033357923466</v>
@@ -1117,7 +1117,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J12" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
@@ -1127,11 +1127,11 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>47.79220550403807</v>
+        <v>47.79220550406649</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>-179.3521498512973</v>
+        <v>-179.3521498513257</v>
       </c>
       <c r="Q12" t="n">
         <v>-196.064295792354</v>
@@ -1174,7 +1174,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J13" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
@@ -1184,11 +1184,11 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>179.4641455040562</v>
+        <v>179.4641455040846</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>-47.68020985127919</v>
+        <v>-47.68020985130761</v>
       </c>
       <c r="Q13" t="n">
         <v>-64.39235579233582</v>
@@ -1231,7 +1231,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J14" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
@@ -1241,11 +1241,11 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>14.21445550403178</v>
+        <v>14.2144555040602</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>-212.9298998513036</v>
+        <v>-212.929899851332</v>
       </c>
       <c r="Q14" t="n">
         <v>-229.6420457923602</v>
@@ -1288,7 +1288,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J15" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
@@ -1298,11 +1298,11 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>15.06347550403575</v>
+        <v>15.06347550406417</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>-212.0808798512996</v>
+        <v>-212.0808798513281</v>
       </c>
       <c r="Q15" t="n">
         <v>-228.7930257923563</v>
@@ -1345,7 +1345,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J16" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
@@ -1355,11 +1355,11 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>25.67708550404291</v>
+        <v>25.67708550407133</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>-201.4672698512925</v>
+        <v>-201.4672698513209</v>
       </c>
       <c r="Q16" t="n">
         <v>-218.1794157923491</v>
@@ -1402,7 +1402,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J17" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
@@ -1412,11 +1412,11 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>24.43076550403589</v>
+        <v>24.43076550406431</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>-202.7135898512995</v>
+        <v>-202.7135898513279</v>
       </c>
       <c r="Q17" t="n">
         <v>-219.4257357923561</v>
@@ -1459,7 +1459,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J18" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
@@ -1469,11 +1469,11 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>20.91291550405572</v>
+        <v>20.91291550408414</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>-206.2314398512797</v>
+        <v>-206.2314398513081</v>
       </c>
       <c r="Q18" t="n">
         <v>-222.9435857923363</v>
@@ -1516,7 +1516,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J19" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
@@ -1526,11 +1526,11 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>186.1767955040534</v>
+        <v>186.1767955040818</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>-40.96755985128198</v>
+        <v>-40.9675598513104</v>
       </c>
       <c r="Q19" t="n">
         <v>-57.67970579233861</v>
@@ -1573,7 +1573,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J20" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
@@ -1583,11 +1583,11 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>13.307345504046</v>
+        <v>13.30734550407442</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>-213.8370098512894</v>
+        <v>-213.8370098513178</v>
       </c>
       <c r="Q20" t="n">
         <v>-230.549155792346</v>
@@ -1630,7 +1630,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J21" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
@@ -1640,11 +1640,11 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>23.90818550404106</v>
+        <v>23.90818550406948</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>-203.2361698512943</v>
+        <v>-203.2361698513228</v>
       </c>
       <c r="Q21" t="n">
         <v>-219.948315792351</v>
@@ -1687,7 +1687,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J22" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
@@ -1697,11 +1697,11 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>9.196335504043418</v>
+        <v>9.19633550407184</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>-217.948019851292</v>
+        <v>-217.9480198513204</v>
       </c>
       <c r="Q22" t="n">
         <v>-234.6601657923486</v>
@@ -1744,7 +1744,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J23" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
@@ -1754,11 +1754,11 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>10.60261550404107</v>
+        <v>10.60261550406949</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>-216.5417398512943</v>
+        <v>-216.5417398513227</v>
       </c>
       <c r="Q23" t="n">
         <v>-233.253885792351</v>
@@ -1801,7 +1801,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J24" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
@@ -1811,11 +1811,11 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>20.04067550404898</v>
+        <v>20.0406755040774</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>-207.1036798512864</v>
+        <v>-207.1036798513148</v>
       </c>
       <c r="Q24" t="n">
         <v>-223.815825792343</v>
@@ -1858,7 +1858,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J25" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
@@ -1868,11 +1868,11 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>183.762785504058</v>
+        <v>183.7627855040864</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>-43.38156985127739</v>
+        <v>-43.38156985130581</v>
       </c>
       <c r="Q25" t="n">
         <v>-60.09371579233402</v>
@@ -1915,7 +1915,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J26" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
@@ -1925,11 +1925,11 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>17.26795550405313</v>
+        <v>17.26795550408156</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>-209.8763998512823</v>
+        <v>-209.8763998513107</v>
       </c>
       <c r="Q26" t="n">
         <v>-226.5885457923389</v>
@@ -1972,7 +1972,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J27" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
@@ -1982,11 +1982,11 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>53.58427550405054</v>
+        <v>53.58427550407896</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>-173.5600798512849</v>
+        <v>-173.5600798513133</v>
       </c>
       <c r="Q27" t="n">
         <v>-190.2722257923415</v>
@@ -2029,7 +2029,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J28" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
@@ -2039,11 +2039,11 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>11.44283550405589</v>
+        <v>11.44283550408431</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>-215.7015198512795</v>
+        <v>-215.7015198513079</v>
       </c>
       <c r="Q28" t="n">
         <v>-232.4136657923361</v>
@@ -2086,7 +2086,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J29" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
@@ -2096,11 +2096,11 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>40.65523550403327</v>
+        <v>40.65523550406169</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>-186.4891198513021</v>
+        <v>-186.4891198513305</v>
       </c>
       <c r="Q29" t="n">
         <v>-203.2012657923588</v>
@@ -2143,7 +2143,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J30" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
@@ -2153,11 +2153,11 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>17.53118550405475</v>
+        <v>17.53118550408317</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>-209.6131698512806</v>
+        <v>-209.6131698513091</v>
       </c>
       <c r="Q30" t="n">
         <v>-226.3253157923373</v>
@@ -2200,7 +2200,7 @@
         <v>-213.3436138098513</v>
       </c>
       <c r="J31" t="n">
-        <v>-213.116469454496</v>
+        <v>-213.1164694544959</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
@@ -2210,11 +2210,11 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>155.510235504039</v>
+        <v>155.5102355040674</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>-71.63411985129642</v>
+        <v>-71.63411985132484</v>
       </c>
       <c r="Q31" t="n">
         <v>-88.34626579235305</v>
@@ -7504,7 +7504,7 @@
         <v>4</v>
       </c>
       <c r="I122" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J122" t="n">
         <v>-56.20522331321214</v>
@@ -7525,7 +7525,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P122" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q122" t="n">
         <v>301.3675192665275</v>
@@ -7565,7 +7565,7 @@
         <v>4</v>
       </c>
       <c r="I123" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J123" t="n">
         <v>-56.20522331321214</v>
@@ -7586,7 +7586,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P123" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q123" t="n">
         <v>301.3675192665275</v>
@@ -7626,7 +7626,7 @@
         <v>4</v>
       </c>
       <c r="I124" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J124" t="n">
         <v>-56.20522331321214</v>
@@ -7647,7 +7647,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P124" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q124" t="n">
         <v>301.3675192665275</v>
@@ -7687,7 +7687,7 @@
         <v>4</v>
       </c>
       <c r="I125" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J125" t="n">
         <v>-56.20522331321214</v>
@@ -7708,7 +7708,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P125" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q125" t="n">
         <v>301.3675192665275</v>
@@ -7748,7 +7748,7 @@
         <v>4</v>
       </c>
       <c r="I126" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J126" t="n">
         <v>-56.20522331321214</v>
@@ -7769,7 +7769,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P126" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q126" t="n">
         <v>301.3675192665275</v>
@@ -7809,7 +7809,7 @@
         <v>4</v>
       </c>
       <c r="I127" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J127" t="n">
         <v>-56.20522331321214</v>
@@ -7830,7 +7830,7 @@
         <v>-3.216402433281473e-05</v>
       </c>
       <c r="P127" t="n">
-        <v>0.002214823119572884</v>
+        <v>0.002214823126678311</v>
       </c>
       <c r="Q127" t="n">
         <v>301.3674892665321</v>
@@ -7870,7 +7870,7 @@
         <v>4</v>
       </c>
       <c r="I128" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J128" t="n">
         <v>-56.20522331321214</v>
@@ -7891,7 +7891,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P128" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q128" t="n">
         <v>301.3675192665275</v>
@@ -7931,7 +7931,7 @@
         <v>4</v>
       </c>
       <c r="I129" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J129" t="n">
         <v>-56.20522331321214</v>
@@ -7952,7 +7952,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P129" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q129" t="n">
         <v>301.3675192665275</v>
@@ -7992,7 +7992,7 @@
         <v>4</v>
       </c>
       <c r="I130" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J130" t="n">
         <v>-56.20522331321214</v>
@@ -8013,7 +8013,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P130" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q130" t="n">
         <v>301.3675192665275</v>
@@ -8053,7 +8053,7 @@
         <v>4</v>
       </c>
       <c r="I131" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J131" t="n">
         <v>-56.20522331321214</v>
@@ -8074,7 +8074,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P131" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q131" t="n">
         <v>301.3675192665275</v>
@@ -8114,7 +8114,7 @@
         <v>4</v>
       </c>
       <c r="I132" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J132" t="n">
         <v>-56.20522331321214</v>
@@ -8135,7 +8135,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P132" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q132" t="n">
         <v>301.3675192665275</v>
@@ -8175,7 +8175,7 @@
         <v>4</v>
       </c>
       <c r="I133" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J133" t="n">
         <v>-56.20522331321214</v>
@@ -8196,7 +8196,7 @@
         <v>-2.216402350541102e-05</v>
       </c>
       <c r="P133" t="n">
-        <v>0.002224823120400288</v>
+        <v>0.002224823127505715</v>
       </c>
       <c r="Q133" t="n">
         <v>301.3674992665329</v>
@@ -8236,7 +8236,7 @@
         <v>4</v>
       </c>
       <c r="I134" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J134" t="n">
         <v>-56.20522331321214</v>
@@ -8257,7 +8257,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P134" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q134" t="n">
         <v>301.3675192665275</v>
@@ -8297,7 +8297,7 @@
         <v>4</v>
       </c>
       <c r="I135" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J135" t="n">
         <v>-56.20522331321214</v>
@@ -8318,7 +8318,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P135" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q135" t="n">
         <v>301.3675192665275</v>
@@ -8358,7 +8358,7 @@
         <v>4</v>
       </c>
       <c r="I136" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J136" t="n">
         <v>-56.20522331321214</v>
@@ -8379,7 +8379,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P136" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q136" t="n">
         <v>301.3675192665275</v>
@@ -8419,7 +8419,7 @@
         <v>4</v>
       </c>
       <c r="I137" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J137" t="n">
         <v>-56.20522331321214</v>
@@ -8440,7 +8440,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P137" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q137" t="n">
         <v>301.3675192665275</v>
@@ -8480,7 +8480,7 @@
         <v>4</v>
       </c>
       <c r="I138" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J138" t="n">
         <v>-56.20522331321214</v>
@@ -8501,7 +8501,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P138" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q138" t="n">
         <v>301.3675192665275</v>
@@ -8541,7 +8541,7 @@
         <v>4</v>
       </c>
       <c r="I139" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J139" t="n">
         <v>-56.20522331321214</v>
@@ -8562,7 +8562,7 @@
         <v>-3.216402433281473e-05</v>
       </c>
       <c r="P139" t="n">
-        <v>0.002214823119572884</v>
+        <v>0.002214823126678311</v>
       </c>
       <c r="Q139" t="n">
         <v>301.3674892665321</v>
@@ -8602,7 +8602,7 @@
         <v>4</v>
       </c>
       <c r="I140" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J140" t="n">
         <v>-56.20522331321214</v>
@@ -8623,7 +8623,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P140" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q140" t="n">
         <v>301.3675192665275</v>
@@ -8663,7 +8663,7 @@
         <v>4</v>
       </c>
       <c r="I141" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J141" t="n">
         <v>-56.20522331321214</v>
@@ -8684,7 +8684,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P141" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q141" t="n">
         <v>301.3675192665275</v>
@@ -8724,7 +8724,7 @@
         <v>4</v>
       </c>
       <c r="I142" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J142" t="n">
         <v>-56.20522331321214</v>
@@ -8745,7 +8745,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P142" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q142" t="n">
         <v>301.3675192665275</v>
@@ -8785,7 +8785,7 @@
         <v>4</v>
       </c>
       <c r="I143" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J143" t="n">
         <v>-56.20522331321214</v>
@@ -8806,7 +8806,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P143" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q143" t="n">
         <v>301.3675192665275</v>
@@ -8846,7 +8846,7 @@
         <v>4</v>
       </c>
       <c r="I144" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J144" t="n">
         <v>-56.20522331321214</v>
@@ -8867,7 +8867,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P144" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q144" t="n">
         <v>301.3675192665275</v>
@@ -8907,7 +8907,7 @@
         <v>4</v>
       </c>
       <c r="I145" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J145" t="n">
         <v>-56.20522331321214</v>
@@ -8928,7 +8928,7 @@
         <v>-1.216402267800731e-05</v>
       </c>
       <c r="P145" t="n">
-        <v>0.002234823121227691</v>
+        <v>0.002234823128333119</v>
       </c>
       <c r="Q145" t="n">
         <v>301.3675092665338</v>
@@ -8968,7 +8968,7 @@
         <v>4</v>
       </c>
       <c r="I146" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J146" t="n">
         <v>-56.20522331321214</v>
@@ -8989,7 +8989,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P146" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q146" t="n">
         <v>301.3675192665275</v>
@@ -9029,7 +9029,7 @@
         <v>4</v>
       </c>
       <c r="I147" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J147" t="n">
         <v>-56.20522331321214</v>
@@ -9050,7 +9050,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P147" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q147" t="n">
         <v>301.3675192665275</v>
@@ -9090,7 +9090,7 @@
         <v>4</v>
       </c>
       <c r="I148" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J148" t="n">
         <v>-56.20522331321214</v>
@@ -9111,7 +9111,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P148" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q148" t="n">
         <v>301.3675192665275</v>
@@ -9151,7 +9151,7 @@
         <v>4</v>
       </c>
       <c r="I149" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J149" t="n">
         <v>-56.20522331321214</v>
@@ -9172,7 +9172,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P149" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q149" t="n">
         <v>301.3675192665275</v>
@@ -9212,7 +9212,7 @@
         <v>4</v>
       </c>
       <c r="I150" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J150" t="n">
         <v>-56.20522331321214</v>
@@ -9233,7 +9233,7 @@
         <v>-2.164028956030961e-06</v>
       </c>
       <c r="P150" t="n">
-        <v>0.002244823114949668</v>
+        <v>0.002244823122055095</v>
       </c>
       <c r="Q150" t="n">
         <v>301.3675192665275</v>
@@ -9273,7 +9273,7 @@
         <v>4</v>
       </c>
       <c r="I151" t="n">
-        <v>-56.20530663517688</v>
+        <v>-56.20530663517687</v>
       </c>
       <c r="J151" t="n">
         <v>-56.20522331321214</v>
@@ -9294,7 +9294,7 @@
         <v>-3.216402433281473e-05</v>
       </c>
       <c r="P151" t="n">
-        <v>0.002214823119572884</v>
+        <v>0.002214823126678311</v>
       </c>
       <c r="Q151" t="n">
         <v>301.3674892665321</v>
@@ -9349,7 +9349,7 @@
         <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O152" t="n">
         <v>-1.631742208019205e-05</v>
@@ -9410,7 +9410,7 @@
         <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O153" t="n">
         <v>-1.631742208019205e-05</v>
@@ -9471,7 +9471,7 @@
         <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O154" t="n">
         <v>-1.631742208019205e-05</v>
@@ -9532,7 +9532,7 @@
         <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O155" t="n">
         <v>-1.631742208019205e-05</v>
@@ -9593,7 +9593,7 @@
         <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O156" t="n">
         <v>-1.631742208019205e-05</v>
@@ -9654,7 +9654,7 @@
         <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>11.11979359664872</v>
+        <v>11.11979359665582</v>
       </c>
       <c r="O157" t="n">
         <v>-0.0001763174211077967</v>
@@ -9715,7 +9715,7 @@
         <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O158" t="n">
         <v>-1.631742208019205e-05</v>
@@ -9776,7 +9776,7 @@
         <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O159" t="n">
         <v>-1.631742208019205e-05</v>
@@ -9837,7 +9837,7 @@
         <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O160" t="n">
         <v>-1.631742208019205e-05</v>
@@ -9898,7 +9898,7 @@
         <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O161" t="n">
         <v>-1.631742208019205e-05</v>
@@ -9959,7 +9959,7 @@
         <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O162" t="n">
         <v>-1.631742208019205e-05</v>
@@ -10020,7 +10020,7 @@
         <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>11.11984359664575</v>
+        <v>11.11984359665286</v>
       </c>
       <c r="O163" t="n">
         <v>-0.0001263174240762055</v>
@@ -10081,7 +10081,7 @@
         <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O164" t="n">
         <v>-1.631742208019205e-05</v>
@@ -10142,7 +10142,7 @@
         <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O165" t="n">
         <v>-1.631742208019205e-05</v>
@@ -10203,7 +10203,7 @@
         <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O166" t="n">
         <v>-1.631742208019205e-05</v>
@@ -10264,7 +10264,7 @@
         <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O167" t="n">
         <v>-1.631742208019205e-05</v>
@@ -10325,7 +10325,7 @@
         <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O168" t="n">
         <v>-1.631742208019205e-05</v>
@@ -10386,7 +10386,7 @@
         <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>11.11987359664823</v>
+        <v>11.11987359665534</v>
       </c>
       <c r="O169" t="n">
         <v>-9.631742159399437e-05</v>
@@ -10447,7 +10447,7 @@
         <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O170" t="n">
         <v>-1.631742208019205e-05</v>
@@ -10508,7 +10508,7 @@
         <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O171" t="n">
         <v>-1.631742208019205e-05</v>
@@ -10569,7 +10569,7 @@
         <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O172" t="n">
         <v>-1.631742208019205e-05</v>
@@ -10630,7 +10630,7 @@
         <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O173" t="n">
         <v>-1.631742208019205e-05</v>
@@ -10691,7 +10691,7 @@
         <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O174" t="n">
         <v>-1.631742208019205e-05</v>
@@ -10752,7 +10752,7 @@
         <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>11.11990359664361</v>
+        <v>11.11990359665072</v>
       </c>
       <c r="O175" t="n">
         <v>-6.63174262172106e-05</v>
@@ -10813,7 +10813,7 @@
         <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O176" t="n">
         <v>-1.631742208019205e-05</v>
@@ -10874,7 +10874,7 @@
         <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O177" t="n">
         <v>-1.631742208019205e-05</v>
@@ -10935,7 +10935,7 @@
         <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O178" t="n">
         <v>-1.631742208019205e-05</v>
@@ -10996,7 +10996,7 @@
         <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O179" t="n">
         <v>-1.631742208019205e-05</v>
@@ -11057,7 +11057,7 @@
         <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>11.11995359664775</v>
+        <v>11.11995359665485</v>
       </c>
       <c r="O180" t="n">
         <v>-1.631742208019205e-05</v>
@@ -11118,7 +11118,7 @@
         <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>11.11983359664492</v>
+        <v>11.11983359665203</v>
       </c>
       <c r="O181" t="n">
         <v>-0.0001363174249036092</v>
@@ -54017,7 +54017,7 @@
         <v>0</v>
       </c>
       <c r="N902" t="n">
-        <v>133.8007811942816</v>
+        <v>133.8007811942532</v>
       </c>
       <c r="O902" t="inlineStr"/>
       <c r="P902" t="n">
@@ -54074,7 +54074,7 @@
         <v>0</v>
       </c>
       <c r="N903" t="n">
-        <v>30.60974119426874</v>
+        <v>30.60974119424031</v>
       </c>
       <c r="O903" t="inlineStr"/>
       <c r="P903" t="n">
@@ -54131,7 +54131,7 @@
         <v>0</v>
       </c>
       <c r="N904" t="n">
-        <v>68.95023119429311</v>
+        <v>68.95023119426469</v>
       </c>
       <c r="O904" t="inlineStr"/>
       <c r="P904" t="n">
@@ -54188,7 +54188,7 @@
         <v>0</v>
       </c>
       <c r="N905" t="n">
-        <v>18.92639119427031</v>
+        <v>18.92639119424189</v>
       </c>
       <c r="O905" t="inlineStr"/>
       <c r="P905" t="n">
@@ -54245,7 +54245,7 @@
         <v>0</v>
       </c>
       <c r="N906" t="n">
-        <v>2.261601194277318</v>
+        <v>2.261601194248897</v>
       </c>
       <c r="O906" t="inlineStr"/>
       <c r="P906" t="n">
@@ -54302,7 +54302,7 @@
         <v>0</v>
       </c>
       <c r="N907" t="n">
-        <v>211.3868211942815</v>
+        <v>211.3868211942531</v>
       </c>
       <c r="O907" t="inlineStr"/>
       <c r="P907" t="n">
@@ -54359,7 +54359,7 @@
         <v>0</v>
       </c>
       <c r="N908" t="n">
-        <v>10.55412119427501</v>
+        <v>10.55412119424659</v>
       </c>
       <c r="O908" t="inlineStr"/>
       <c r="P908" t="n">
@@ -54416,7 +54416,7 @@
         <v>0</v>
       </c>
       <c r="N909" t="n">
-        <v>14.47989119427007</v>
+        <v>14.47989119424165</v>
       </c>
       <c r="O909" t="inlineStr"/>
       <c r="P909" t="n">
@@ -54473,7 +54473,7 @@
         <v>0</v>
       </c>
       <c r="N910" t="n">
-        <v>0.2617111942697647</v>
+        <v>0.261711194241343</v>
       </c>
       <c r="O910" t="inlineStr"/>
       <c r="P910" t="n">
@@ -54530,7 +54530,7 @@
         <v>0</v>
       </c>
       <c r="N911" t="n">
-        <v>37.93545119427222</v>
+        <v>37.9354511942438</v>
       </c>
       <c r="O911" t="inlineStr"/>
       <c r="P911" t="n">
@@ -54587,7 +54587,7 @@
         <v>0</v>
       </c>
       <c r="N912" t="n">
-        <v>3.427621194276753</v>
+        <v>3.427621194248331</v>
       </c>
       <c r="O912" t="inlineStr"/>
       <c r="P912" t="n">
@@ -54644,7 +54644,7 @@
         <v>0</v>
       </c>
       <c r="N913" t="n">
-        <v>212.6960611942934</v>
+        <v>212.696061194265</v>
       </c>
       <c r="O913" t="inlineStr"/>
       <c r="P913" t="n">
@@ -54701,7 +54701,7 @@
         <v>0</v>
       </c>
       <c r="N914" t="n">
-        <v>7.347691194269146</v>
+        <v>7.347691194240724</v>
       </c>
       <c r="O914" t="inlineStr"/>
       <c r="P914" t="n">
@@ -54758,7 +54758,7 @@
         <v>0</v>
       </c>
       <c r="N915" t="n">
-        <v>9.420881194273534</v>
+        <v>9.420881194245112</v>
       </c>
       <c r="O915" t="inlineStr"/>
       <c r="P915" t="n">
@@ -54815,7 +54815,7 @@
         <v>0</v>
       </c>
       <c r="N916" t="n">
-        <v>11.76894119427629</v>
+        <v>11.76894119424787</v>
       </c>
       <c r="O916" t="inlineStr"/>
       <c r="P916" t="n">
@@ -54872,7 +54872,7 @@
         <v>0</v>
       </c>
       <c r="N917" t="n">
-        <v>32.74884119429089</v>
+        <v>32.74884119426247</v>
       </c>
       <c r="O917" t="inlineStr"/>
       <c r="P917" t="n">
@@ -54929,7 +54929,7 @@
         <v>0</v>
       </c>
       <c r="N918" t="n">
-        <v>4.544831194266408</v>
+        <v>4.544831194237986</v>
       </c>
       <c r="O918" t="inlineStr"/>
       <c r="P918" t="n">
@@ -54986,7 +54986,7 @@
         <v>0</v>
       </c>
       <c r="N919" t="n">
-        <v>200.1835611942795</v>
+        <v>200.1835611942511</v>
       </c>
       <c r="O919" t="inlineStr"/>
       <c r="P919" t="n">
@@ -55043,7 +55043,7 @@
         <v>0</v>
       </c>
       <c r="N920" t="n">
-        <v>7.42672119429244</v>
+        <v>7.426721194264019</v>
       </c>
       <c r="O920" t="inlineStr"/>
       <c r="P920" t="n">
@@ -55100,7 +55100,7 @@
         <v>0</v>
       </c>
       <c r="N921" t="n">
-        <v>45.91803119427595</v>
+        <v>45.91803119424753</v>
       </c>
       <c r="O921" t="inlineStr"/>
       <c r="P921" t="n">
@@ -55157,7 +55157,7 @@
         <v>0</v>
       </c>
       <c r="N922" t="n">
-        <v>6.13761119427636</v>
+        <v>6.137611194247938</v>
       </c>
       <c r="O922" t="inlineStr"/>
       <c r="P922" t="n">
@@ -55214,7 +55214,7 @@
         <v>0</v>
       </c>
       <c r="N923" t="n">
-        <v>2.020251194267075</v>
+        <v>2.020251194238654</v>
       </c>
       <c r="O923" t="inlineStr"/>
       <c r="P923" t="n">
@@ -55271,7 +55271,7 @@
         <v>0</v>
       </c>
       <c r="N924" t="n">
-        <v>16.2967811942849</v>
+        <v>16.29678119425648</v>
       </c>
       <c r="O924" t="inlineStr"/>
       <c r="P924" t="n">
@@ -55328,7 +55328,7 @@
         <v>0</v>
       </c>
       <c r="N925" t="n">
-        <v>146.2915411942731</v>
+        <v>146.2915411942447</v>
       </c>
       <c r="O925" t="inlineStr"/>
       <c r="P925" t="n">
@@ -55385,7 +55385,7 @@
         <v>0</v>
       </c>
       <c r="N926" t="n">
-        <v>6.89056119426823</v>
+        <v>6.890561194239808</v>
       </c>
       <c r="O926" t="inlineStr"/>
       <c r="P926" t="n">
@@ -55442,7 +55442,7 @@
         <v>0</v>
       </c>
       <c r="N927" t="n">
-        <v>1.144901194265913</v>
+        <v>1.144901194237491</v>
       </c>
       <c r="O927" t="inlineStr"/>
       <c r="P927" t="n">
@@ -55499,7 +55499,7 @@
         <v>0</v>
       </c>
       <c r="N928" t="n">
-        <v>12.42525119428706</v>
+        <v>12.42525119425864</v>
       </c>
       <c r="O928" t="inlineStr"/>
       <c r="P928" t="n">
@@ -55556,7 +55556,7 @@
         <v>0</v>
       </c>
       <c r="N929" t="n">
-        <v>6.624331194274191</v>
+        <v>6.624331194245769</v>
       </c>
       <c r="O929" t="inlineStr"/>
       <c r="P929" t="n">
@@ -55613,7 +55613,7 @@
         <v>0</v>
       </c>
       <c r="N930" t="n">
-        <v>3.770581194288525</v>
+        <v>3.770581194260103</v>
       </c>
       <c r="O930" t="inlineStr"/>
       <c r="P930" t="n">
@@ -55670,7 +55670,7 @@
         <v>0</v>
       </c>
       <c r="N931" t="n">
-        <v>206.3054711942698</v>
+        <v>206.3054711942414</v>
       </c>
       <c r="O931" t="inlineStr"/>
       <c r="P931" t="n">
